--- a/SALTA 1167/Diciembre/SALTA1167-Diciembre.xlsx
+++ b/SALTA 1167/Diciembre/SALTA1167-Diciembre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\SALTA 1167\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B95CB72-91C7-46C7-ACC6-9FA021E67D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7092D5B-C5D0-43B7-926F-A2D4C688733A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,15 +19,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">EDESUR!$B$3:$J$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$97</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$95</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="139">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -399,27 +399,9 @@
     <t>CAJA B</t>
   </si>
   <si>
-    <t>Transf 18/11</t>
-  </si>
-  <si>
-    <t>Transf 13/11</t>
-  </si>
-  <si>
     <t>Full Clean - Servicio de limpieza</t>
   </si>
   <si>
-    <t>Transf 07/11</t>
-  </si>
-  <si>
-    <t>Service de blindez por cierre defectuoso - Cerrajeria CITTA</t>
-  </si>
-  <si>
-    <t>Transf 27/11</t>
-  </si>
-  <si>
-    <t>Transf 03/11</t>
-  </si>
-  <si>
     <t>Indugar SRL - Compra de pinturas trabajo en medianera</t>
   </si>
   <si>
@@ -429,24 +411,12 @@
     <t>Bonificacion apertura de cuenta bancaria (pago de servicios)</t>
   </si>
   <si>
-    <t>Efectivo</t>
-  </si>
-  <si>
-    <t>GF elevadores - Mantenimiento de ascensores - Mes de septiembre</t>
-  </si>
-  <si>
     <t>VTO 15/01</t>
   </si>
   <si>
     <t>PERÍODO: DICIEMBRE</t>
   </si>
   <si>
-    <t>GF elevadores - Mantenimiento de ascensores - Mes de DICIEMBRE</t>
-  </si>
-  <si>
-    <t>GF elevadores - Mantenimiento de ascensores - Mes de NOVIEMBRE</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chavez Pablo - Impermeabilizacion de medianera </t>
   </si>
   <si>
@@ -454,6 +424,30 @@
   </si>
   <si>
     <t>Transf 22/12</t>
+  </si>
+  <si>
+    <t>Transf 02/12</t>
+  </si>
+  <si>
+    <t>Debito 09/12</t>
+  </si>
+  <si>
+    <t>Lema - Ascensores - Servicio de mantenimiento - Se abona a mes vencido</t>
+  </si>
+  <si>
+    <t>Pintureria Gianonni - Bricol para ceramicos</t>
+  </si>
+  <si>
+    <t>Sr.  Pucheta</t>
+  </si>
+  <si>
+    <t>QUIENES ESTAN MARCADOS DE COLOR VERDE NO HAN ABONADO A LA CUENTA BANCARIA CORRESPONDIENTE. REITERAMOS QUE LOS DATOS DE LA CUENTA EN DONDE DEBEN ABONAR LAS EXPENSAS SON: CONSORCIO DE PROPIETARIOS EDIFICIO CALLE SALTA 1167/1169  - C DE P SALTA 1167 1169 LANUS - CTA CTE $   039 - 22273/6                                                                                                                 CBU: 0720039720000002227368</t>
+  </si>
+  <si>
+    <t>Alejo Moreno</t>
+  </si>
+  <si>
+    <t>QUIENES ESTAN EN VIOLETA NO ESTAN RESPETANDO LOS CENTAVOS AL ABONAR.</t>
   </si>
 </sst>
 </file>
@@ -471,7 +465,7 @@
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -665,8 +659,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -727,6 +728,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="31">
     <border>
@@ -1098,14 +1111,13 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="239">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1150,7 +1162,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1302,9 +1313,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1345,30 +1353,6 @@
     <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1376,13 +1360,23 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1401,14 +1395,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1422,12 +1416,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1443,12 +1431,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1458,9 +1440,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1473,12 +1452,115 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="26" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="26" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="26" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="11" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="11" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="11" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="11" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="26" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="12" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="12" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="12" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="12" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1843,7 +1925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
@@ -1859,111 +1941,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="14"/>
-      <c r="B1" s="53" t="s">
+      <c r="A1" s="13"/>
+      <c r="B1" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="54"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="52"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="15"/>
-      <c r="B2" s="55" t="s">
+      <c r="A2" s="14"/>
+      <c r="B2" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="56"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="54"/>
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15"/>
-      <c r="B3" s="166" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="159" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="166"/>
-      <c r="D3" s="166"/>
-      <c r="E3" s="167"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="73" t="s">
+      <c r="A4" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="20"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="55" t="s">
+      <c r="B5" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="17"/>
+      <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="20"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="169" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="169"/>
+      <c r="B8" s="162" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="162"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="169"/>
-      <c r="C9" s="169"/>
+      <c r="B9" s="162"/>
+      <c r="C9" s="162"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="169"/>
-      <c r="C10" s="169"/>
+      <c r="B10" s="162"/>
+      <c r="C10" s="162"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="168" t="s">
+      <c r="A13" s="161" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="168"/>
-      <c r="C13" s="168"/>
-      <c r="D13" s="168"/>
-      <c r="E13" s="168"/>
+      <c r="B13" s="161"/>
+      <c r="C13" s="161"/>
+      <c r="D13" s="161"/>
+      <c r="E13" s="161"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="168"/>
-      <c r="B14" s="168"/>
-      <c r="C14" s="168"/>
-      <c r="D14" s="168"/>
-      <c r="E14" s="168"/>
+      <c r="A14" s="161"/>
+      <c r="B14" s="161"/>
+      <c r="C14" s="161"/>
+      <c r="D14" s="161"/>
+      <c r="E14" s="161"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="168"/>
-      <c r="B15" s="168"/>
-      <c r="C15" s="168"/>
-      <c r="D15" s="168"/>
-      <c r="E15" s="168"/>
+      <c r="A15" s="161"/>
+      <c r="B15" s="161"/>
+      <c r="C15" s="161"/>
+      <c r="D15" s="161"/>
+      <c r="E15" s="161"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="168"/>
-      <c r="B16" s="168"/>
-      <c r="C16" s="168"/>
-      <c r="D16" s="168"/>
-      <c r="E16" s="168"/>
+      <c r="A16" s="161"/>
+      <c r="B16" s="161"/>
+      <c r="C16" s="161"/>
+      <c r="D16" s="161"/>
+      <c r="E16" s="161"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -1971,99 +2053,99 @@
     </row>
     <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="13"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="12"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="106"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="104"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="164" t="s">
-        <v>124</v>
-      </c>
-      <c r="B22" s="165"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="198">
+      <c r="A22" s="155" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="156"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="153">
         <v>464897.27</v>
       </c>
-      <c r="E22" s="135" t="s">
-        <v>125</v>
-      </c>
-      <c r="H22" s="95"/>
+      <c r="E22" s="113" t="s">
+        <v>131</v>
+      </c>
+      <c r="H22" s="93"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="164"/>
-      <c r="B23" s="165"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="122"/>
-      <c r="E23" s="115"/>
-      <c r="H23" s="95"/>
+      <c r="A23" s="155"/>
+      <c r="B23" s="156"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="113"/>
+      <c r="H23" s="93"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="123"/>
-      <c r="E24" s="137">
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="121"/>
+      <c r="E24" s="134">
         <f>SUM(D22:D23)</f>
         <v>464897.27</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="124"/>
-      <c r="E25" s="136"/>
-    </row>
-    <row r="26" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="170" t="s">
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="122"/>
+      <c r="E25" s="133"/>
+    </row>
+    <row r="26" spans="1:8" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="185" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="171"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="197">
-        <v>66146</v>
-      </c>
-      <c r="E26" s="108" t="s">
+      <c r="B26" s="186"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="184">
+        <v>74591</v>
+      </c>
+      <c r="E26" s="106" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="123"/>
-      <c r="E27" s="107">
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="121"/>
+      <c r="E27" s="105">
         <f>SUM(D26:D26)</f>
-        <v>66146</v>
+        <v>74591</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="110"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="125"/>
-      <c r="E28" s="111"/>
+      <c r="B28" s="108"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="123"/>
+      <c r="E28" s="109"/>
     </row>
     <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
@@ -2071,10 +2153,10 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="116">
-        <v>0</v>
-      </c>
-      <c r="E29" s="115"/>
+      <c r="D29" s="114">
+        <v>0</v>
+      </c>
+      <c r="E29" s="113"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
@@ -2082,608 +2164,583 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="199">
+      <c r="D30" s="154">
         <v>5494.37</v>
       </c>
-      <c r="E30" s="115" t="s">
-        <v>128</v>
+      <c r="E30" s="113" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="132"/>
+      <c r="B31" s="130"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="199">
+      <c r="D31" s="154">
         <v>323182.89</v>
       </c>
-      <c r="E31" s="115" t="s">
+      <c r="E31" s="113" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="163" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="164"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="154">
+        <v>358176.46</v>
+      </c>
+      <c r="E32" s="113" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="116" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="112"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="154">
+        <v>21236.33</v>
+      </c>
+      <c r="E33" s="113" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="124"/>
+      <c r="E34" s="107">
+        <f>SUM(D29:D33)</f>
+        <v>708090.04999999993</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="25"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="121"/>
+      <c r="E35" s="110"/>
+    </row>
+    <row r="36" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="155" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" s="156"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="114"/>
+      <c r="E36" s="115"/>
+    </row>
+    <row r="37" spans="1:5" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="155" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="170" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" s="171"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="199">
-        <v>358176.46</v>
-      </c>
-      <c r="E32" s="115" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="118" t="s">
-        <v>83</v>
-      </c>
-      <c r="B33" s="114"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="116">
-        <v>20718.39</v>
-      </c>
-      <c r="E33" s="115" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="126"/>
-      <c r="E34" s="109">
-        <f>SUM(D29:D33)</f>
-        <v>707572.11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="26"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="123"/>
-      <c r="E35" s="112"/>
-    </row>
-    <row r="36" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="164" t="s">
-        <v>133</v>
-      </c>
-      <c r="B36" s="165"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="116">
-        <v>75000</v>
-      </c>
-      <c r="E36" s="117" t="s">
+      <c r="B37" s="156"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="152">
+        <v>1537000</v>
+      </c>
+      <c r="E37" s="115" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="155" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="164" t="s">
-        <v>137</v>
-      </c>
-      <c r="B37" s="165"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="116">
-        <v>75000</v>
-      </c>
-      <c r="E37" s="117" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="164" t="s">
-        <v>136</v>
-      </c>
-      <c r="B38" s="165"/>
+      <c r="B38" s="156"/>
       <c r="C38" s="5"/>
-      <c r="D38" s="116">
-        <v>75000</v>
-      </c>
-      <c r="E38" s="117" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="133" t="s">
-        <v>138</v>
-      </c>
-      <c r="B39" s="134"/>
+      <c r="D38" s="152">
+        <v>42370</v>
+      </c>
+      <c r="E38" s="115" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="155" t="s">
+        <v>134</v>
+      </c>
+      <c r="B39" s="156"/>
       <c r="C39" s="5"/>
-      <c r="D39" s="196">
-        <v>1537000</v>
-      </c>
-      <c r="E39" s="117" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="164" t="s">
-        <v>129</v>
-      </c>
-      <c r="B40" s="165"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="196">
-        <v>51267.81</v>
-      </c>
-      <c r="E40" s="117" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="164" t="s">
-        <v>126</v>
-      </c>
-      <c r="B41" s="165"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="80">
-        <v>90000</v>
-      </c>
-      <c r="E41" s="117" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="22" t="s">
+      <c r="D39" s="152">
+        <v>24884.21</v>
+      </c>
+      <c r="E39" s="115" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="107">
-        <f>SUM(D36:D41)</f>
-        <v>1903267.81</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="26" t="s">
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="105">
+        <f>SUM(D36:D39)</f>
+        <v>1604254.21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="121"/>
-      <c r="E43" s="106"/>
-    </row>
-    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="164" t="s">
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="119"/>
+      <c r="E41" s="104"/>
+    </row>
+    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="155" t="s">
         <v>29</v>
       </c>
-      <c r="B44" s="165"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="122">
+      <c r="B42" s="156"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="153">
         <v>140000</v>
       </c>
-      <c r="E44" s="140"/>
-    </row>
-    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="133"/>
-      <c r="B45" s="134"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="151"/>
-      <c r="E45" s="140"/>
+      <c r="E42" s="137"/>
+    </row>
+    <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="131"/>
+      <c r="B43" s="132"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="148"/>
+      <c r="E43" s="137"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="121"/>
+      <c r="E44" s="134">
+        <f>SUM(D42:D43)</f>
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="49"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="118"/>
+      <c r="E45" s="105"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="22" t="s">
+      <c r="A46" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="114"/>
+      <c r="E46" s="111"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="154">
+        <f>40662.21-311.85-1485-4686.04-151.2-720-450</f>
+        <v>32858.120000000003</v>
+      </c>
+      <c r="E47" s="29"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="123"/>
-      <c r="E46" s="137">
-        <f>SUM(D44:D45)</f>
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B47" s="51"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="120"/>
-      <c r="E47" s="107"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="116"/>
-      <c r="E48" s="113"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="38"/>
+      <c r="D48" s="80"/>
+      <c r="E48" s="135">
+        <f>SUM(D46:D47)</f>
+        <v>32858.120000000003</v>
+      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
-        <v>130</v>
-      </c>
+      <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="116">
-        <f>35049.2-9-40</f>
-        <v>35000.199999999997</v>
-      </c>
-      <c r="E49" s="30"/>
+      <c r="D49" s="75"/>
+      <c r="E49" s="81"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" s="39"/>
-      <c r="C50" s="39"/>
+      <c r="A50" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
       <c r="D50" s="82"/>
-      <c r="E50" s="138">
-        <f>SUM(D48:D49)</f>
-        <v>35000.199999999997</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="77"/>
-      <c r="E51" s="83"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="84"/>
-      <c r="E52" s="139"/>
-    </row>
-    <row r="53" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="1"/>
-      <c r="D53" s="85"/>
-      <c r="E53" s="86"/>
-      <c r="F53" s="32"/>
+      <c r="E50" s="136"/>
+    </row>
+    <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="1"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="84"/>
+      <c r="F51" s="31"/>
+    </row>
+    <row r="52" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" s="8"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="85"/>
+      <c r="E52" s="86">
+        <f>(SUM(E21:E50))</f>
+        <v>3024690.65</v>
+      </c>
+      <c r="F52" s="103"/>
+      <c r="G52" s="31"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D53" s="83"/>
+      <c r="E53" s="83"/>
     </row>
     <row r="54" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B54" s="9"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="87"/>
-      <c r="E54" s="88">
-        <f>(SUM(E21:E52))</f>
-        <v>3316883.39</v>
-      </c>
-      <c r="F54" s="105"/>
-      <c r="G54" s="32"/>
+      <c r="D54" s="83"/>
+      <c r="E54" s="83"/>
+      <c r="H54" s="125"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D55" s="85"/>
-      <c r="E55" s="85"/>
-    </row>
-    <row r="56" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D56" s="85"/>
-      <c r="E56" s="85"/>
-      <c r="H56" s="127"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="10" t="s">
+      <c r="A55" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B57" s="11"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="89"/>
-      <c r="E57" s="90"/>
-    </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="79"/>
-      <c r="B58" s="114"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="87"/>
+      <c r="E55" s="88"/>
+    </row>
+    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="77"/>
+      <c r="B56" s="112"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="78"/>
+      <c r="E56" s="76"/>
+    </row>
+    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="187"/>
+      <c r="B57" s="187"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="114"/>
+      <c r="E57" s="76"/>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="5"/>
+      <c r="B58" s="5"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="80"/>
-      <c r="E58" s="78"/>
-    </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="164"/>
-      <c r="B59" s="165"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="77"/>
+      <c r="B59" s="79"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="80"/>
-      <c r="E59" s="78"/>
-    </row>
-    <row r="60" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="79"/>
-      <c r="B61" s="81"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="80"/>
-      <c r="E61" s="78"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="37"/>
-      <c r="B62" s="36"/>
-      <c r="C62" s="36"/>
-      <c r="D62" s="44"/>
-      <c r="E62" s="44">
-        <f>SUM(D58:D61)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+      <c r="D59" s="78"/>
+      <c r="E59" s="76"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="36"/>
+      <c r="B60" s="35"/>
+      <c r="C60" s="35"/>
+      <c r="D60" s="42"/>
+      <c r="E60" s="42">
+        <f>SUM(D56:D59)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="B63" s="22"/>
+      <c r="C63" s="22"/>
+      <c r="D63" s="23"/>
+      <c r="E63" s="74"/>
+    </row>
+    <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="B65" s="23"/>
-      <c r="C65" s="23"/>
-      <c r="D65" s="24"/>
-      <c r="E65" s="76"/>
+      <c r="A65" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B65" s="8"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="50">
+        <f>E60+E63</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B67" s="9"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="52">
-        <f>E62+E65</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+      <c r="A67" s="72" t="s">
+        <v>112</v>
+      </c>
+      <c r="B67" s="73">
+        <f>E52</f>
+        <v>3024690.65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="72" t="s">
+        <v>113</v>
+      </c>
+      <c r="B68" s="73">
+        <f>E52-E50</f>
+        <v>3024690.65</v>
+      </c>
+    </row>
     <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="74" t="s">
-        <v>112</v>
-      </c>
-      <c r="B69" s="75">
-        <f>E54</f>
-        <v>3316883.39</v>
+      <c r="A69" s="72" t="s">
+        <v>114</v>
+      </c>
+      <c r="B69" s="73">
+        <f>E65-E63</f>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="74" t="s">
-        <v>113</v>
-      </c>
-      <c r="B70" s="75">
-        <f>E54-E52</f>
-        <v>3316883.39</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="74" t="s">
-        <v>114</v>
-      </c>
-      <c r="B71" s="75">
-        <f>E67-E65</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="74" t="s">
+      <c r="A70" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="B72" s="75">
-        <f>E67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A74"/>
-      <c r="B74" s="31"/>
-      <c r="C74" s="28"/>
-    </row>
-    <row r="75" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="97" t="s">
+      <c r="B70" s="73">
+        <f>E65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72"/>
+      <c r="B72" s="30"/>
+      <c r="C72" s="27"/>
+    </row>
+    <row r="73" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="95" t="s">
         <v>116</v>
       </c>
-      <c r="B75" s="162">
-        <v>610252.12999999989</v>
-      </c>
-      <c r="C75" s="28"/>
-      <c r="D75" s="35"/>
+      <c r="B73" s="151">
+        <v>115565.9499999996</v>
+      </c>
+      <c r="C73" s="27"/>
+      <c r="D73" s="34"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="B74" s="100">
+        <f>-B68</f>
+        <v>-3024690.65</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B75" s="100">
+        <f>B94</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="B76" s="102">
-        <f>-B70</f>
-        <v>-3316883.39</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="42" t="s">
+      <c r="A76" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="B76" s="101">
+        <f>PRORRATEO!G36-B84</f>
+        <v>1986908.7200000002</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="B77" s="101">
+        <f>102287.66+2747.19</f>
+        <v>105034.85</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" s="126"/>
+    </row>
+    <row r="79" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="98" t="s">
+        <v>120</v>
+      </c>
+      <c r="B79" s="99">
+        <f>SUM(B73:C78)</f>
+        <v>-817181.13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="96"/>
+      <c r="B80" s="96"/>
+      <c r="D80" s="31"/>
+      <c r="E80" s="30"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A81" s="95" t="s">
+        <v>117</v>
+      </c>
+      <c r="B81" s="151">
+        <v>2000000</v>
+      </c>
+      <c r="D81" s="30"/>
+      <c r="E81" s="31"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A82" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="B82" s="100">
+        <f>-B69</f>
+        <v>0</v>
+      </c>
+      <c r="D82" s="31"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A83" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="B77" s="102">
-        <f>B96</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="B78" s="103">
-        <f>PRORRATEO!G34-B86</f>
-        <v>2038799.4999999998</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A79" s="42" t="s">
-        <v>131</v>
-      </c>
-      <c r="B79" s="103">
-        <f>2728.58+121218.14+160659.23+10359.2</f>
-        <v>294965.15000000002</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="104" t="s">
+      <c r="B83" s="100">
+        <f>B102</f>
+        <v>0</v>
+      </c>
+      <c r="D83" s="31"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A84" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="B84" s="101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A85" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="B80" s="128"/>
-    </row>
-    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="100" t="s">
-        <v>120</v>
-      </c>
-      <c r="B81" s="101">
-        <f>SUM(B75:C80)</f>
-        <v>-372866.61000000045</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="98"/>
-      <c r="B82" s="98"/>
-      <c r="D82" s="32"/>
-      <c r="E82" s="31"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="97" t="s">
-        <v>117</v>
-      </c>
-      <c r="B83" s="162">
+      <c r="B85" s="126"/>
+    </row>
+    <row r="86" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="B86" s="99">
+        <f>SUM(B81:C85)</f>
         <v>2000000</v>
       </c>
-      <c r="D83" s="31"/>
-      <c r="E83" s="32"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="B84" s="102">
-        <f>-B71</f>
-        <v>0</v>
-      </c>
-      <c r="D84" s="32"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="B85" s="102">
-        <f>B104</f>
-        <v>0</v>
-      </c>
-      <c r="D85" s="32"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="42" t="s">
-        <v>119</v>
-      </c>
-      <c r="B86" s="103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="104" t="s">
-        <v>25</v>
-      </c>
-      <c r="B87" s="128"/>
-    </row>
-    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="100" t="s">
-        <v>121</v>
-      </c>
-      <c r="B88" s="101">
-        <f>SUM(B83:C87)</f>
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="98"/>
-      <c r="B89" s="98"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" s="98"/>
-      <c r="B90" s="98"/>
-    </row>
-    <row r="91" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="173" t="s">
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87" s="96"/>
+      <c r="B87" s="96"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A88" s="96"/>
+      <c r="B88" s="96"/>
+    </row>
+    <row r="89" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A90" s="158" t="s">
         <v>19</v>
       </c>
-      <c r="B92" s="173"/>
-      <c r="C92" s="173"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="173"/>
-      <c r="B93" s="173"/>
-      <c r="C93" s="173"/>
-    </row>
-    <row r="94" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="92"/>
-      <c r="B94" s="27"/>
-      <c r="C94" s="27">
+      <c r="B90" s="158"/>
+      <c r="C90" s="158"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A91" s="158"/>
+      <c r="B91" s="158"/>
+      <c r="C91" s="158"/>
+    </row>
+    <row r="92" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="90"/>
+      <c r="B92" s="26"/>
+      <c r="C92" s="26">
         <v>40000</v>
       </c>
-      <c r="E94" s="105"/>
-    </row>
-    <row r="95" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="92"/>
-      <c r="B95" s="94"/>
-      <c r="C95" s="91"/>
-      <c r="D95" s="105"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="33" t="s">
+      <c r="E92" s="103"/>
+    </row>
+    <row r="93" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="90"/>
+      <c r="B93" s="92"/>
+      <c r="C93" s="89"/>
+      <c r="D93" s="103"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A94" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B96" s="93">
-        <f>SUM(B94:B95)</f>
-        <v>0</v>
-      </c>
-      <c r="C96" s="34"/>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M97" s="7"/>
-    </row>
-    <row r="98" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="172"/>
-      <c r="B98" s="172"/>
-      <c r="C98" s="172"/>
-      <c r="D98" s="172"/>
-      <c r="E98" s="172"/>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A99" s="172"/>
-      <c r="B99" s="172"/>
-      <c r="C99" s="172"/>
-      <c r="D99" s="172"/>
-      <c r="E99" s="172"/>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A100" s="172"/>
-      <c r="B100" s="172"/>
-      <c r="C100" s="172"/>
-      <c r="D100" s="172"/>
-      <c r="E100" s="172"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A101" s="172"/>
-      <c r="B101" s="172"/>
-      <c r="C101" s="172"/>
-      <c r="D101" s="172"/>
-      <c r="E101" s="172"/>
+      <c r="B94" s="91">
+        <f>SUM(B92:B93)</f>
+        <v>0</v>
+      </c>
+      <c r="C94" s="33"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M95" s="6"/>
+    </row>
+    <row r="96" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="157"/>
+      <c r="B96" s="157"/>
+      <c r="C96" s="157"/>
+      <c r="D96" s="157"/>
+      <c r="E96" s="157"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="157"/>
+      <c r="B97" s="157"/>
+      <c r="C97" s="157"/>
+      <c r="D97" s="157"/>
+      <c r="E97" s="157"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="157"/>
+      <c r="B98" s="157"/>
+      <c r="C98" s="157"/>
+      <c r="D98" s="157"/>
+      <c r="E98" s="157"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="157"/>
+      <c r="B99" s="157"/>
+      <c r="C99" s="157"/>
+      <c r="D99" s="157"/>
+      <c r="E99" s="157"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A98:E101"/>
-    <mergeCell ref="A92:C93"/>
-    <mergeCell ref="A59:B59"/>
+  <mergeCells count="15">
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A40:B40"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A96:E99"/>
+    <mergeCell ref="A90:C91"/>
+    <mergeCell ref="A57:B57"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2693,7 +2750,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="4.33203125" customWidth="1"/>
@@ -2709,1717 +2766,1774 @@
     <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.6640625" customWidth="1"/>
     <col min="14" max="14" width="12" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" customWidth="1"/>
-    <col min="16" max="16" width="0.109375" customWidth="1"/>
+    <col min="15" max="15" width="14.21875" customWidth="1"/>
+    <col min="16" max="16" width="7.21875" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="174"/>
-      <c r="I1" s="174"/>
-      <c r="J1" s="174"/>
-      <c r="K1" s="174"/>
-      <c r="L1" s="174"/>
-      <c r="M1" s="174"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
+      <c r="A1" s="201"/>
+      <c r="B1" s="202"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="204"/>
+      <c r="K1" s="204"/>
+      <c r="L1" s="204"/>
+      <c r="M1" s="204"/>
+      <c r="N1" s="202"/>
+      <c r="O1" s="205"/>
     </row>
     <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="152"/>
-      <c r="D2" s="153"/>
-      <c r="E2" s="153" t="s">
+      <c r="A2" s="206"/>
+      <c r="B2" s="207"/>
+      <c r="C2" s="208"/>
+      <c r="D2" s="209"/>
+      <c r="E2" s="209" t="s">
         <v>102</v>
       </c>
-      <c r="F2" s="153"/>
-      <c r="G2" s="154">
-        <v>0</v>
-      </c>
-      <c r="H2" s="153"/>
-      <c r="I2" s="153"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="153" t="s">
+      <c r="F2" s="209"/>
+      <c r="G2" s="210">
+        <v>0</v>
+      </c>
+      <c r="H2" s="209"/>
+      <c r="I2" s="209"/>
+      <c r="J2" s="211"/>
+      <c r="K2" s="209" t="s">
         <v>101</v>
       </c>
-      <c r="L2" s="156">
+      <c r="L2" s="212">
         <v>2000000</v>
       </c>
-      <c r="M2" s="157"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="21"/>
-    </row>
-    <row r="3" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="152"/>
-      <c r="D3" s="152"/>
-      <c r="E3" s="152"/>
-      <c r="F3" s="152"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="152"/>
-      <c r="I3" s="152"/>
-      <c r="J3" s="159"/>
-      <c r="K3" s="152"/>
-      <c r="L3" s="152"/>
-      <c r="M3" s="157"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="21"/>
+      <c r="M2" s="213"/>
+      <c r="N2" s="214"/>
+      <c r="O2" s="215"/>
+      <c r="P2" s="20"/>
+    </row>
+    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="206"/>
+      <c r="B3" s="207"/>
+      <c r="C3" s="208"/>
+      <c r="D3" s="208"/>
+      <c r="E3" s="208"/>
+      <c r="F3" s="208"/>
+      <c r="G3" s="216"/>
+      <c r="H3" s="208"/>
+      <c r="I3" s="208"/>
+      <c r="J3" s="217"/>
+      <c r="K3" s="208"/>
+      <c r="L3" s="208"/>
+      <c r="M3" s="213"/>
+      <c r="N3" s="214"/>
+      <c r="O3" s="215"/>
+      <c r="P3" s="20"/>
     </row>
     <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="223" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="187"/>
-      <c r="C4" s="187"/>
-      <c r="D4" s="187"/>
-      <c r="E4" s="187"/>
-      <c r="F4" s="187"/>
-      <c r="G4" s="187"/>
-      <c r="H4" s="187"/>
-      <c r="I4" s="187"/>
-      <c r="J4" s="187"/>
-      <c r="K4" s="187"/>
-      <c r="L4" s="187"/>
-      <c r="M4" s="187"/>
-      <c r="N4" s="187"/>
-      <c r="O4" s="187"/>
-      <c r="P4" s="21"/>
+      <c r="B4" s="224"/>
+      <c r="C4" s="224"/>
+      <c r="D4" s="224"/>
+      <c r="E4" s="224"/>
+      <c r="F4" s="224"/>
+      <c r="G4" s="224"/>
+      <c r="H4" s="224"/>
+      <c r="I4" s="224"/>
+      <c r="J4" s="224"/>
+      <c r="K4" s="224"/>
+      <c r="L4" s="224"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="225"/>
+      <c r="P4" s="20"/>
     </row>
     <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="187"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="187"/>
-      <c r="D5" s="187"/>
-      <c r="E5" s="187"/>
-      <c r="F5" s="187"/>
-      <c r="G5" s="187"/>
-      <c r="H5" s="187"/>
-      <c r="I5" s="187"/>
-      <c r="J5" s="187"/>
-      <c r="K5" s="187"/>
-      <c r="L5" s="187"/>
-      <c r="M5" s="187"/>
-      <c r="N5" s="187"/>
-      <c r="O5" s="187"/>
-      <c r="P5" s="21"/>
+      <c r="A5" s="220"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="218"/>
+      <c r="E5" s="218"/>
+      <c r="F5" s="218"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="218"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="218"/>
+      <c r="K5" s="218"/>
+      <c r="L5" s="218"/>
+      <c r="M5" s="218"/>
+      <c r="N5" s="218"/>
+      <c r="O5" s="219"/>
+      <c r="P5" s="20"/>
     </row>
     <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="187"/>
-      <c r="B6" s="187"/>
-      <c r="C6" s="187"/>
-      <c r="D6" s="187"/>
-      <c r="E6" s="187"/>
-      <c r="F6" s="187"/>
-      <c r="G6" s="187"/>
-      <c r="H6" s="187"/>
-      <c r="I6" s="187"/>
-      <c r="J6" s="187"/>
-      <c r="K6" s="187"/>
-      <c r="L6" s="187"/>
-      <c r="M6" s="187"/>
-      <c r="N6" s="187"/>
-      <c r="O6" s="187"/>
-      <c r="P6" s="21"/>
+      <c r="A6" s="220"/>
+      <c r="B6" s="218"/>
+      <c r="C6" s="218"/>
+      <c r="D6" s="218"/>
+      <c r="E6" s="218"/>
+      <c r="F6" s="218"/>
+      <c r="G6" s="218"/>
+      <c r="H6" s="218"/>
+      <c r="I6" s="218"/>
+      <c r="J6" s="218"/>
+      <c r="K6" s="218"/>
+      <c r="L6" s="218"/>
+      <c r="M6" s="218"/>
+      <c r="N6" s="218"/>
+      <c r="O6" s="219"/>
+      <c r="P6" s="20"/>
     </row>
     <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="187"/>
-      <c r="B7" s="187"/>
-      <c r="C7" s="187"/>
-      <c r="D7" s="187"/>
-      <c r="E7" s="187"/>
-      <c r="F7" s="187"/>
-      <c r="G7" s="187"/>
-      <c r="H7" s="187"/>
-      <c r="I7" s="187"/>
-      <c r="J7" s="187"/>
-      <c r="K7" s="187"/>
-      <c r="L7" s="187"/>
-      <c r="M7" s="187"/>
-      <c r="N7" s="187"/>
-      <c r="O7" s="187"/>
-      <c r="P7" s="21"/>
+      <c r="A7" s="220"/>
+      <c r="B7" s="218"/>
+      <c r="C7" s="218"/>
+      <c r="D7" s="218"/>
+      <c r="E7" s="218"/>
+      <c r="F7" s="218"/>
+      <c r="G7" s="218"/>
+      <c r="H7" s="218"/>
+      <c r="I7" s="218"/>
+      <c r="J7" s="218"/>
+      <c r="K7" s="218"/>
+      <c r="L7" s="218"/>
+      <c r="M7" s="218"/>
+      <c r="N7" s="218"/>
+      <c r="O7" s="219"/>
+      <c r="P7" s="20"/>
     </row>
     <row r="8" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="188"/>
-      <c r="B8" s="188"/>
-      <c r="C8" s="188"/>
-      <c r="D8" s="188"/>
-      <c r="E8" s="188"/>
-      <c r="F8" s="188"/>
-      <c r="G8" s="188"/>
-      <c r="H8" s="188"/>
-      <c r="I8" s="188"/>
-      <c r="J8" s="188"/>
-      <c r="K8" s="188"/>
-      <c r="L8" s="188"/>
-      <c r="M8" s="188"/>
-      <c r="N8" s="188"/>
-      <c r="O8" s="188"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="179" t="s">
+      <c r="A8" s="221"/>
+      <c r="B8" s="177"/>
+      <c r="C8" s="177"/>
+      <c r="D8" s="177"/>
+      <c r="E8" s="177"/>
+      <c r="F8" s="177"/>
+      <c r="G8" s="177"/>
+      <c r="H8" s="177"/>
+      <c r="I8" s="177"/>
+      <c r="J8" s="177"/>
+      <c r="K8" s="177"/>
+      <c r="L8" s="177"/>
+      <c r="M8" s="177"/>
+      <c r="N8" s="177"/>
+      <c r="O8" s="222"/>
+    </row>
+    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="226" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" s="227"/>
+      <c r="C9" s="227"/>
+      <c r="D9" s="227"/>
+      <c r="E9" s="227"/>
+      <c r="F9" s="227"/>
+      <c r="G9" s="227"/>
+      <c r="H9" s="227"/>
+      <c r="I9" s="227"/>
+      <c r="J9" s="227"/>
+      <c r="K9" s="227"/>
+      <c r="L9" s="227"/>
+      <c r="M9" s="227"/>
+      <c r="N9" s="227"/>
+      <c r="O9" s="227"/>
+    </row>
+    <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="228" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" s="228"/>
+      <c r="C10" s="228"/>
+      <c r="D10" s="228"/>
+      <c r="E10" s="228"/>
+      <c r="F10" s="228"/>
+      <c r="G10" s="228"/>
+      <c r="H10" s="228"/>
+      <c r="I10" s="228"/>
+      <c r="J10" s="228"/>
+      <c r="K10" s="228"/>
+      <c r="L10" s="228"/>
+      <c r="M10" s="228"/>
+      <c r="N10" s="228"/>
+      <c r="O10" s="228"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="165" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="129"/>
-      <c r="C9" s="179" t="s">
+      <c r="B11" s="127"/>
+      <c r="C11" s="165" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="179" t="s">
+      <c r="D11" s="165" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="179" t="s">
+      <c r="E11" s="165" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="175" t="s">
+      <c r="F11" s="168" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="179" t="s">
+      <c r="G11" s="165" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="181" t="s">
+      <c r="H11" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="175" t="s">
+      <c r="I11" s="168" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="175" t="s">
+      <c r="J11" s="168" t="s">
         <v>84</v>
       </c>
-      <c r="K9" s="175" t="s">
+      <c r="K11" s="168" t="s">
         <v>101</v>
       </c>
-      <c r="L9" s="184" t="s">
+      <c r="L11" s="175" t="s">
         <v>102</v>
       </c>
-      <c r="M9" s="47" t="s">
+      <c r="M11" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="N9" s="177" t="s">
+      <c r="N11" s="170" t="s">
         <v>12</v>
       </c>
-      <c r="O9" s="189" t="s">
+      <c r="O11" s="178" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="180"/>
-      <c r="B10" s="130"/>
-      <c r="C10" s="180"/>
-      <c r="D10" s="191"/>
-      <c r="E10" s="180"/>
-      <c r="F10" s="176"/>
-      <c r="G10" s="180"/>
-      <c r="H10" s="182"/>
-      <c r="I10" s="176"/>
-      <c r="J10" s="183"/>
-      <c r="K10" s="176"/>
-      <c r="L10" s="185"/>
-      <c r="M10" s="45" t="str">
+    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="167"/>
+      <c r="B12" s="128"/>
+      <c r="C12" s="167"/>
+      <c r="D12" s="166"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="169"/>
+      <c r="G12" s="167"/>
+      <c r="H12" s="173"/>
+      <c r="I12" s="169"/>
+      <c r="J12" s="174"/>
+      <c r="K12" s="169"/>
+      <c r="L12" s="176"/>
+      <c r="M12" s="43" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 15/01</v>
       </c>
-      <c r="N10" s="178"/>
-      <c r="O10" s="190"/>
-    </row>
-    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="48">
+      <c r="N12" s="171"/>
+      <c r="O12" s="179"/>
+    </row>
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="46">
         <v>1</v>
       </c>
-      <c r="B11" s="48" t="s">
+      <c r="B13" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C13" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="48"/>
-      <c r="E11" s="57">
+      <c r="D13" s="46"/>
+      <c r="E13" s="55">
         <v>12</v>
       </c>
-      <c r="F11" s="58">
-        <v>239940.01</v>
-      </c>
-      <c r="G11" s="59">
-        <f>271858-G27-G28</f>
-        <v>247857.65</v>
-      </c>
-      <c r="H11" s="60">
-        <f t="shared" ref="H11:H33" si="0">F11-G11</f>
-        <v>-7917.6399999999849</v>
-      </c>
-      <c r="I11" s="60">
-        <f>IF(H11&gt;0,H11*3%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="61">
+      <c r="F13" s="56">
+        <v>232082.01</v>
+      </c>
+      <c r="G13" s="188">
+        <f>256082.01-G29-G30</f>
+        <v>232081.66</v>
+      </c>
+      <c r="H13" s="58">
+        <f t="shared" ref="H13:H35" si="0">F13-G13</f>
+        <v>0.35000000000582077</v>
+      </c>
+      <c r="I13" s="58">
+        <f>IF(H13&gt;0,H13*3%,0)</f>
+        <v>1.0500000000174623E-2</v>
+      </c>
+      <c r="J13" s="59">
         <f>EDESUR!I5</f>
         <v>0</v>
       </c>
-      <c r="K11" s="119">
-        <f>L$2*E11/100</f>
+      <c r="K13" s="117">
+        <f>L$2*E13/100</f>
         <v>240000</v>
       </c>
-      <c r="L11" s="119">
-        <f>G$2*E11/100</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="62">
-        <f>ROUND(SUM(H11:L11),0) + P11</f>
-        <v>232082.01</v>
-      </c>
-      <c r="N11" s="63">
-        <f>ROUND(M11*6% + M11,0) + P11</f>
-        <v>246007.01</v>
-      </c>
-      <c r="O11" s="64">
-        <f>ROUND(M11*3%,0) + M11</f>
-        <v>239044.01</v>
-      </c>
-      <c r="P11" s="32">
+      <c r="L13" s="117">
+        <f>G$2*E13/100</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="60">
+        <f>ROUND(SUM(H13:L13),0) + P13</f>
+        <v>240000.01</v>
+      </c>
+      <c r="N13" s="61">
+        <f>ROUND(M13*6% + M13,0) + P13</f>
+        <v>254400.01</v>
+      </c>
+      <c r="O13" s="62">
+        <f>ROUND(M13*3%,0) + M13</f>
+        <v>247200.01</v>
+      </c>
+      <c r="P13" s="31">
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="46">
         <v>2</v>
       </c>
-      <c r="B12" s="48" t="s">
+      <c r="B14" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C14" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="57">
+      <c r="D14" s="47"/>
+      <c r="E14" s="55">
         <v>6.6</v>
       </c>
-      <c r="F12" s="58">
+      <c r="F14" s="56">
         <v>132000.01999999999</v>
       </c>
-      <c r="G12" s="59">
-        <f>F12</f>
+      <c r="G14" s="188">
+        <f>F14</f>
         <v>132000.01999999999</v>
       </c>
-      <c r="H12" s="60">
+      <c r="H14" s="58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="60">
-        <f t="shared" ref="I12:I33" si="1">IF(H12&gt;0,H12*3%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="61">
+      <c r="I14" s="58">
+        <f t="shared" ref="I14:I35" si="1">IF(H14&gt;0,H14*3%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="59">
         <f>EDESUR!I6</f>
         <v>0</v>
       </c>
-      <c r="K12" s="119">
-        <f t="shared" ref="K12:K33" si="2">L$2*E12/100</f>
+      <c r="K14" s="117">
+        <f t="shared" ref="K14:K35" si="2">L$2*E14/100</f>
         <v>132000</v>
       </c>
-      <c r="L12" s="119">
-        <f t="shared" ref="L12:L33" si="3">G$2*E12/100</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="62">
-        <f t="shared" ref="M12:M33" si="4">ROUND(SUM(H12:L12),0) + P12</f>
+      <c r="L14" s="117">
+        <f t="shared" ref="L14:L35" si="3">G$2*E14/100</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="60">
+        <f t="shared" ref="M14:M35" si="4">ROUND(SUM(H14:L14),0) + P14</f>
         <v>132000.01999999999</v>
       </c>
-      <c r="N12" s="63">
-        <f t="shared" ref="N12:N28" si="5">ROUND(M12*6% + M12,0) + P12</f>
+      <c r="N14" s="61">
+        <f t="shared" ref="N14:N30" si="5">ROUND(M14*6% + M14,0) + P14</f>
         <v>139920.01999999999</v>
       </c>
-      <c r="O12" s="64">
-        <f t="shared" ref="O12:O33" si="6">ROUND(M12*3%,0) + M12</f>
+      <c r="O14" s="62">
+        <f t="shared" ref="O14:O35" si="6">ROUND(M14*3%,0) + M14</f>
         <v>135960.01999999999</v>
       </c>
-      <c r="P12" s="32">
-        <f>P11+0.01</f>
+      <c r="P14" s="31">
+        <f>P13+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="48">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="46">
         <v>3</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B15" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C15" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="49" t="s">
+      <c r="D15" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="57">
+      <c r="E15" s="55">
         <v>5.4</v>
       </c>
-      <c r="F13" s="58">
+      <c r="F15" s="56">
         <v>108000.03</v>
       </c>
-      <c r="G13" s="59">
-        <f>F13</f>
+      <c r="G15" s="188">
+        <f>F15</f>
         <v>108000.03</v>
       </c>
-      <c r="H13" s="60">
+      <c r="H15" s="58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="60">
+      <c r="I15" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J13" s="61">
+      <c r="J15" s="59">
         <f>EDESUR!I7</f>
         <v>0</v>
       </c>
-      <c r="K13" s="119">
+      <c r="K15" s="117">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L13" s="119">
+      <c r="L15" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M13" s="62">
+      <c r="M15" s="60">
         <f t="shared" si="4"/>
         <v>108000.03</v>
       </c>
-      <c r="N13" s="63">
+      <c r="N15" s="61">
         <f t="shared" si="5"/>
         <v>114480.03</v>
       </c>
-      <c r="O13" s="64">
+      <c r="O15" s="62">
         <f t="shared" si="6"/>
         <v>111240.03</v>
       </c>
-      <c r="P13" s="32">
-        <f t="shared" ref="P13:P28" si="7">P12+0.01</f>
+      <c r="P15" s="31">
+        <f t="shared" ref="P15:P30" si="7">P14+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="48">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="46">
         <v>4</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B16" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C16" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D16" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="57">
+      <c r="E16" s="55">
         <v>6.6</v>
       </c>
-      <c r="F14" s="58">
-        <v>132000.04</v>
-      </c>
-      <c r="G14" s="59">
-        <f>134300</f>
-        <v>134300</v>
-      </c>
-      <c r="H14" s="60">
+      <c r="F16" s="56">
+        <v>129700.04</v>
+      </c>
+      <c r="G16" s="188">
+        <f>154060-G32</f>
+        <v>129700</v>
+      </c>
+      <c r="H16" s="58">
         <f t="shared" si="0"/>
-        <v>-2299.9599999999919</v>
-      </c>
-      <c r="I14" s="60">
+        <v>3.9999999993597157E-2</v>
+      </c>
+      <c r="I16" s="58">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="61">
+        <v>1.1999999998079146E-3</v>
+      </c>
+      <c r="J16" s="59">
         <f>EDESUR!I8</f>
         <v>0</v>
       </c>
-      <c r="K14" s="119">
+      <c r="K16" s="117">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L14" s="119">
+      <c r="L16" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M14" s="62">
+      <c r="M16" s="60">
         <f t="shared" si="4"/>
-        <v>129700.04</v>
-      </c>
-      <c r="N14" s="63">
+        <v>132000.04</v>
+      </c>
+      <c r="N16" s="61">
         <f t="shared" si="5"/>
-        <v>137482.04</v>
-      </c>
-      <c r="O14" s="64">
+        <v>139920.04</v>
+      </c>
+      <c r="O16" s="62">
         <f t="shared" si="6"/>
-        <v>133591.03999999998</v>
-      </c>
-      <c r="P14" s="32">
+        <v>135960.04</v>
+      </c>
+      <c r="P16" s="31">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="48">
+    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="229">
         <v>5</v>
       </c>
-      <c r="B15" s="48" t="s">
+      <c r="B17" s="229" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="48" t="s">
+      <c r="C17" s="229" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="48" t="s">
+      <c r="D17" s="229" t="s">
         <v>99</v>
       </c>
-      <c r="E15" s="57">
+      <c r="E17" s="230">
         <v>6.6</v>
       </c>
-      <c r="F15" s="58">
+      <c r="F17" s="231">
         <v>132000.04999999999</v>
       </c>
-      <c r="G15" s="59">
-        <f t="shared" ref="G15:G19" si="8">F15</f>
+      <c r="G17" s="232">
+        <f t="shared" ref="G17:G21" si="8">F17</f>
         <v>132000.04999999999</v>
       </c>
-      <c r="H15" s="60">
+      <c r="H17" s="233">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="60">
+      <c r="I17" s="233">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="61">
+      <c r="J17" s="234">
         <f>EDESUR!I9</f>
         <v>0</v>
       </c>
-      <c r="K15" s="119">
+      <c r="K17" s="235">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L15" s="119">
+      <c r="L17" s="235">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M15" s="62">
+      <c r="M17" s="236">
         <f t="shared" si="4"/>
         <v>132000.04999999999</v>
       </c>
-      <c r="N15" s="63">
+      <c r="N17" s="237">
         <f t="shared" si="5"/>
         <v>139920.04999999999</v>
       </c>
-      <c r="O15" s="64">
+      <c r="O17" s="238">
         <f t="shared" si="6"/>
         <v>135960.04999999999</v>
       </c>
-      <c r="P15" s="32">
+      <c r="P17" s="31">
         <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="48">
+      <c r="Q17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="46">
         <v>6</v>
       </c>
-      <c r="B16" s="48" t="s">
+      <c r="B18" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C18" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="48" t="s">
+      <c r="D18" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="E16" s="57">
+      <c r="E18" s="55">
         <v>5.4</v>
       </c>
-      <c r="F16" s="58">
+      <c r="F18" s="56">
         <v>108000.06</v>
       </c>
-      <c r="G16" s="59">
+      <c r="G18" s="188">
         <f t="shared" si="8"/>
         <v>108000.06</v>
       </c>
-      <c r="H16" s="60">
+      <c r="H18" s="58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I16" s="60">
+      <c r="I18" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J16" s="61">
+      <c r="J18" s="59">
         <f>EDESUR!I10</f>
         <v>0</v>
       </c>
-      <c r="K16" s="119">
+      <c r="K18" s="117">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L16" s="119">
+      <c r="L18" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M16" s="62">
+      <c r="M18" s="60">
         <f t="shared" si="4"/>
         <v>108000.06</v>
       </c>
-      <c r="N16" s="63">
+      <c r="N18" s="61">
         <f t="shared" si="5"/>
         <v>114480.06</v>
       </c>
-      <c r="O16" s="64">
+      <c r="O18" s="62">
         <f t="shared" si="6"/>
         <v>111240.06</v>
       </c>
-      <c r="P16" s="32">
+      <c r="P18" s="31">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="48">
+    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="190">
         <v>7</v>
       </c>
-      <c r="B17" s="48" t="s">
+      <c r="B19" s="190" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="48" t="s">
+      <c r="C19" s="190" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="48" t="s">
+      <c r="D19" s="190" t="s">
         <v>97</v>
       </c>
-      <c r="E17" s="57">
+      <c r="E19" s="192">
         <v>5.4</v>
       </c>
-      <c r="F17" s="58">
+      <c r="F19" s="193">
         <v>108000.07</v>
       </c>
-      <c r="G17" s="59">
+      <c r="G19" s="194">
         <f t="shared" si="8"/>
         <v>108000.07</v>
       </c>
-      <c r="H17" s="60">
+      <c r="H19" s="195">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="60">
+      <c r="I19" s="195">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="61">
+      <c r="J19" s="196">
         <f>EDESUR!I11</f>
         <v>0</v>
       </c>
-      <c r="K17" s="119">
+      <c r="K19" s="197">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L17" s="119">
+      <c r="L19" s="197">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M17" s="62">
+      <c r="M19" s="198">
         <f t="shared" si="4"/>
         <v>108000.07</v>
       </c>
-      <c r="N17" s="63">
+      <c r="N19" s="199">
         <f t="shared" si="5"/>
         <v>114480.07</v>
       </c>
-      <c r="O17" s="64">
+      <c r="O19" s="200">
         <f t="shared" si="6"/>
         <v>111240.07</v>
       </c>
-      <c r="P17" s="32">
+      <c r="P19" s="31">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="48">
+    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="190">
         <v>8</v>
       </c>
-      <c r="B18" s="48" t="s">
+      <c r="B20" s="190" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="48" t="s">
+      <c r="C20" s="190" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="49" t="s">
+      <c r="D20" s="191" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="57">
+      <c r="E20" s="192">
         <v>6.6</v>
       </c>
-      <c r="F18" s="58">
+      <c r="F20" s="193">
         <v>132000.07999999999</v>
       </c>
-      <c r="G18" s="59">
+      <c r="G20" s="194">
         <f t="shared" si="8"/>
         <v>132000.07999999999</v>
       </c>
-      <c r="H18" s="60">
+      <c r="H20" s="195">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I18" s="60">
+      <c r="I20" s="195">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J18" s="61">
+      <c r="J20" s="196">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="K18" s="119">
+      <c r="K20" s="197">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L18" s="119">
+      <c r="L20" s="197">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M18" s="62">
+      <c r="M20" s="198">
         <f t="shared" si="4"/>
         <v>132000.07999999999</v>
       </c>
-      <c r="N18" s="63">
+      <c r="N20" s="199">
         <f t="shared" si="5"/>
         <v>139920.07999999999</v>
       </c>
-      <c r="O18" s="64">
+      <c r="O20" s="200">
         <f t="shared" si="6"/>
         <v>135960.07999999999</v>
       </c>
-      <c r="P18" s="32">
+      <c r="P20" s="31">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="48">
+    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="46">
         <v>9</v>
       </c>
-      <c r="B19" s="48" t="s">
+      <c r="B21" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C21" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="49" t="s">
+      <c r="D21" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="E19" s="57">
+      <c r="E21" s="55">
         <v>6.6</v>
       </c>
-      <c r="F19" s="58">
+      <c r="F21" s="56">
         <v>132000.09</v>
       </c>
-      <c r="G19" s="59">
+      <c r="G21" s="188">
         <f t="shared" si="8"/>
         <v>132000.09</v>
       </c>
-      <c r="H19" s="60">
+      <c r="H21" s="58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="60">
+      <c r="I21" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="61">
+      <c r="J21" s="59">
         <f>EDESUR!I13</f>
         <v>0</v>
       </c>
-      <c r="K19" s="119">
+      <c r="K21" s="117">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L19" s="119">
+      <c r="L21" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M19" s="62">
+      <c r="M21" s="60">
         <f t="shared" si="4"/>
         <v>132000.09</v>
       </c>
-      <c r="N19" s="63">
+      <c r="N21" s="61">
         <f t="shared" si="5"/>
         <v>139920.09</v>
       </c>
-      <c r="O19" s="64">
+      <c r="O21" s="62">
         <f t="shared" si="6"/>
         <v>135960.09</v>
       </c>
-      <c r="P19" s="32">
+      <c r="P21" s="31">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="48">
+    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="46">
         <v>10</v>
       </c>
-      <c r="B20" s="48" t="s">
+      <c r="B22" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="48" t="s">
+      <c r="C22" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="49" t="s">
+      <c r="D22" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="57">
+      <c r="E22" s="55">
         <v>5.4</v>
       </c>
-      <c r="F20" s="58">
-        <v>104680.1</v>
-      </c>
-      <c r="G20" s="59">
-        <f>F20+40000</f>
-        <v>144680.1</v>
-      </c>
-      <c r="H20" s="60">
+      <c r="F22" s="56">
+        <v>68000.100000000006</v>
+      </c>
+      <c r="G22" s="188">
+        <f>F22</f>
+        <v>68000.100000000006</v>
+      </c>
+      <c r="H22" s="58">
         <f t="shared" si="0"/>
-        <v>-40000</v>
-      </c>
-      <c r="I20" s="60">
+        <v>0</v>
+      </c>
+      <c r="I22" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="61">
+      <c r="J22" s="59">
         <f>EDESUR!I14</f>
         <v>0</v>
       </c>
-      <c r="K20" s="119">
+      <c r="K22" s="117">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L20" s="119">
+      <c r="L22" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M20" s="62">
+      <c r="M22" s="60">
         <f t="shared" si="4"/>
-        <v>68000.100000000006</v>
-      </c>
-      <c r="N20" s="63">
+        <v>108000.1</v>
+      </c>
+      <c r="N22" s="61">
         <f t="shared" si="5"/>
-        <v>72080.100000000006</v>
-      </c>
-      <c r="O20" s="64">
+        <v>114480.1</v>
+      </c>
+      <c r="O22" s="62">
         <f t="shared" si="6"/>
-        <v>70040.100000000006</v>
-      </c>
-      <c r="P20" s="32">
+        <v>111240.1</v>
+      </c>
+      <c r="P22" s="31">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="48">
+    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="46">
         <v>11</v>
       </c>
-      <c r="B21" s="48" t="s">
+      <c r="B23" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="48" t="s">
+      <c r="C23" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="49"/>
-      <c r="E21" s="57">
+      <c r="D23" s="47"/>
+      <c r="E23" s="55">
         <v>5.4</v>
       </c>
-      <c r="F21" s="58">
+      <c r="F23" s="56">
         <v>108000.11</v>
       </c>
-      <c r="G21" s="59">
-        <f>114000.11-G32</f>
+      <c r="G23" s="188">
+        <f>114000.11-G34</f>
         <v>108000.11</v>
       </c>
-      <c r="H21" s="60">
+      <c r="H23" s="58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I21" s="60">
+      <c r="I23" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="61">
+      <c r="J23" s="59">
         <f>EDESUR!I15</f>
         <v>0</v>
       </c>
-      <c r="K21" s="119">
+      <c r="K23" s="117">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L21" s="119">
+      <c r="L23" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M21" s="62">
+      <c r="M23" s="60">
         <f t="shared" si="4"/>
         <v>108000.11</v>
       </c>
-      <c r="N21" s="63">
+      <c r="N23" s="61">
         <f t="shared" si="5"/>
         <v>114480.11</v>
       </c>
-      <c r="O21" s="64">
+      <c r="O23" s="62">
         <f t="shared" si="6"/>
         <v>111240.11</v>
       </c>
-      <c r="P21" s="32">
+      <c r="P23" s="31">
         <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="Q23" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="48">
+    <row r="24" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="46">
         <v>12</v>
       </c>
-      <c r="B22" s="48" t="s">
+      <c r="B24" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="48" t="s">
+      <c r="C24" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="49" t="s">
+      <c r="D24" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="57">
+      <c r="E24" s="55">
         <v>6.6</v>
       </c>
-      <c r="F22" s="58">
+      <c r="F24" s="56">
         <v>132000.12</v>
       </c>
-      <c r="G22" s="59">
-        <f>F22</f>
+      <c r="G24" s="188">
+        <f>F24</f>
         <v>132000.12</v>
       </c>
-      <c r="H22" s="60">
+      <c r="H24" s="58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I22" s="60">
+      <c r="I24" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J22" s="61">
+      <c r="J24" s="59">
         <f>EDESUR!I16</f>
         <v>0</v>
       </c>
-      <c r="K22" s="119">
+      <c r="K24" s="117">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L22" s="119">
+      <c r="L24" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M22" s="62">
+      <c r="M24" s="60">
         <f t="shared" si="4"/>
         <v>132000.12</v>
       </c>
-      <c r="N22" s="63">
+      <c r="N24" s="61">
         <f t="shared" si="5"/>
         <v>139920.12</v>
       </c>
-      <c r="O22" s="64">
+      <c r="O24" s="62">
         <f t="shared" si="6"/>
         <v>135960.12</v>
       </c>
-      <c r="P22" s="32">
+      <c r="P24" s="31">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="48">
+    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="46">
         <v>13</v>
       </c>
-      <c r="B23" s="48" t="s">
+      <c r="B25" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="48" t="s">
+      <c r="C25" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="49" t="s">
+      <c r="D25" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="E23" s="57">
+      <c r="E25" s="55">
         <v>6.6</v>
       </c>
-      <c r="F23" s="58">
-        <v>132000.13</v>
-      </c>
-      <c r="G23" s="59">
-        <f>135960.13</f>
-        <v>135960.13</v>
-      </c>
-      <c r="H23" s="60">
+      <c r="F25" s="56">
+        <v>128040.13</v>
+      </c>
+      <c r="G25" s="188">
+        <v>131881.13</v>
+      </c>
+      <c r="H25" s="58">
         <f t="shared" si="0"/>
-        <v>-3960</v>
-      </c>
-      <c r="I23" s="60">
+        <v>-3841</v>
+      </c>
+      <c r="I25" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J23" s="61">
+      <c r="J25" s="59">
         <f>EDESUR!I17</f>
         <v>0</v>
       </c>
-      <c r="K23" s="119">
+      <c r="K25" s="117">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L23" s="119">
+      <c r="L25" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M23" s="62">
+      <c r="M25" s="60">
         <f t="shared" si="4"/>
-        <v>128040.13</v>
-      </c>
-      <c r="N23" s="63">
+        <v>128159.13</v>
+      </c>
+      <c r="N25" s="61">
         <f t="shared" si="5"/>
-        <v>135723.13</v>
-      </c>
-      <c r="O23" s="64">
+        <v>135849.13</v>
+      </c>
+      <c r="O25" s="62">
         <f t="shared" si="6"/>
-        <v>131881.13</v>
-      </c>
-      <c r="P23" s="32">
+        <v>132004.13</v>
+      </c>
+      <c r="P25" s="31">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="48">
+    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="46">
         <v>14</v>
       </c>
-      <c r="B24" s="48" t="s">
+      <c r="B26" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="48" t="s">
+      <c r="C26" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="49"/>
-      <c r="E24" s="57">
+      <c r="D26" s="47"/>
+      <c r="E26" s="55">
         <v>5.4</v>
       </c>
-      <c r="F24" s="58">
+      <c r="F26" s="56">
         <v>108000.14</v>
       </c>
-      <c r="G24" s="59">
-        <f>F24</f>
-        <v>108000.14</v>
-      </c>
-      <c r="H24" s="60">
+      <c r="G26" s="188">
+        <f>F26+RESUMEN!D39</f>
+        <v>132884.35</v>
+      </c>
+      <c r="H26" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="60">
+        <v>-24884.210000000006</v>
+      </c>
+      <c r="I26" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J24" s="61">
+      <c r="J26" s="59">
         <f>EDESUR!I18</f>
         <v>0</v>
       </c>
-      <c r="K24" s="119">
+      <c r="K26" s="117">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L24" s="119">
+      <c r="L26" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M24" s="62">
+      <c r="M26" s="60">
         <f t="shared" si="4"/>
-        <v>108000.14</v>
-      </c>
-      <c r="N24" s="63">
+        <v>83116.14</v>
+      </c>
+      <c r="N26" s="61">
         <f t="shared" si="5"/>
-        <v>114480.14</v>
-      </c>
-      <c r="O24" s="64">
+        <v>88103.14</v>
+      </c>
+      <c r="O26" s="62">
         <f t="shared" si="6"/>
-        <v>111240.14</v>
-      </c>
-      <c r="P24" s="32">
+        <v>85609.14</v>
+      </c>
+      <c r="P26" s="31">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="48">
+    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="46">
         <v>15</v>
       </c>
-      <c r="B25" s="48" t="s">
+      <c r="B27" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="48" t="s">
+      <c r="C27" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="49"/>
-      <c r="E25" s="57">
+      <c r="D27" s="47"/>
+      <c r="E27" s="55">
         <v>5.4</v>
       </c>
-      <c r="F25" s="58">
+      <c r="F27" s="56">
         <v>108000.15</v>
       </c>
-      <c r="G25" s="59">
-        <f>F25</f>
+      <c r="G27" s="188">
+        <f>F27</f>
         <v>108000.15</v>
       </c>
-      <c r="H25" s="60">
+      <c r="H27" s="58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I25" s="60">
+      <c r="I27" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J25" s="61">
+      <c r="J27" s="59">
         <f>EDESUR!I19</f>
         <v>0</v>
       </c>
-      <c r="K25" s="119">
+      <c r="K27" s="117">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L25" s="119">
+      <c r="L27" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M25" s="62">
+      <c r="M27" s="60">
         <f t="shared" si="4"/>
         <v>108000.15</v>
       </c>
-      <c r="N25" s="63">
+      <c r="N27" s="61">
         <f t="shared" si="5"/>
         <v>114480.15</v>
       </c>
-      <c r="O25" s="64">
+      <c r="O27" s="62">
         <f t="shared" si="6"/>
         <v>111240.15</v>
       </c>
-      <c r="P25" s="32">
+      <c r="P27" s="31">
         <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="48">
+    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="46">
         <v>16</v>
       </c>
-      <c r="B26" s="48" t="s">
+      <c r="B28" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="48" t="s">
+      <c r="C28" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="48" t="s">
+      <c r="D28" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="E26" s="57">
+      <c r="E28" s="55">
         <v>0.7</v>
       </c>
-      <c r="F26" s="58">
+      <c r="F28" s="56">
         <v>14000.16</v>
       </c>
-      <c r="G26" s="59">
-        <f>F26</f>
+      <c r="G28" s="188">
+        <f>F28</f>
         <v>14000.16</v>
       </c>
-      <c r="H26" s="60">
+      <c r="H28" s="58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I26" s="60">
+      <c r="I28" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J26" s="61">
+      <c r="J28" s="59">
         <f>EDESUR!I22</f>
         <v>0</v>
       </c>
-      <c r="K26" s="119">
+      <c r="K28" s="117">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="L26" s="119">
+      <c r="L28" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M26" s="62">
+      <c r="M28" s="60">
         <f t="shared" si="4"/>
         <v>14000.16</v>
       </c>
-      <c r="N26" s="63">
+      <c r="N28" s="61">
         <f t="shared" si="5"/>
         <v>14840.16</v>
       </c>
-      <c r="O26" s="64">
+      <c r="O28" s="62">
         <f t="shared" si="6"/>
         <v>14420.16</v>
       </c>
-      <c r="P26" s="32">
+      <c r="P28" s="31">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="48">
+    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="46">
         <v>17</v>
       </c>
-      <c r="B27" s="48" t="s">
+      <c r="B29" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="48" t="s">
+      <c r="C29" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="49"/>
-      <c r="E27" s="57">
+      <c r="D29" s="47"/>
+      <c r="E29" s="55">
         <v>0.6</v>
       </c>
-      <c r="F27" s="59">
+      <c r="F29" s="57">
         <v>12000.17</v>
       </c>
-      <c r="G27" s="59">
-        <f t="shared" ref="G27:G29" si="9">F27</f>
+      <c r="G29" s="188">
+        <f t="shared" ref="G29:G31" si="9">F29</f>
         <v>12000.17</v>
       </c>
-      <c r="H27" s="60">
+      <c r="H29" s="58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I27" s="60">
+      <c r="I29" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J27" s="61">
+      <c r="J29" s="59">
         <f>EDESUR!I21</f>
         <v>0</v>
       </c>
-      <c r="K27" s="119">
+      <c r="K29" s="117">
         <f t="shared" si="2"/>
         <v>12000</v>
       </c>
-      <c r="L27" s="119">
+      <c r="L29" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M27" s="62">
+      <c r="M29" s="60">
         <f t="shared" si="4"/>
         <v>12000.17</v>
       </c>
-      <c r="N27" s="63">
+      <c r="N29" s="61">
         <f t="shared" si="5"/>
         <v>12720.17</v>
       </c>
-      <c r="O27" s="64">
+      <c r="O29" s="62">
         <f t="shared" si="6"/>
         <v>12360.17</v>
       </c>
-      <c r="P27" s="32">
+      <c r="P29" s="31">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="48">
+    <row r="30" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="46">
         <v>18</v>
       </c>
-      <c r="B28" s="48" t="s">
+      <c r="B30" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="48" t="s">
+      <c r="C30" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="96"/>
-      <c r="E28" s="57">
+      <c r="D30" s="94"/>
+      <c r="E30" s="55">
         <v>0.6</v>
       </c>
-      <c r="F28" s="58">
+      <c r="F30" s="56">
         <v>12000.18</v>
       </c>
-      <c r="G28" s="59">
+      <c r="G30" s="188">
         <f t="shared" si="9"/>
         <v>12000.18</v>
       </c>
-      <c r="H28" s="60">
+      <c r="H30" s="58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I28" s="60">
+      <c r="I30" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J28" s="61">
+      <c r="J30" s="59">
         <f>EDESUR!I22</f>
         <v>0</v>
       </c>
-      <c r="K28" s="119">
+      <c r="K30" s="117">
         <f t="shared" si="2"/>
         <v>12000</v>
       </c>
-      <c r="L28" s="119">
+      <c r="L30" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M28" s="62">
+      <c r="M30" s="60">
         <f t="shared" si="4"/>
         <v>12000.18</v>
       </c>
-      <c r="N28" s="63">
+      <c r="N30" s="61">
         <f t="shared" si="5"/>
         <v>12720.18</v>
       </c>
-      <c r="O28" s="64">
+      <c r="O30" s="62">
         <f t="shared" si="6"/>
         <v>12360.18</v>
       </c>
-      <c r="P28" s="32">
+      <c r="P30" s="31">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="48">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A31" s="46">
         <v>19</v>
       </c>
-      <c r="B29" s="48" t="s">
+      <c r="B31" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="C29" s="48" t="s">
+      <c r="C31" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="49"/>
-      <c r="E29" s="57">
+      <c r="D31" s="47"/>
+      <c r="E31" s="55">
         <v>0.6</v>
       </c>
-      <c r="F29" s="58">
+      <c r="F31" s="56">
         <v>12000.19</v>
       </c>
-      <c r="G29" s="59">
+      <c r="G31" s="188">
         <f t="shared" si="9"/>
         <v>12000.19</v>
       </c>
-      <c r="H29" s="60">
+      <c r="H31" s="58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I29" s="60">
+      <c r="I31" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J29" s="61">
+      <c r="J31" s="59">
         <f>EDESUR!I23</f>
         <v>0</v>
       </c>
-      <c r="K29" s="119">
+      <c r="K31" s="117">
         <f t="shared" si="2"/>
         <v>12000</v>
       </c>
-      <c r="L29" s="119">
+      <c r="L31" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M29" s="62">
+      <c r="M31" s="60">
         <f t="shared" si="4"/>
         <v>12000.19</v>
       </c>
-      <c r="N29" s="63"/>
-      <c r="O29" s="64">
+      <c r="N31" s="61"/>
+      <c r="O31" s="62">
         <f t="shared" si="6"/>
         <v>12360.19</v>
       </c>
-      <c r="P29" s="32">
-        <f>P28+0.01</f>
+      <c r="P31" s="31">
+        <f>P30+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="65">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A32" s="63">
         <v>20</v>
       </c>
-      <c r="B30" s="65" t="s">
+      <c r="B32" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="48" t="s">
+      <c r="C32" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="D30" s="49" t="s">
+      <c r="D32" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="E30" s="57">
+      <c r="E32" s="55">
         <v>0.6</v>
       </c>
-      <c r="F30" s="67">
-        <v>12000</v>
-      </c>
-      <c r="G30" s="59"/>
-      <c r="H30" s="60">
+      <c r="F32" s="65">
+        <v>24360</v>
+      </c>
+      <c r="G32" s="188">
+        <f>F32</f>
+        <v>24360</v>
+      </c>
+      <c r="H32" s="58">
         <f t="shared" si="0"/>
-        <v>12000</v>
-      </c>
-      <c r="I30" s="60">
+        <v>0</v>
+      </c>
+      <c r="I32" s="58">
         <f t="shared" si="1"/>
-        <v>360</v>
-      </c>
-      <c r="J30" s="61">
+        <v>0</v>
+      </c>
+      <c r="J32" s="59">
         <f>EDESUR!I24</f>
         <v>0</v>
       </c>
-      <c r="K30" s="119">
+      <c r="K32" s="117">
         <f t="shared" si="2"/>
         <v>12000</v>
       </c>
-      <c r="L30" s="119">
+      <c r="L32" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M30" s="62">
+      <c r="M32" s="60">
         <f t="shared" si="4"/>
-        <v>24360</v>
-      </c>
-      <c r="N30" s="63"/>
-      <c r="O30" s="64">
+        <v>12000.2</v>
+      </c>
+      <c r="N32" s="61"/>
+      <c r="O32" s="62">
         <f t="shared" si="6"/>
-        <v>25091</v>
-      </c>
-      <c r="P30" s="32"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="65">
+        <v>12360.2</v>
+      </c>
+      <c r="P32" s="31">
+        <f t="shared" ref="P32:P35" si="10">P31+0.01</f>
+        <v>0.20000000000000004</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" s="63">
         <v>21</v>
       </c>
-      <c r="B31" s="65" t="s">
+      <c r="B33" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="50" t="s">
+      <c r="C33" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="49" t="s">
+      <c r="D33" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="57">
+      <c r="E33" s="55">
         <v>0.3</v>
       </c>
-      <c r="F31" s="67">
+      <c r="F33" s="65">
         <v>6000</v>
       </c>
-      <c r="G31" s="163">
-        <f>F31</f>
+      <c r="G33" s="189">
+        <f>F33</f>
         <v>6000</v>
       </c>
-      <c r="H31" s="60">
+      <c r="H33" s="58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="60">
+      <c r="I33" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J31" s="61">
+      <c r="J33" s="59">
         <f>EDESUR!I25</f>
         <v>0</v>
       </c>
-      <c r="K31" s="119">
+      <c r="K33" s="117">
         <f t="shared" si="2"/>
         <v>6000</v>
       </c>
-      <c r="L31" s="119">
+      <c r="L33" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M31" s="62">
+      <c r="M33" s="60">
         <f t="shared" si="4"/>
+        <v>6000.21</v>
+      </c>
+      <c r="N33" s="61"/>
+      <c r="O33" s="62">
+        <f t="shared" si="6"/>
+        <v>6180.21</v>
+      </c>
+      <c r="P33" s="31">
+        <f t="shared" si="10"/>
+        <v>0.21000000000000005</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" s="64">
+        <v>22</v>
+      </c>
+      <c r="B34" s="64" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" s="47"/>
+      <c r="E34" s="55">
+        <v>0.3</v>
+      </c>
+      <c r="F34" s="65">
         <v>6000</v>
       </c>
-      <c r="N31" s="63"/>
-      <c r="O31" s="64">
-        <f t="shared" si="6"/>
-        <v>6180</v>
-      </c>
-      <c r="P31" s="32"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="66">
-        <v>22</v>
-      </c>
-      <c r="B32" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" s="49"/>
-      <c r="E32" s="57">
-        <v>0.3</v>
-      </c>
-      <c r="F32" s="67">
+      <c r="G34" s="189">
+        <f>F34</f>
         <v>6000</v>
       </c>
-      <c r="G32" s="163">
-        <f>F32</f>
-        <v>6000</v>
-      </c>
-      <c r="H32" s="60">
+      <c r="H34" s="58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I32" s="60">
+      <c r="I34" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J32" s="61">
+      <c r="J34" s="59">
         <f>EDESUR!I26</f>
         <v>0</v>
       </c>
-      <c r="K32" s="119">
+      <c r="K34" s="117">
         <f t="shared" si="2"/>
         <v>6000</v>
       </c>
-      <c r="L32" s="119">
+      <c r="L34" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M32" s="62">
+      <c r="M34" s="60">
         <f t="shared" si="4"/>
+        <v>6000.22</v>
+      </c>
+      <c r="N34" s="61"/>
+      <c r="O34" s="62">
+        <f t="shared" si="6"/>
+        <v>6180.22</v>
+      </c>
+      <c r="P34" s="31">
+        <f t="shared" si="10"/>
+        <v>0.22000000000000006</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="46">
+        <v>23</v>
+      </c>
+      <c r="B35" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" s="55">
+        <v>0.3</v>
+      </c>
+      <c r="F35" s="65">
         <v>6000</v>
       </c>
-      <c r="N32" s="63"/>
-      <c r="O32" s="64">
-        <f t="shared" si="6"/>
-        <v>6180</v>
-      </c>
-      <c r="P32" s="32"/>
-    </row>
-    <row r="33" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="48">
-        <v>23</v>
-      </c>
-      <c r="B33" s="68" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="68" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="E33" s="57">
-        <v>0.3</v>
-      </c>
-      <c r="F33" s="67">
+      <c r="G35" s="189">
+        <f>F35</f>
         <v>6000</v>
       </c>
-      <c r="G33" s="163">
-        <f>F33</f>
-        <v>6000</v>
-      </c>
-      <c r="H33" s="60">
+      <c r="H35" s="58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I33" s="60">
+      <c r="I35" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J33" s="61">
+      <c r="J35" s="59">
         <f>EDESUR!I27</f>
         <v>0</v>
       </c>
-      <c r="K33" s="119">
+      <c r="K35" s="117">
         <f t="shared" si="2"/>
         <v>6000</v>
       </c>
-      <c r="L33" s="119">
+      <c r="L35" s="117">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M33" s="62">
+      <c r="M35" s="60">
         <f t="shared" si="4"/>
-        <v>6000</v>
-      </c>
-      <c r="N33" s="69"/>
-      <c r="O33" s="64">
+        <v>6000.23</v>
+      </c>
+      <c r="N35" s="67"/>
+      <c r="O35" s="62">
         <f t="shared" si="6"/>
-        <v>6180</v>
-      </c>
-      <c r="P33" s="32"/>
-    </row>
-    <row r="34" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="70"/>
-      <c r="B34" s="70"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="131">
-        <f>SUM(E11:E33)</f>
+        <v>6180.23</v>
+      </c>
+      <c r="P35" s="31">
+        <f t="shared" si="10"/>
+        <v>0.23000000000000007</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="68"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="129">
+        <f>SUM(E13:E35)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="F34" s="41">
-        <f>SUM(F11:F33)</f>
-        <v>1996621.9000000001</v>
-      </c>
-      <c r="G34" s="46">
-        <f>SUM(G11:G33)</f>
-        <v>2038799.4999999998</v>
-      </c>
-      <c r="H34" s="46">
-        <f>SUM(H11:H33)</f>
-        <v>-42177.599999999977</v>
-      </c>
-      <c r="I34" s="46">
-        <f t="shared" ref="I34:N34" si="10">SUM(I11:I33)</f>
-        <v>360</v>
-      </c>
-      <c r="J34" s="46">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="99">
-        <f t="shared" si="10"/>
+      <c r="F36" s="40">
+        <f>SUM(F13:F35)</f>
+        <v>1958183.9000000001</v>
+      </c>
+      <c r="G36" s="44">
+        <f>SUM(G13:G35)</f>
+        <v>1986908.7200000002</v>
+      </c>
+      <c r="H36" s="44">
+        <f>SUM(H13:H35)</f>
+        <v>-28724.820000000007</v>
+      </c>
+      <c r="I36" s="44">
+        <f t="shared" ref="I36:N36" si="11">SUM(I13:I35)</f>
+        <v>1.1699999999982537E-2</v>
+      </c>
+      <c r="J36" s="44">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="97">
+        <f t="shared" si="11"/>
         <v>2000000</v>
       </c>
-      <c r="L34" s="46">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="M34" s="72">
-        <f>SUM(M11:M33)</f>
-        <v>1958183.9000000001</v>
-      </c>
-      <c r="N34" s="72">
-        <f t="shared" si="10"/>
-        <v>2018053.7100000002</v>
-      </c>
-      <c r="O34" s="72">
-        <f>SUM(O11:O33)</f>
-        <v>2016928.9000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="38"/>
-      <c r="D35" s="38"/>
-    </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="172" t="str">
+      <c r="L36" s="44">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M36" s="70">
+        <f>SUM(M13:M35)</f>
+        <v>1971277.76</v>
+      </c>
+      <c r="N36" s="70">
+        <f t="shared" si="11"/>
+        <v>2045033.7100000002</v>
+      </c>
+      <c r="O36" s="70">
+        <f>SUM(O13:O35)</f>
+        <v>2030415.76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+    </row>
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="157" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D37" s="172"/>
-      <c r="E37" s="172"/>
-      <c r="F37" s="172"/>
-      <c r="G37" s="172"/>
-      <c r="H37" s="172"/>
-      <c r="I37" s="172"/>
-      <c r="J37" s="172"/>
-      <c r="K37" s="172"/>
-      <c r="L37" s="172"/>
-      <c r="M37" s="172"/>
-    </row>
-    <row r="38" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="172"/>
-      <c r="D38" s="172"/>
-      <c r="E38" s="172"/>
-      <c r="F38" s="172"/>
-      <c r="G38" s="172"/>
-      <c r="H38" s="172"/>
-      <c r="I38" s="172"/>
-      <c r="J38" s="172"/>
-      <c r="K38" s="172"/>
-      <c r="L38" s="172"/>
-      <c r="M38" s="172"/>
-    </row>
-    <row r="39" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="172"/>
-      <c r="D39" s="172"/>
-      <c r="E39" s="172"/>
-      <c r="F39" s="172"/>
-      <c r="G39" s="172"/>
-      <c r="H39" s="172"/>
-      <c r="I39" s="172"/>
-      <c r="J39" s="172"/>
-      <c r="K39" s="172"/>
-      <c r="L39" s="172"/>
-      <c r="M39" s="172"/>
+      <c r="D39" s="157"/>
+      <c r="E39" s="157"/>
+      <c r="F39" s="157"/>
+      <c r="G39" s="157"/>
+      <c r="H39" s="157"/>
+      <c r="I39" s="157"/>
+      <c r="J39" s="157"/>
+      <c r="K39" s="157"/>
+      <c r="L39" s="157"/>
+      <c r="M39" s="157"/>
     </row>
     <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="172"/>
-      <c r="D40" s="172"/>
-      <c r="E40" s="172"/>
-      <c r="F40" s="172"/>
-      <c r="G40" s="172"/>
-      <c r="H40" s="172"/>
-      <c r="I40" s="172"/>
-      <c r="J40" s="172"/>
-      <c r="K40" s="172"/>
-      <c r="L40" s="172"/>
-      <c r="M40" s="172"/>
+      <c r="C40" s="157"/>
+      <c r="D40" s="157"/>
+      <c r="E40" s="157"/>
+      <c r="F40" s="157"/>
+      <c r="G40" s="157"/>
+      <c r="H40" s="157"/>
+      <c r="I40" s="157"/>
+      <c r="J40" s="157"/>
+      <c r="K40" s="157"/>
+      <c r="L40" s="157"/>
+      <c r="M40" s="157"/>
     </row>
     <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="172"/>
-      <c r="D41" s="172"/>
-      <c r="E41" s="172"/>
-      <c r="F41" s="172"/>
-      <c r="G41" s="172"/>
-      <c r="H41" s="172"/>
-      <c r="I41" s="172"/>
-      <c r="J41" s="172"/>
-      <c r="K41" s="172"/>
-      <c r="L41" s="172"/>
-      <c r="M41" s="172"/>
-    </row>
-    <row r="42" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="172"/>
-      <c r="D42" s="172"/>
-      <c r="E42" s="172"/>
-      <c r="F42" s="172"/>
-      <c r="G42" s="172"/>
-      <c r="H42" s="172"/>
-      <c r="I42" s="172"/>
-      <c r="J42" s="172"/>
-      <c r="K42" s="172"/>
-      <c r="L42" s="172"/>
-      <c r="M42" s="172"/>
+      <c r="C41" s="157"/>
+      <c r="D41" s="157"/>
+      <c r="E41" s="157"/>
+      <c r="F41" s="157"/>
+      <c r="G41" s="157"/>
+      <c r="H41" s="157"/>
+      <c r="I41" s="157"/>
+      <c r="J41" s="157"/>
+      <c r="K41" s="157"/>
+      <c r="L41" s="157"/>
+      <c r="M41" s="157"/>
+    </row>
+    <row r="42" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="157"/>
+      <c r="D42" s="157"/>
+      <c r="E42" s="157"/>
+      <c r="F42" s="157"/>
+      <c r="G42" s="157"/>
+      <c r="H42" s="157"/>
+      <c r="I42" s="157"/>
+      <c r="J42" s="157"/>
+      <c r="K42" s="157"/>
+      <c r="L42" s="157"/>
+      <c r="M42" s="157"/>
+    </row>
+    <row r="43" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C43" s="157"/>
+      <c r="D43" s="157"/>
+      <c r="E43" s="157"/>
+      <c r="F43" s="157"/>
+      <c r="G43" s="157"/>
+      <c r="H43" s="157"/>
+      <c r="I43" s="157"/>
+      <c r="J43" s="157"/>
+      <c r="K43" s="157"/>
+      <c r="L43" s="157"/>
+      <c r="M43" s="157"/>
+    </row>
+    <row r="44" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C44" s="157"/>
+      <c r="D44" s="157"/>
+      <c r="E44" s="157"/>
+      <c r="F44" s="157"/>
+      <c r="G44" s="157"/>
+      <c r="H44" s="157"/>
+      <c r="I44" s="157"/>
+      <c r="J44" s="157"/>
+      <c r="K44" s="157"/>
+      <c r="L44" s="157"/>
+      <c r="M44" s="157"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="C37:M42"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E9:E10"/>
+  <mergeCells count="18">
     <mergeCell ref="E1:M1"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
     <mergeCell ref="A4:O8"/>
-    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="A9:O9"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="C39:M44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4440,570 +4554,555 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="141" t="s">
+      <c r="B3" s="138" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="141" t="s">
+      <c r="C3" s="138" t="s">
         <v>86</v>
       </c>
-      <c r="E3" s="143" t="s">
+      <c r="E3" s="140" t="s">
         <v>92</v>
       </c>
-      <c r="G3" s="144" t="s">
+      <c r="G3" s="141" t="s">
         <v>93</v>
       </c>
-      <c r="I3" s="194" t="s">
+      <c r="I3" s="182" t="s">
         <v>94</v>
       </c>
-      <c r="J3" s="195"/>
+      <c r="J3" s="183"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="141"/>
-      <c r="C4" s="141"/>
-      <c r="E4" s="141"/>
-      <c r="G4" s="145"/>
-      <c r="I4" s="194"/>
-      <c r="J4" s="195"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="G4" s="142"/>
+      <c r="I4" s="182"/>
+      <c r="J4" s="183"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="141">
+      <c r="B5" s="138">
         <v>1</v>
       </c>
-      <c r="C5" s="141" t="s">
+      <c r="C5" s="138" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="146">
+      <c r="E5" s="143">
         <v>61353.383534261804</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="147">
+      <c r="G5" s="144">
         <v>61353.383534261804</v>
       </c>
-      <c r="I5" s="192">
+      <c r="I5" s="180">
         <f>E5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="193"/>
+      <c r="J5" s="181"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="141">
+      <c r="B6" s="138">
         <v>1</v>
       </c>
-      <c r="C6" s="141" t="s">
+      <c r="C6" s="138" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="146">
+      <c r="E6" s="143">
         <v>34428.700834302756</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="147">
+      <c r="G6" s="144">
         <v>34428.700834302756</v>
       </c>
-      <c r="I6" s="192">
+      <c r="I6" s="180">
         <f t="shared" ref="I6:I21" si="0">E6-G6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="193"/>
+      <c r="J6" s="181"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="141">
+      <c r="B7" s="138">
         <v>1</v>
       </c>
-      <c r="C7" s="141" t="s">
+      <c r="C7" s="138" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="146">
+      <c r="E7" s="143">
         <v>14356.010802482968</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="147">
+      <c r="G7" s="144">
         <v>14356.010802482968</v>
       </c>
-      <c r="I7" s="192">
+      <c r="I7" s="180">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J7" s="193"/>
+      <c r="J7" s="181"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="141">
+      <c r="B8" s="138">
         <v>2</v>
       </c>
-      <c r="C8" s="141" t="s">
+      <c r="C8" s="138" t="s">
         <v>87</v>
       </c>
-      <c r="E8" s="146">
+      <c r="E8" s="143">
         <v>12061.218355435631</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="147">
+      <c r="G8" s="144">
         <v>12061.218355435631</v>
       </c>
-      <c r="I8" s="192">
+      <c r="I8" s="180">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="193"/>
+      <c r="J8" s="181"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="142">
+      <c r="B9" s="139">
         <v>2</v>
       </c>
-      <c r="C9" s="142" t="s">
+      <c r="C9" s="139" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="146">
+      <c r="E9" s="143">
         <v>53068.035404197428</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="147">
+      <c r="G9" s="144">
         <v>53068.035404197428</v>
       </c>
-      <c r="I9" s="192">
+      <c r="I9" s="180">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="193"/>
+      <c r="J9" s="181"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="142">
+      <c r="B10" s="139">
         <v>2</v>
       </c>
-      <c r="C10" s="142" t="s">
+      <c r="C10" s="139" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="146">
+      <c r="E10" s="143">
         <v>9841.6389016527519</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="147">
+      <c r="G10" s="144">
         <v>9841.6389016527519</v>
       </c>
-      <c r="I10" s="192">
+      <c r="I10" s="180">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="193"/>
+      <c r="J10" s="181"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="142">
+      <c r="B11" s="139">
         <v>2</v>
       </c>
-      <c r="C11" s="142" t="s">
+      <c r="C11" s="139" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="146">
+      <c r="E11" s="143">
         <v>9327.3712310195588</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="147">
+      <c r="G11" s="144">
         <v>9327.3712310195588</v>
       </c>
-      <c r="I11" s="192">
+      <c r="I11" s="180">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="193"/>
+      <c r="J11" s="181"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="142">
+      <c r="B12" s="139">
         <v>3</v>
       </c>
-      <c r="C12" s="142" t="s">
+      <c r="C12" s="139" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="146">
+      <c r="E12" s="143">
         <v>9216.1440460861631</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="147">
+      <c r="G12" s="144">
         <v>9216.1440460861631</v>
       </c>
-      <c r="I12" s="192">
+      <c r="I12" s="180">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="193"/>
+      <c r="J12" s="181"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="141">
+      <c r="B13" s="138">
         <v>3</v>
       </c>
-      <c r="C13" s="141" t="s">
+      <c r="C13" s="138" t="s">
         <v>90</v>
       </c>
-      <c r="E13" s="146">
+      <c r="E13" s="143">
         <v>23200.609218392572</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="147">
+      <c r="G13" s="144">
         <v>23200.609218392572</v>
       </c>
-      <c r="I13" s="192">
+      <c r="I13" s="180">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="193"/>
+      <c r="J13" s="181"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="142">
+      <c r="B14" s="139">
         <v>3</v>
       </c>
-      <c r="C14" s="142" t="s">
+      <c r="C14" s="139" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="146">
+      <c r="E14" s="143">
         <v>7781.0089492021225</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="147">
+      <c r="G14" s="144">
         <v>7781.0089492021225</v>
       </c>
-      <c r="I14" s="192">
+      <c r="I14" s="180">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="193"/>
+      <c r="J14" s="181"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="142">
+      <c r="B15" s="139">
         <v>3</v>
       </c>
-      <c r="C15" s="142" t="s">
+      <c r="C15" s="139" t="s">
         <v>89</v>
       </c>
-      <c r="E15" s="146">
+      <c r="E15" s="143">
         <v>10351.832144880002</v>
       </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="147">
+      <c r="G15" s="144">
         <v>10351.832144880002</v>
       </c>
-      <c r="I15" s="192">
+      <c r="I15" s="180">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="193"/>
+      <c r="J15" s="181"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="141">
+      <c r="B16" s="138">
         <v>4</v>
       </c>
-      <c r="C16" s="141" t="s">
+      <c r="C16" s="138" t="s">
         <v>87</v>
       </c>
-      <c r="E16" s="146">
+      <c r="E16" s="143">
         <v>49509.655303807594</v>
       </c>
       <c r="F16" s="2"/>
-      <c r="G16" s="147">
+      <c r="G16" s="144">
         <v>49509.655303807594</v>
       </c>
-      <c r="I16" s="192">
+      <c r="I16" s="180">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="193"/>
+      <c r="J16" s="181"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="142">
+      <c r="B17" s="139">
         <v>4</v>
       </c>
-      <c r="C17" s="142" t="s">
+      <c r="C17" s="139" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="146">
+      <c r="E17" s="143">
         <v>16866.513739552778</v>
       </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="147">
+      <c r="G17" s="144">
         <v>16866.513739552778</v>
       </c>
-      <c r="I17" s="192">
+      <c r="I17" s="180">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="193"/>
+      <c r="J17" s="181"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="141">
+      <c r="B18" s="138">
         <v>4</v>
       </c>
-      <c r="C18" s="141" t="s">
+      <c r="C18" s="138" t="s">
         <v>88</v>
       </c>
-      <c r="E18" s="146">
+      <c r="E18" s="143">
         <v>24968.536052597399</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="147">
+      <c r="G18" s="144">
         <v>24968.536052597399</v>
       </c>
-      <c r="I18" s="192">
+      <c r="I18" s="180">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="193"/>
+      <c r="J18" s="181"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="142">
+      <c r="B19" s="139">
         <v>4</v>
       </c>
-      <c r="C19" s="142" t="s">
+      <c r="C19" s="139" t="s">
         <v>89</v>
       </c>
-      <c r="E19" s="146">
+      <c r="E19" s="143">
         <v>10779.178697518902</v>
       </c>
       <c r="F19" s="2"/>
-      <c r="G19" s="147">
+      <c r="G19" s="144">
         <v>10779.178697518902</v>
       </c>
-      <c r="I19" s="192">
+      <c r="I19" s="180">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="193"/>
+      <c r="J19" s="181"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="141"/>
-      <c r="C20" s="141"/>
-      <c r="E20" s="141"/>
-      <c r="G20" s="145"/>
-      <c r="I20" s="192"/>
-      <c r="J20" s="193"/>
+      <c r="B20" s="138"/>
+      <c r="C20" s="138"/>
+      <c r="E20" s="138"/>
+      <c r="G20" s="142"/>
+      <c r="I20" s="180"/>
+      <c r="J20" s="181"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="141"/>
-      <c r="C21" s="141"/>
-      <c r="E21" s="150">
+      <c r="B21" s="138"/>
+      <c r="C21" s="138"/>
+      <c r="E21" s="147">
         <f>SUM(E5:E20)</f>
         <v>347109.83721539041</v>
       </c>
-      <c r="G21" s="147">
+      <c r="G21" s="144">
         <f>SUM(G5:G20)</f>
         <v>347109.83721539041</v>
       </c>
-      <c r="I21" s="192">
+      <c r="I21" s="180">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="193"/>
+      <c r="J21" s="181"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="141" t="s">
+      <c r="B22" s="138" t="s">
         <v>91</v>
       </c>
-      <c r="C22" s="141">
+      <c r="C22" s="138">
         <v>1</v>
       </c>
-      <c r="E22" s="160">
+      <c r="E22" s="149">
         <v>723.43331893167124</v>
       </c>
-      <c r="G22" s="161">
+      <c r="G22" s="150">
         <v>723.43331893167124</v>
       </c>
-      <c r="I22" s="192">
+      <c r="I22" s="180">
         <f t="shared" ref="I22" si="1">E22-G22</f>
         <v>0</v>
       </c>
-      <c r="J22" s="193"/>
+      <c r="J22" s="181"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="141" t="s">
+      <c r="B23" s="138" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="141">
+      <c r="C23" s="138">
         <v>2</v>
       </c>
-      <c r="E23" s="160">
+      <c r="E23" s="149">
         <v>620.08570194143249</v>
       </c>
-      <c r="G23" s="161">
+      <c r="G23" s="150">
         <v>620.08570194143249</v>
       </c>
-      <c r="I23" s="192">
+      <c r="I23" s="180">
         <f t="shared" ref="I23:I31" si="2">E23-G23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="193"/>
+      <c r="J23" s="181"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="141" t="s">
+      <c r="B24" s="138" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="141">
+      <c r="C24" s="138">
         <v>3</v>
       </c>
-      <c r="E24" s="160">
+      <c r="E24" s="149">
         <v>620.08570194143249</v>
       </c>
-      <c r="G24" s="161">
+      <c r="G24" s="150">
         <v>620.08570194143249</v>
       </c>
-      <c r="I24" s="192">
+      <c r="I24" s="180">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J24" s="193"/>
+      <c r="J24" s="181"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="141" t="s">
+      <c r="B25" s="138" t="s">
         <v>91</v>
       </c>
-      <c r="C25" s="141">
+      <c r="C25" s="138">
         <v>4</v>
       </c>
-      <c r="E25" s="160">
+      <c r="E25" s="149">
         <v>620.08570194143249</v>
       </c>
-      <c r="G25" s="161">
+      <c r="G25" s="150">
         <v>620.08570194143249</v>
       </c>
-      <c r="I25" s="192">
+      <c r="I25" s="180">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J25" s="193"/>
+      <c r="J25" s="181"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="141" t="s">
+      <c r="B26" s="138" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="141">
+      <c r="C26" s="138">
         <v>5</v>
       </c>
-      <c r="E26" s="160">
+      <c r="E26" s="149">
         <v>620.08570194143249</v>
       </c>
-      <c r="G26" s="161">
+      <c r="G26" s="150">
         <v>620.08570194143249</v>
       </c>
-      <c r="I26" s="192">
+      <c r="I26" s="180">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J26" s="193"/>
+      <c r="J26" s="181"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="141" t="s">
+      <c r="B27" s="138" t="s">
         <v>91</v>
       </c>
-      <c r="C27" s="141">
+      <c r="C27" s="138">
         <v>6</v>
       </c>
-      <c r="E27" s="160">
+      <c r="E27" s="149">
         <v>310.04285097071624</v>
       </c>
-      <c r="G27" s="161">
+      <c r="G27" s="150">
         <v>310.04285097071624</v>
       </c>
-      <c r="I27" s="192">
+      <c r="I27" s="180">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J27" s="193"/>
+      <c r="J27" s="181"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B28" s="141" t="s">
+      <c r="B28" s="138" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="141">
+      <c r="C28" s="138">
         <v>7</v>
       </c>
-      <c r="E28" s="160">
+      <c r="E28" s="149">
         <v>310.04285097071624</v>
       </c>
-      <c r="G28" s="161">
+      <c r="G28" s="150">
         <v>310.04285097071624</v>
       </c>
-      <c r="I28" s="192">
+      <c r="I28" s="180">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J28" s="193"/>
+      <c r="J28" s="181"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B29" s="141" t="s">
+      <c r="B29" s="138" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="141">
+      <c r="C29" s="138">
         <v>8</v>
       </c>
-      <c r="E29" s="160">
+      <c r="E29" s="149">
         <v>310.04285097071624</v>
       </c>
-      <c r="G29" s="161">
+      <c r="G29" s="150">
         <v>310.04285097071624</v>
       </c>
-      <c r="I29" s="192">
+      <c r="I29" s="180">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J29" s="193"/>
+      <c r="J29" s="181"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E30" s="150">
+      <c r="E30" s="147">
         <f>SUM(E22:E29)</f>
         <v>4133.9046796095499</v>
       </c>
-      <c r="G30" s="147">
+      <c r="G30" s="144">
         <f>SUM(G22:G29)</f>
         <v>4133.9046796095499</v>
       </c>
-      <c r="I30" s="192">
+      <c r="I30" s="180">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J30" s="193"/>
+      <c r="J30" s="181"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E31" s="150"/>
-      <c r="G31" s="147"/>
-      <c r="I31" s="192">
+      <c r="E31" s="147"/>
+      <c r="G31" s="144"/>
+      <c r="I31" s="180">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J31" s="193"/>
+      <c r="J31" s="181"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E32" s="148"/>
-      <c r="G32" s="149"/>
-      <c r="I32" s="192"/>
-      <c r="J32" s="193"/>
+      <c r="E32" s="145"/>
+      <c r="G32" s="146"/>
+      <c r="I32" s="180"/>
+      <c r="J32" s="181"/>
     </row>
     <row r="33" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E33" s="150">
+      <c r="E33" s="147">
         <f>E30+E21</f>
         <v>351243.74189499998</v>
       </c>
-      <c r="G33" s="147">
+      <c r="G33" s="144">
         <f>G21+G30</f>
         <v>351243.74189499998</v>
       </c>
-      <c r="I33" s="192">
+      <c r="I33" s="180">
         <f>E33-G33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="193"/>
+      <c r="J33" s="181"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
@@ -5020,6 +5119,21 @@
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>

--- a/SALTA 1167/Diciembre/SALTA1167-Diciembre.xlsx
+++ b/SALTA 1167/Diciembre/SALTA1167-Diciembre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\SALTA 1167\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7092D5B-C5D0-43B7-926F-A2D4C688733A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925466A4-DAAC-42F4-82A5-F326B30279E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="140">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -448,6 +448,9 @@
   </si>
   <si>
     <t>QUIENES ESTAN EN VIOLETA NO ESTAN RESPETANDO LOS CENTAVOS AL ABONAR.</t>
+  </si>
+  <si>
+    <t>Totales</t>
   </si>
 </sst>
 </file>
@@ -1111,7 +1114,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="239">
+  <cellXfs count="246">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1365,103 +1368,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="26" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="26" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1484,22 +1391,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1510,44 +1414,11 @@
     </xf>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1561,6 +1432,149 @@
     <xf numFmtId="44" fontId="17" fillId="12" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="12" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="12" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1960,12 +1974,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14"/>
-      <c r="B3" s="159" t="s">
+      <c r="B3" s="197" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
+      <c r="C3" s="197"/>
+      <c r="D3" s="197"/>
+      <c r="E3" s="198"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
@@ -2003,49 +2017,49 @@
       <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="162" t="s">
+      <c r="B8" s="200" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="162"/>
+      <c r="C8" s="200"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="162"/>
-      <c r="C9" s="162"/>
+      <c r="B9" s="200"/>
+      <c r="C9" s="200"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="162"/>
-      <c r="C10" s="162"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="200"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="161" t="s">
+      <c r="A13" s="199" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="161"/>
-      <c r="C13" s="161"/>
-      <c r="D13" s="161"/>
-      <c r="E13" s="161"/>
+      <c r="B13" s="199"/>
+      <c r="C13" s="199"/>
+      <c r="D13" s="199"/>
+      <c r="E13" s="199"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="161"/>
-      <c r="B14" s="161"/>
-      <c r="C14" s="161"/>
-      <c r="D14" s="161"/>
-      <c r="E14" s="161"/>
+      <c r="A14" s="199"/>
+      <c r="B14" s="199"/>
+      <c r="C14" s="199"/>
+      <c r="D14" s="199"/>
+      <c r="E14" s="199"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="161"/>
-      <c r="B15" s="161"/>
-      <c r="C15" s="161"/>
-      <c r="D15" s="161"/>
-      <c r="E15" s="161"/>
+      <c r="A15" s="199"/>
+      <c r="B15" s="199"/>
+      <c r="C15" s="199"/>
+      <c r="D15" s="199"/>
+      <c r="E15" s="199"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="161"/>
-      <c r="B16" s="161"/>
-      <c r="C16" s="161"/>
-      <c r="D16" s="161"/>
-      <c r="E16" s="161"/>
+      <c r="A16" s="199"/>
+      <c r="B16" s="199"/>
+      <c r="C16" s="199"/>
+      <c r="D16" s="199"/>
+      <c r="E16" s="199"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -2071,10 +2085,10 @@
       <c r="E21" s="104"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="155" t="s">
+      <c r="A22" s="195" t="s">
         <v>122</v>
       </c>
-      <c r="B22" s="156"/>
+      <c r="B22" s="196"/>
       <c r="C22" s="39"/>
       <c r="D22" s="153">
         <v>464897.27</v>
@@ -2085,8 +2099,8 @@
       <c r="H22" s="93"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="155"/>
-      <c r="B23" s="156"/>
+      <c r="A23" s="195"/>
+      <c r="B23" s="196"/>
       <c r="C23" s="39"/>
       <c r="D23" s="120"/>
       <c r="E23" s="113"/>
@@ -2114,12 +2128,12 @@
       <c r="E25" s="133"/>
     </row>
     <row r="26" spans="1:8" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="185" t="s">
+      <c r="A26" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="186"/>
+      <c r="B26" s="202"/>
       <c r="C26" s="41"/>
-      <c r="D26" s="184">
+      <c r="D26" s="155">
         <v>74591</v>
       </c>
       <c r="E26" s="106" t="s">
@@ -2185,10 +2199,10 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="163" t="s">
+      <c r="A32" s="203" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="164"/>
+      <c r="B32" s="204"/>
       <c r="C32" s="5"/>
       <c r="D32" s="154">
         <v>358176.46</v>
@@ -2230,19 +2244,19 @@
       <c r="E35" s="110"/>
     </row>
     <row r="36" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="155" t="s">
+      <c r="A36" s="195" t="s">
         <v>133</v>
       </c>
-      <c r="B36" s="156"/>
+      <c r="B36" s="196"/>
       <c r="C36" s="5"/>
       <c r="D36" s="114"/>
       <c r="E36" s="115"/>
     </row>
     <row r="37" spans="1:5" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="155" t="s">
+      <c r="A37" s="195" t="s">
         <v>128</v>
       </c>
-      <c r="B37" s="156"/>
+      <c r="B37" s="196"/>
       <c r="C37" s="5"/>
       <c r="D37" s="152">
         <v>1537000</v>
@@ -2252,10 +2266,10 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="155" t="s">
+      <c r="A38" s="195" t="s">
         <v>123</v>
       </c>
-      <c r="B38" s="156"/>
+      <c r="B38" s="196"/>
       <c r="C38" s="5"/>
       <c r="D38" s="152">
         <v>42370</v>
@@ -2265,10 +2279,10 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="155" t="s">
+      <c r="A39" s="195" t="s">
         <v>134</v>
       </c>
-      <c r="B39" s="156"/>
+      <c r="B39" s="196"/>
       <c r="C39" s="5"/>
       <c r="D39" s="152">
         <v>24884.21</v>
@@ -2299,10 +2313,10 @@
       <c r="E41" s="104"/>
     </row>
     <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="155" t="s">
+      <c r="A42" s="195" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="156"/>
+      <c r="B42" s="196"/>
       <c r="C42" s="39"/>
       <c r="D42" s="153">
         <v>140000</v>
@@ -2432,8 +2446,8 @@
       <c r="E56" s="76"/>
     </row>
     <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="187"/>
-      <c r="B57" s="187"/>
+      <c r="A57" s="207"/>
+      <c r="B57" s="207"/>
       <c r="C57" s="5"/>
       <c r="D57" s="114"/>
       <c r="E57" s="76"/>
@@ -2658,16 +2672,16 @@
     </row>
     <row r="89" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A90" s="158" t="s">
+      <c r="A90" s="206" t="s">
         <v>19</v>
       </c>
-      <c r="B90" s="158"/>
-      <c r="C90" s="158"/>
+      <c r="B90" s="206"/>
+      <c r="C90" s="206"/>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A91" s="158"/>
-      <c r="B91" s="158"/>
-      <c r="C91" s="158"/>
+      <c r="A91" s="206"/>
+      <c r="B91" s="206"/>
+      <c r="C91" s="206"/>
     </row>
     <row r="92" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="90"/>
@@ -2697,35 +2711,40 @@
       <c r="M95" s="6"/>
     </row>
     <row r="96" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="157"/>
-      <c r="B96" s="157"/>
-      <c r="C96" s="157"/>
-      <c r="D96" s="157"/>
-      <c r="E96" s="157"/>
+      <c r="A96" s="205"/>
+      <c r="B96" s="205"/>
+      <c r="C96" s="205"/>
+      <c r="D96" s="205"/>
+      <c r="E96" s="205"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="157"/>
-      <c r="B97" s="157"/>
-      <c r="C97" s="157"/>
-      <c r="D97" s="157"/>
-      <c r="E97" s="157"/>
+      <c r="A97" s="205"/>
+      <c r="B97" s="205"/>
+      <c r="C97" s="205"/>
+      <c r="D97" s="205"/>
+      <c r="E97" s="205"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="157"/>
-      <c r="B98" s="157"/>
-      <c r="C98" s="157"/>
-      <c r="D98" s="157"/>
-      <c r="E98" s="157"/>
+      <c r="A98" s="205"/>
+      <c r="B98" s="205"/>
+      <c r="C98" s="205"/>
+      <c r="D98" s="205"/>
+      <c r="E98" s="205"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="157"/>
-      <c r="B99" s="157"/>
-      <c r="C99" s="157"/>
-      <c r="D99" s="157"/>
-      <c r="E99" s="157"/>
+      <c r="A99" s="205"/>
+      <c r="B99" s="205"/>
+      <c r="C99" s="205"/>
+      <c r="D99" s="205"/>
+      <c r="E99" s="205"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A96:E99"/>
+    <mergeCell ref="A90:C91"/>
+    <mergeCell ref="A57:B57"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A37:B37"/>
@@ -2736,11 +2755,6 @@
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A96:E99"/>
-    <mergeCell ref="A90:C91"/>
-    <mergeCell ref="A57:B57"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2773,259 +2787,259 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="201"/>
-      <c r="B1" s="202"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-      <c r="K1" s="204"/>
-      <c r="L1" s="204"/>
-      <c r="M1" s="204"/>
-      <c r="N1" s="202"/>
-      <c r="O1" s="205"/>
+      <c r="A1" s="169"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="208"/>
+      <c r="G1" s="208"/>
+      <c r="H1" s="208"/>
+      <c r="I1" s="208"/>
+      <c r="J1" s="208"/>
+      <c r="K1" s="208"/>
+      <c r="L1" s="208"/>
+      <c r="M1" s="208"/>
+      <c r="N1" s="170"/>
+      <c r="O1" s="172"/>
     </row>
     <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="206"/>
-      <c r="B2" s="207"/>
-      <c r="C2" s="208"/>
-      <c r="D2" s="209"/>
-      <c r="E2" s="209" t="s">
+      <c r="A2" s="173"/>
+      <c r="B2" s="174"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176" t="s">
         <v>102</v>
       </c>
-      <c r="F2" s="209"/>
-      <c r="G2" s="210">
-        <v>0</v>
-      </c>
-      <c r="H2" s="209"/>
-      <c r="I2" s="209"/>
-      <c r="J2" s="211"/>
-      <c r="K2" s="209" t="s">
+      <c r="F2" s="176"/>
+      <c r="G2" s="177">
+        <v>0</v>
+      </c>
+      <c r="H2" s="176"/>
+      <c r="I2" s="176"/>
+      <c r="J2" s="178"/>
+      <c r="K2" s="176" t="s">
         <v>101</v>
       </c>
-      <c r="L2" s="212">
+      <c r="L2" s="179">
         <v>2000000</v>
       </c>
-      <c r="M2" s="213"/>
-      <c r="N2" s="214"/>
-      <c r="O2" s="215"/>
+      <c r="M2" s="180"/>
+      <c r="N2" s="181"/>
+      <c r="O2" s="182"/>
       <c r="P2" s="20"/>
     </row>
     <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="206"/>
-      <c r="B3" s="207"/>
-      <c r="C3" s="208"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="208"/>
-      <c r="F3" s="208"/>
-      <c r="G3" s="216"/>
-      <c r="H3" s="208"/>
-      <c r="I3" s="208"/>
-      <c r="J3" s="217"/>
-      <c r="K3" s="208"/>
-      <c r="L3" s="208"/>
-      <c r="M3" s="213"/>
-      <c r="N3" s="214"/>
-      <c r="O3" s="215"/>
+      <c r="A3" s="173"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="175"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="175"/>
+      <c r="L3" s="175"/>
+      <c r="M3" s="180"/>
+      <c r="N3" s="181"/>
+      <c r="O3" s="182"/>
       <c r="P3" s="20"/>
     </row>
     <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="223" t="s">
+      <c r="A4" s="220" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="224"/>
-      <c r="C4" s="224"/>
-      <c r="D4" s="224"/>
-      <c r="E4" s="224"/>
-      <c r="F4" s="224"/>
-      <c r="G4" s="224"/>
-      <c r="H4" s="224"/>
-      <c r="I4" s="224"/>
-      <c r="J4" s="224"/>
-      <c r="K4" s="224"/>
-      <c r="L4" s="224"/>
-      <c r="M4" s="224"/>
-      <c r="N4" s="224"/>
-      <c r="O4" s="225"/>
+      <c r="B4" s="221"/>
+      <c r="C4" s="221"/>
+      <c r="D4" s="221"/>
+      <c r="E4" s="221"/>
+      <c r="F4" s="221"/>
+      <c r="G4" s="221"/>
+      <c r="H4" s="221"/>
+      <c r="I4" s="221"/>
+      <c r="J4" s="221"/>
+      <c r="K4" s="221"/>
+      <c r="L4" s="221"/>
+      <c r="M4" s="221"/>
+      <c r="N4" s="221"/>
+      <c r="O4" s="222"/>
       <c r="P4" s="20"/>
     </row>
     <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="220"/>
-      <c r="B5" s="218"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="218"/>
-      <c r="E5" s="218"/>
-      <c r="F5" s="218"/>
-      <c r="G5" s="218"/>
-      <c r="H5" s="218"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="218"/>
-      <c r="K5" s="218"/>
-      <c r="L5" s="218"/>
-      <c r="M5" s="218"/>
-      <c r="N5" s="218"/>
-      <c r="O5" s="219"/>
+      <c r="A5" s="223"/>
+      <c r="B5" s="224"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="224"/>
+      <c r="E5" s="224"/>
+      <c r="F5" s="224"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="224"/>
+      <c r="I5" s="224"/>
+      <c r="J5" s="224"/>
+      <c r="K5" s="224"/>
+      <c r="L5" s="224"/>
+      <c r="M5" s="224"/>
+      <c r="N5" s="224"/>
+      <c r="O5" s="225"/>
       <c r="P5" s="20"/>
     </row>
     <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="220"/>
-      <c r="B6" s="218"/>
-      <c r="C6" s="218"/>
-      <c r="D6" s="218"/>
-      <c r="E6" s="218"/>
-      <c r="F6" s="218"/>
-      <c r="G6" s="218"/>
-      <c r="H6" s="218"/>
-      <c r="I6" s="218"/>
-      <c r="J6" s="218"/>
-      <c r="K6" s="218"/>
-      <c r="L6" s="218"/>
-      <c r="M6" s="218"/>
-      <c r="N6" s="218"/>
-      <c r="O6" s="219"/>
+      <c r="A6" s="223"/>
+      <c r="B6" s="224"/>
+      <c r="C6" s="224"/>
+      <c r="D6" s="224"/>
+      <c r="E6" s="224"/>
+      <c r="F6" s="224"/>
+      <c r="G6" s="224"/>
+      <c r="H6" s="224"/>
+      <c r="I6" s="224"/>
+      <c r="J6" s="224"/>
+      <c r="K6" s="224"/>
+      <c r="L6" s="224"/>
+      <c r="M6" s="224"/>
+      <c r="N6" s="224"/>
+      <c r="O6" s="225"/>
       <c r="P6" s="20"/>
     </row>
     <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="220"/>
-      <c r="B7" s="218"/>
-      <c r="C7" s="218"/>
-      <c r="D7" s="218"/>
-      <c r="E7" s="218"/>
-      <c r="F7" s="218"/>
-      <c r="G7" s="218"/>
-      <c r="H7" s="218"/>
-      <c r="I7" s="218"/>
-      <c r="J7" s="218"/>
-      <c r="K7" s="218"/>
-      <c r="L7" s="218"/>
-      <c r="M7" s="218"/>
-      <c r="N7" s="218"/>
-      <c r="O7" s="219"/>
+      <c r="A7" s="223"/>
+      <c r="B7" s="224"/>
+      <c r="C7" s="224"/>
+      <c r="D7" s="224"/>
+      <c r="E7" s="224"/>
+      <c r="F7" s="224"/>
+      <c r="G7" s="224"/>
+      <c r="H7" s="224"/>
+      <c r="I7" s="224"/>
+      <c r="J7" s="224"/>
+      <c r="K7" s="224"/>
+      <c r="L7" s="224"/>
+      <c r="M7" s="224"/>
+      <c r="N7" s="224"/>
+      <c r="O7" s="225"/>
       <c r="P7" s="20"/>
     </row>
     <row r="8" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="221"/>
-      <c r="B8" s="177"/>
-      <c r="C8" s="177"/>
-      <c r="D8" s="177"/>
-      <c r="E8" s="177"/>
-      <c r="F8" s="177"/>
-      <c r="G8" s="177"/>
-      <c r="H8" s="177"/>
-      <c r="I8" s="177"/>
-      <c r="J8" s="177"/>
-      <c r="K8" s="177"/>
-      <c r="L8" s="177"/>
-      <c r="M8" s="177"/>
-      <c r="N8" s="177"/>
-      <c r="O8" s="222"/>
+      <c r="A8" s="226"/>
+      <c r="B8" s="227"/>
+      <c r="C8" s="227"/>
+      <c r="D8" s="227"/>
+      <c r="E8" s="227"/>
+      <c r="F8" s="227"/>
+      <c r="G8" s="227"/>
+      <c r="H8" s="227"/>
+      <c r="I8" s="227"/>
+      <c r="J8" s="227"/>
+      <c r="K8" s="227"/>
+      <c r="L8" s="227"/>
+      <c r="M8" s="227"/>
+      <c r="N8" s="227"/>
+      <c r="O8" s="228"/>
     </row>
     <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="226" t="s">
+      <c r="A9" s="231" t="s">
         <v>136</v>
       </c>
-      <c r="B9" s="227"/>
-      <c r="C9" s="227"/>
-      <c r="D9" s="227"/>
-      <c r="E9" s="227"/>
-      <c r="F9" s="227"/>
-      <c r="G9" s="227"/>
-      <c r="H9" s="227"/>
-      <c r="I9" s="227"/>
-      <c r="J9" s="227"/>
-      <c r="K9" s="227"/>
-      <c r="L9" s="227"/>
-      <c r="M9" s="227"/>
-      <c r="N9" s="227"/>
-      <c r="O9" s="227"/>
+      <c r="B9" s="232"/>
+      <c r="C9" s="232"/>
+      <c r="D9" s="232"/>
+      <c r="E9" s="232"/>
+      <c r="F9" s="232"/>
+      <c r="G9" s="232"/>
+      <c r="H9" s="232"/>
+      <c r="I9" s="232"/>
+      <c r="J9" s="232"/>
+      <c r="K9" s="232"/>
+      <c r="L9" s="232"/>
+      <c r="M9" s="232"/>
+      <c r="N9" s="232"/>
+      <c r="O9" s="232"/>
     </row>
     <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="228" t="s">
+      <c r="A10" s="233" t="s">
         <v>138</v>
       </c>
-      <c r="B10" s="228"/>
-      <c r="C10" s="228"/>
-      <c r="D10" s="228"/>
-      <c r="E10" s="228"/>
-      <c r="F10" s="228"/>
-      <c r="G10" s="228"/>
-      <c r="H10" s="228"/>
-      <c r="I10" s="228"/>
-      <c r="J10" s="228"/>
-      <c r="K10" s="228"/>
-      <c r="L10" s="228"/>
-      <c r="M10" s="228"/>
-      <c r="N10" s="228"/>
-      <c r="O10" s="228"/>
+      <c r="B10" s="233"/>
+      <c r="C10" s="233"/>
+      <c r="D10" s="233"/>
+      <c r="E10" s="233"/>
+      <c r="F10" s="233"/>
+      <c r="G10" s="233"/>
+      <c r="H10" s="233"/>
+      <c r="I10" s="233"/>
+      <c r="J10" s="233"/>
+      <c r="K10" s="233"/>
+      <c r="L10" s="233"/>
+      <c r="M10" s="233"/>
+      <c r="N10" s="233"/>
+      <c r="O10" s="233"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="165" t="s">
+      <c r="A11" s="213" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="127"/>
-      <c r="C11" s="165" t="s">
+      <c r="C11" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="165" t="s">
+      <c r="D11" s="213" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="165" t="s">
+      <c r="E11" s="213" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="168" t="s">
+      <c r="F11" s="209" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="165" t="s">
+      <c r="G11" s="213" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="172" t="s">
+      <c r="H11" s="215" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="168" t="s">
+      <c r="I11" s="209" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="168" t="s">
+      <c r="J11" s="209" t="s">
         <v>84</v>
       </c>
-      <c r="K11" s="168" t="s">
+      <c r="K11" s="209" t="s">
         <v>101</v>
       </c>
-      <c r="L11" s="175" t="s">
+      <c r="L11" s="218" t="s">
         <v>102</v>
       </c>
       <c r="M11" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="N11" s="170" t="s">
+      <c r="N11" s="211" t="s">
         <v>12</v>
       </c>
-      <c r="O11" s="178" t="s">
+      <c r="O11" s="229" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="167"/>
+      <c r="A12" s="214"/>
       <c r="B12" s="128"/>
-      <c r="C12" s="167"/>
-      <c r="D12" s="166"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="169"/>
-      <c r="G12" s="167"/>
-      <c r="H12" s="173"/>
-      <c r="I12" s="169"/>
-      <c r="J12" s="174"/>
-      <c r="K12" s="169"/>
-      <c r="L12" s="176"/>
+      <c r="C12" s="214"/>
+      <c r="D12" s="234"/>
+      <c r="E12" s="214"/>
+      <c r="F12" s="210"/>
+      <c r="G12" s="214"/>
+      <c r="H12" s="216"/>
+      <c r="I12" s="210"/>
+      <c r="J12" s="217"/>
+      <c r="K12" s="210"/>
+      <c r="L12" s="219"/>
       <c r="M12" s="43" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 15/01</v>
       </c>
-      <c r="N12" s="171"/>
-      <c r="O12" s="179"/>
+      <c r="N12" s="212"/>
+      <c r="O12" s="230"/>
     </row>
     <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="46">
@@ -3044,7 +3058,7 @@
       <c r="F13" s="56">
         <v>232082.01</v>
       </c>
-      <c r="G13" s="188">
+      <c r="G13" s="156">
         <f>256082.01-G29-G30</f>
         <v>232081.66</v>
       </c>
@@ -3101,7 +3115,7 @@
       <c r="F14" s="56">
         <v>132000.01999999999</v>
       </c>
-      <c r="G14" s="188">
+      <c r="G14" s="156">
         <f>F14</f>
         <v>132000.01999999999</v>
       </c>
@@ -3161,7 +3175,7 @@
       <c r="F15" s="56">
         <v>108000.03</v>
       </c>
-      <c r="G15" s="188">
+      <c r="G15" s="156">
         <f>F15</f>
         <v>108000.03</v>
       </c>
@@ -3221,7 +3235,7 @@
       <c r="F16" s="56">
         <v>129700.04</v>
       </c>
-      <c r="G16" s="188">
+      <c r="G16" s="156">
         <f>154060-G32</f>
         <v>129700</v>
       </c>
@@ -3263,57 +3277,57 @@
       </c>
     </row>
     <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="229">
+      <c r="A17" s="185">
         <v>5</v>
       </c>
-      <c r="B17" s="229" t="s">
+      <c r="B17" s="185" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="229" t="s">
+      <c r="C17" s="185" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="229" t="s">
+      <c r="D17" s="185" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="230">
+      <c r="E17" s="186">
         <v>6.6</v>
       </c>
-      <c r="F17" s="231">
+      <c r="F17" s="187">
         <v>132000.04999999999</v>
       </c>
-      <c r="G17" s="232">
+      <c r="G17" s="188">
         <f t="shared" ref="G17:G21" si="8">F17</f>
         <v>132000.04999999999</v>
       </c>
-      <c r="H17" s="233">
+      <c r="H17" s="189">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="233">
+      <c r="I17" s="189">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="234">
+      <c r="J17" s="190">
         <f>EDESUR!I9</f>
         <v>0</v>
       </c>
-      <c r="K17" s="235">
+      <c r="K17" s="191">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L17" s="235">
+      <c r="L17" s="191">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M17" s="236">
+      <c r="M17" s="192">
         <f t="shared" si="4"/>
         <v>132000.04999999999</v>
       </c>
-      <c r="N17" s="237">
+      <c r="N17" s="193">
         <f t="shared" si="5"/>
         <v>139920.04999999999</v>
       </c>
-      <c r="O17" s="238">
+      <c r="O17" s="194">
         <f t="shared" si="6"/>
         <v>135960.04999999999</v>
       </c>
@@ -3344,7 +3358,7 @@
       <c r="F18" s="56">
         <v>108000.06</v>
       </c>
-      <c r="G18" s="188">
+      <c r="G18" s="156">
         <f t="shared" si="8"/>
         <v>108000.06</v>
       </c>
@@ -3386,57 +3400,57 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="190">
+      <c r="A19" s="158">
         <v>7</v>
       </c>
-      <c r="B19" s="190" t="s">
+      <c r="B19" s="158" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="190" t="s">
+      <c r="C19" s="158" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="190" t="s">
+      <c r="D19" s="158" t="s">
         <v>97</v>
       </c>
-      <c r="E19" s="192">
+      <c r="E19" s="160">
         <v>5.4</v>
       </c>
-      <c r="F19" s="193">
+      <c r="F19" s="161">
         <v>108000.07</v>
       </c>
-      <c r="G19" s="194">
+      <c r="G19" s="162">
         <f t="shared" si="8"/>
         <v>108000.07</v>
       </c>
-      <c r="H19" s="195">
+      <c r="H19" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="195">
+      <c r="I19" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="196">
+      <c r="J19" s="164">
         <f>EDESUR!I11</f>
         <v>0</v>
       </c>
-      <c r="K19" s="197">
+      <c r="K19" s="165">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L19" s="197">
+      <c r="L19" s="165">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M19" s="198">
+      <c r="M19" s="166">
         <f t="shared" si="4"/>
         <v>108000.07</v>
       </c>
-      <c r="N19" s="199">
+      <c r="N19" s="167">
         <f t="shared" si="5"/>
         <v>114480.07</v>
       </c>
-      <c r="O19" s="200">
+      <c r="O19" s="168">
         <f t="shared" si="6"/>
         <v>111240.07</v>
       </c>
@@ -3446,57 +3460,57 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="190">
+      <c r="A20" s="158">
         <v>8</v>
       </c>
-      <c r="B20" s="190" t="s">
+      <c r="B20" s="158" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="190" t="s">
+      <c r="C20" s="158" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="191" t="s">
+      <c r="D20" s="159" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="192">
+      <c r="E20" s="160">
         <v>6.6</v>
       </c>
-      <c r="F20" s="193">
+      <c r="F20" s="161">
         <v>132000.07999999999</v>
       </c>
-      <c r="G20" s="194">
+      <c r="G20" s="162">
         <f t="shared" si="8"/>
         <v>132000.07999999999</v>
       </c>
-      <c r="H20" s="195">
+      <c r="H20" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="195">
+      <c r="I20" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="196">
+      <c r="J20" s="164">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="K20" s="197">
+      <c r="K20" s="165">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L20" s="197">
+      <c r="L20" s="165">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M20" s="198">
+      <c r="M20" s="166">
         <f t="shared" si="4"/>
         <v>132000.07999999999</v>
       </c>
-      <c r="N20" s="199">
+      <c r="N20" s="167">
         <f t="shared" si="5"/>
         <v>139920.07999999999</v>
       </c>
-      <c r="O20" s="200">
+      <c r="O20" s="168">
         <f t="shared" si="6"/>
         <v>135960.07999999999</v>
       </c>
@@ -3524,7 +3538,7 @@
       <c r="F21" s="56">
         <v>132000.09</v>
       </c>
-      <c r="G21" s="188">
+      <c r="G21" s="156">
         <f t="shared" si="8"/>
         <v>132000.09</v>
       </c>
@@ -3584,7 +3598,7 @@
       <c r="F22" s="56">
         <v>68000.100000000006</v>
       </c>
-      <c r="G22" s="188">
+      <c r="G22" s="156">
         <f>F22</f>
         <v>68000.100000000006</v>
       </c>
@@ -3642,7 +3656,7 @@
       <c r="F23" s="56">
         <v>108000.11</v>
       </c>
-      <c r="G23" s="188">
+      <c r="G23" s="156">
         <f>114000.11-G34</f>
         <v>108000.11</v>
       </c>
@@ -3705,7 +3719,7 @@
       <c r="F24" s="56">
         <v>132000.12</v>
       </c>
-      <c r="G24" s="188">
+      <c r="G24" s="156">
         <f>F24</f>
         <v>132000.12</v>
       </c>
@@ -3765,7 +3779,7 @@
       <c r="F25" s="56">
         <v>128040.13</v>
       </c>
-      <c r="G25" s="188">
+      <c r="G25" s="156">
         <v>131881.13</v>
       </c>
       <c r="H25" s="58">
@@ -3822,7 +3836,7 @@
       <c r="F26" s="56">
         <v>108000.14</v>
       </c>
-      <c r="G26" s="188">
+      <c r="G26" s="156">
         <f>F26+RESUMEN!D39</f>
         <v>132884.35</v>
       </c>
@@ -3880,7 +3894,7 @@
       <c r="F27" s="56">
         <v>108000.15</v>
       </c>
-      <c r="G27" s="188">
+      <c r="G27" s="156">
         <f>F27</f>
         <v>108000.15</v>
       </c>
@@ -3940,7 +3954,7 @@
       <c r="F28" s="56">
         <v>14000.16</v>
       </c>
-      <c r="G28" s="188">
+      <c r="G28" s="156">
         <f>F28</f>
         <v>14000.16</v>
       </c>
@@ -3998,7 +4012,7 @@
       <c r="F29" s="57">
         <v>12000.17</v>
       </c>
-      <c r="G29" s="188">
+      <c r="G29" s="156">
         <f t="shared" ref="G29:G31" si="9">F29</f>
         <v>12000.17</v>
       </c>
@@ -4056,7 +4070,7 @@
       <c r="F30" s="56">
         <v>12000.18</v>
       </c>
-      <c r="G30" s="188">
+      <c r="G30" s="156">
         <f t="shared" si="9"/>
         <v>12000.18</v>
       </c>
@@ -4114,7 +4128,7 @@
       <c r="F31" s="56">
         <v>12000.19</v>
       </c>
-      <c r="G31" s="188">
+      <c r="G31" s="156">
         <f t="shared" si="9"/>
         <v>12000.19</v>
       </c>
@@ -4171,7 +4185,7 @@
       <c r="F32" s="65">
         <v>24360</v>
       </c>
-      <c r="G32" s="188">
+      <c r="G32" s="156">
         <f>F32</f>
         <v>24360</v>
       </c>
@@ -4228,7 +4242,7 @@
       <c r="F33" s="65">
         <v>6000</v>
       </c>
-      <c r="G33" s="189">
+      <c r="G33" s="157">
         <f>F33</f>
         <v>6000</v>
       </c>
@@ -4283,7 +4297,7 @@
       <c r="F34" s="65">
         <v>6000</v>
       </c>
-      <c r="G34" s="189">
+      <c r="G34" s="157">
         <f>F34</f>
         <v>6000</v>
       </c>
@@ -4340,7 +4354,7 @@
       <c r="F35" s="65">
         <v>6000</v>
       </c>
-      <c r="G35" s="189">
+      <c r="G35" s="157">
         <f>F35</f>
         <v>6000</v>
       </c>
@@ -4434,88 +4448,93 @@
     </row>
     <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="39" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="157" t="str">
+      <c r="C39" s="205" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="157"/>
-      <c r="E39" s="157"/>
-      <c r="F39" s="157"/>
-      <c r="G39" s="157"/>
-      <c r="H39" s="157"/>
-      <c r="I39" s="157"/>
-      <c r="J39" s="157"/>
-      <c r="K39" s="157"/>
-      <c r="L39" s="157"/>
-      <c r="M39" s="157"/>
+      <c r="D39" s="205"/>
+      <c r="E39" s="205"/>
+      <c r="F39" s="205"/>
+      <c r="G39" s="205"/>
+      <c r="H39" s="205"/>
+      <c r="I39" s="205"/>
+      <c r="J39" s="205"/>
+      <c r="K39" s="205"/>
+      <c r="L39" s="205"/>
+      <c r="M39" s="205"/>
     </row>
     <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="157"/>
-      <c r="D40" s="157"/>
-      <c r="E40" s="157"/>
-      <c r="F40" s="157"/>
-      <c r="G40" s="157"/>
-      <c r="H40" s="157"/>
-      <c r="I40" s="157"/>
-      <c r="J40" s="157"/>
-      <c r="K40" s="157"/>
-      <c r="L40" s="157"/>
-      <c r="M40" s="157"/>
+      <c r="C40" s="205"/>
+      <c r="D40" s="205"/>
+      <c r="E40" s="205"/>
+      <c r="F40" s="205"/>
+      <c r="G40" s="205"/>
+      <c r="H40" s="205"/>
+      <c r="I40" s="205"/>
+      <c r="J40" s="205"/>
+      <c r="K40" s="205"/>
+      <c r="L40" s="205"/>
+      <c r="M40" s="205"/>
     </row>
     <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="157"/>
-      <c r="D41" s="157"/>
-      <c r="E41" s="157"/>
-      <c r="F41" s="157"/>
-      <c r="G41" s="157"/>
-      <c r="H41" s="157"/>
-      <c r="I41" s="157"/>
-      <c r="J41" s="157"/>
-      <c r="K41" s="157"/>
-      <c r="L41" s="157"/>
-      <c r="M41" s="157"/>
+      <c r="C41" s="205"/>
+      <c r="D41" s="205"/>
+      <c r="E41" s="205"/>
+      <c r="F41" s="205"/>
+      <c r="G41" s="205"/>
+      <c r="H41" s="205"/>
+      <c r="I41" s="205"/>
+      <c r="J41" s="205"/>
+      <c r="K41" s="205"/>
+      <c r="L41" s="205"/>
+      <c r="M41" s="205"/>
     </row>
     <row r="42" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="157"/>
-      <c r="D42" s="157"/>
-      <c r="E42" s="157"/>
-      <c r="F42" s="157"/>
-      <c r="G42" s="157"/>
-      <c r="H42" s="157"/>
-      <c r="I42" s="157"/>
-      <c r="J42" s="157"/>
-      <c r="K42" s="157"/>
-      <c r="L42" s="157"/>
-      <c r="M42" s="157"/>
+      <c r="C42" s="205"/>
+      <c r="D42" s="205"/>
+      <c r="E42" s="205"/>
+      <c r="F42" s="205"/>
+      <c r="G42" s="205"/>
+      <c r="H42" s="205"/>
+      <c r="I42" s="205"/>
+      <c r="J42" s="205"/>
+      <c r="K42" s="205"/>
+      <c r="L42" s="205"/>
+      <c r="M42" s="205"/>
     </row>
     <row r="43" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="157"/>
-      <c r="D43" s="157"/>
-      <c r="E43" s="157"/>
-      <c r="F43" s="157"/>
-      <c r="G43" s="157"/>
-      <c r="H43" s="157"/>
-      <c r="I43" s="157"/>
-      <c r="J43" s="157"/>
-      <c r="K43" s="157"/>
-      <c r="L43" s="157"/>
-      <c r="M43" s="157"/>
+      <c r="C43" s="205"/>
+      <c r="D43" s="205"/>
+      <c r="E43" s="205"/>
+      <c r="F43" s="205"/>
+      <c r="G43" s="205"/>
+      <c r="H43" s="205"/>
+      <c r="I43" s="205"/>
+      <c r="J43" s="205"/>
+      <c r="K43" s="205"/>
+      <c r="L43" s="205"/>
+      <c r="M43" s="205"/>
     </row>
     <row r="44" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="157"/>
-      <c r="D44" s="157"/>
-      <c r="E44" s="157"/>
-      <c r="F44" s="157"/>
-      <c r="G44" s="157"/>
-      <c r="H44" s="157"/>
-      <c r="I44" s="157"/>
-      <c r="J44" s="157"/>
-      <c r="K44" s="157"/>
-      <c r="L44" s="157"/>
-      <c r="M44" s="157"/>
+      <c r="C44" s="205"/>
+      <c r="D44" s="205"/>
+      <c r="E44" s="205"/>
+      <c r="F44" s="205"/>
+      <c r="G44" s="205"/>
+      <c r="H44" s="205"/>
+      <c r="I44" s="205"/>
+      <c r="J44" s="205"/>
+      <c r="K44" s="205"/>
+      <c r="L44" s="205"/>
+      <c r="M44" s="205"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C39:M44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
     <mergeCell ref="E1:M1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4529,11 +4548,6 @@
     <mergeCell ref="O11:O12"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="A10:O10"/>
-    <mergeCell ref="C39:M44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4566,18 +4580,18 @@
       <c r="G3" s="141" t="s">
         <v>93</v>
       </c>
-      <c r="I3" s="182" t="s">
+      <c r="I3" s="237" t="s">
         <v>94</v>
       </c>
-      <c r="J3" s="183"/>
+      <c r="J3" s="238"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="138"/>
       <c r="C4" s="138"/>
       <c r="E4" s="138"/>
       <c r="G4" s="142"/>
-      <c r="I4" s="182"/>
-      <c r="J4" s="183"/>
+      <c r="I4" s="237"/>
+      <c r="J4" s="238"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="138">
@@ -4587,17 +4601,18 @@
         <v>87</v>
       </c>
       <c r="E5" s="143">
-        <v>61353.383534261804</v>
+        <v>26132.02</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="144">
-        <v>61353.383534261804</v>
-      </c>
-      <c r="I5" s="180">
+        <f>E5</f>
+        <v>26132.02</v>
+      </c>
+      <c r="I5" s="235">
         <f>E5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="181"/>
+      <c r="J5" s="236"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="138">
@@ -4607,17 +4622,18 @@
         <v>88</v>
       </c>
       <c r="E6" s="143">
-        <v>34428.700834302756</v>
+        <v>12925.66</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="144">
-        <v>34428.700834302756</v>
-      </c>
-      <c r="I6" s="180">
-        <f t="shared" ref="I6:I21" si="0">E6-G6</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="181"/>
+        <f t="shared" ref="G6:G19" si="0">E6</f>
+        <v>12925.66</v>
+      </c>
+      <c r="I6" s="235">
+        <f t="shared" ref="I6:I21" si="1">E6-G6</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="236"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="138">
@@ -4627,17 +4643,18 @@
         <v>89</v>
       </c>
       <c r="E7" s="143">
-        <v>14356.010802482968</v>
+        <v>10709.96</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="144">
-        <v>14356.010802482968</v>
-      </c>
-      <c r="I7" s="180">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="181"/>
+        <v>10709.96</v>
+      </c>
+      <c r="I7" s="235">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="236"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="138">
@@ -4647,17 +4664,18 @@
         <v>87</v>
       </c>
       <c r="E8" s="143">
-        <v>12061.218355435631</v>
+        <v>5448.33</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="144">
-        <v>12061.218355435631</v>
-      </c>
-      <c r="I8" s="180">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="181"/>
+        <v>5448.33</v>
+      </c>
+      <c r="I8" s="235">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="236"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="139">
@@ -4667,17 +4685,18 @@
         <v>90</v>
       </c>
       <c r="E9" s="143">
-        <v>53068.035404197428</v>
+        <v>2716.04</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="144">
-        <v>53068.035404197428</v>
-      </c>
-      <c r="I9" s="180">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="181"/>
+        <v>2716.04</v>
+      </c>
+      <c r="I9" s="235">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="236"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="139">
@@ -4687,17 +4706,18 @@
         <v>88</v>
       </c>
       <c r="E10" s="143">
-        <v>9841.6389016527519</v>
+        <v>2716.04</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="144">
-        <v>9841.6389016527519</v>
-      </c>
-      <c r="I10" s="180">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="181"/>
+        <v>2716.04</v>
+      </c>
+      <c r="I10" s="235">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="236"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="139">
@@ -4707,17 +4727,18 @@
         <v>89</v>
       </c>
       <c r="E11" s="143">
-        <v>9327.3712310195588</v>
+        <v>2222.21</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="144">
-        <v>9327.3712310195588</v>
-      </c>
-      <c r="I11" s="180">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="181"/>
+        <v>2222.21</v>
+      </c>
+      <c r="I11" s="235">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="236"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="139">
@@ -4727,17 +4748,18 @@
         <v>87</v>
       </c>
       <c r="E12" s="143">
-        <v>9216.1440460861631</v>
+        <v>2222.21</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="144">
-        <v>9216.1440460861631</v>
-      </c>
-      <c r="I12" s="180">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="181"/>
+        <v>2222.21</v>
+      </c>
+      <c r="I12" s="235">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="236"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="138">
@@ -4747,17 +4769,18 @@
         <v>90</v>
       </c>
       <c r="E13" s="143">
-        <v>23200.609218392572</v>
+        <v>24018.62</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="144">
-        <v>23200.609218392572</v>
-      </c>
-      <c r="I13" s="180">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J13" s="181"/>
+        <v>24018.62</v>
+      </c>
+      <c r="I13" s="235">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="236"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="139">
@@ -4767,17 +4790,18 @@
         <v>88</v>
       </c>
       <c r="E14" s="143">
-        <v>7781.0089492021225</v>
+        <v>2716.04</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="144">
-        <v>7781.0089492021225</v>
-      </c>
-      <c r="I14" s="180">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="181"/>
+        <v>2716.04</v>
+      </c>
+      <c r="I14" s="235">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="236"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="139">
@@ -4787,17 +4811,18 @@
         <v>89</v>
       </c>
       <c r="E15" s="143">
-        <v>10351.832144880002</v>
+        <v>2222.21</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="144">
-        <v>10351.832144880002</v>
-      </c>
-      <c r="I15" s="180">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="181"/>
+        <v>2222.21</v>
+      </c>
+      <c r="I15" s="235">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="236"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="138">
@@ -4807,17 +4832,18 @@
         <v>87</v>
       </c>
       <c r="E16" s="143">
-        <v>49509.655303807594</v>
+        <v>36166.800000000003</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="144">
-        <v>49509.655303807594</v>
-      </c>
-      <c r="I16" s="180">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="181"/>
+        <v>36166.800000000003</v>
+      </c>
+      <c r="I16" s="235">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="236"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="139">
@@ -4827,17 +4853,18 @@
         <v>90</v>
       </c>
       <c r="E17" s="143">
-        <v>16866.513739552778</v>
+        <v>2716.04</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="144">
-        <v>16866.513739552778</v>
-      </c>
-      <c r="I17" s="180">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="181"/>
+        <v>2716.04</v>
+      </c>
+      <c r="I17" s="235">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="236"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="138">
@@ -4847,17 +4874,18 @@
         <v>88</v>
       </c>
       <c r="E18" s="143">
-        <v>24968.536052597399</v>
+        <v>9014.634</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="144">
-        <v>24968.536052597399</v>
-      </c>
-      <c r="I18" s="180">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="181"/>
+        <v>9014.634</v>
+      </c>
+      <c r="I18" s="235">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="236"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="139">
@@ -4867,42 +4895,47 @@
         <v>89</v>
       </c>
       <c r="E19" s="143">
-        <v>10779.178697518902</v>
+        <v>2222.21</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="144">
-        <v>10779.178697518902</v>
-      </c>
-      <c r="I19" s="180">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="181"/>
+        <v>2222.21</v>
+      </c>
+      <c r="I19" s="235">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="236"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="138"/>
       <c r="C20" s="138"/>
       <c r="E20" s="138"/>
       <c r="G20" s="142"/>
-      <c r="I20" s="180"/>
-      <c r="J20" s="181"/>
+      <c r="I20" s="235"/>
+      <c r="J20" s="236"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="138"/>
-      <c r="C21" s="138"/>
-      <c r="E21" s="147">
+      <c r="B21" s="239" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" s="239"/>
+      <c r="D21" s="240"/>
+      <c r="E21" s="241">
         <f>SUM(E5:E20)</f>
-        <v>347109.83721539041</v>
-      </c>
-      <c r="G21" s="144">
+        <v>144169.02399999998</v>
+      </c>
+      <c r="F21" s="242"/>
+      <c r="G21" s="241">
         <f>SUM(G5:G20)</f>
-        <v>347109.83721539041</v>
-      </c>
-      <c r="I21" s="180">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="181"/>
+        <v>144169.02399999998</v>
+      </c>
+      <c r="I21" s="235">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="236"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="138" t="s">
@@ -4912,16 +4945,17 @@
         <v>1</v>
       </c>
       <c r="E22" s="149">
-        <v>723.43331893167124</v>
+        <v>288.06</v>
       </c>
       <c r="G22" s="150">
-        <v>723.43331893167124</v>
-      </c>
-      <c r="I22" s="180">
-        <f t="shared" ref="I22" si="1">E22-G22</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="181"/>
+        <f>E22</f>
+        <v>288.06</v>
+      </c>
+      <c r="I22" s="235">
+        <f t="shared" ref="I22" si="2">E22-G22</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="236"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="138" t="s">
@@ -4931,16 +4965,17 @@
         <v>2</v>
       </c>
       <c r="E23" s="149">
-        <v>620.08570194143249</v>
+        <v>246.91</v>
       </c>
       <c r="G23" s="150">
-        <v>620.08570194143249</v>
-      </c>
-      <c r="I23" s="180">
-        <f t="shared" ref="I23:I31" si="2">E23-G23</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="181"/>
+        <f t="shared" ref="G23:G29" si="3">E23</f>
+        <v>246.91</v>
+      </c>
+      <c r="I23" s="235">
+        <f t="shared" ref="I23:I31" si="4">E23-G23</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="236"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="138" t="s">
@@ -4950,16 +4985,17 @@
         <v>3</v>
       </c>
       <c r="E24" s="149">
-        <v>620.08570194143249</v>
+        <v>246.91</v>
       </c>
       <c r="G24" s="150">
-        <v>620.08570194143249</v>
-      </c>
-      <c r="I24" s="180">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="181"/>
+        <f t="shared" si="3"/>
+        <v>246.91</v>
+      </c>
+      <c r="I24" s="235">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="236"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="138" t="s">
@@ -4969,16 +5005,17 @@
         <v>4</v>
       </c>
       <c r="E25" s="149">
-        <v>620.08570194143249</v>
+        <v>246.91</v>
       </c>
       <c r="G25" s="150">
-        <v>620.08570194143249</v>
-      </c>
-      <c r="I25" s="180">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="181"/>
+        <f t="shared" si="3"/>
+        <v>246.91</v>
+      </c>
+      <c r="I25" s="235">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="236"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="138" t="s">
@@ -4988,16 +5025,17 @@
         <v>5</v>
       </c>
       <c r="E26" s="149">
-        <v>620.08570194143249</v>
+        <v>246.91</v>
       </c>
       <c r="G26" s="150">
-        <v>620.08570194143249</v>
-      </c>
-      <c r="I26" s="180">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="181"/>
+        <f t="shared" si="3"/>
+        <v>246.91</v>
+      </c>
+      <c r="I26" s="235">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="236"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="138" t="s">
@@ -5007,16 +5045,17 @@
         <v>6</v>
       </c>
       <c r="E27" s="149">
-        <v>310.04285097071624</v>
+        <v>123.46</v>
       </c>
       <c r="G27" s="150">
-        <v>310.04285097071624</v>
-      </c>
-      <c r="I27" s="180">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J27" s="181"/>
+        <f t="shared" si="3"/>
+        <v>123.46</v>
+      </c>
+      <c r="I27" s="235">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="236"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="138" t="s">
@@ -5026,16 +5065,17 @@
         <v>7</v>
       </c>
       <c r="E28" s="149">
-        <v>310.04285097071624</v>
+        <v>123.46</v>
       </c>
       <c r="G28" s="150">
-        <v>310.04285097071624</v>
-      </c>
-      <c r="I28" s="180">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="181"/>
+        <f t="shared" si="3"/>
+        <v>123.46</v>
+      </c>
+      <c r="I28" s="235">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="236"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="138" t="s">
@@ -5045,64 +5085,86 @@
         <v>8</v>
       </c>
       <c r="E29" s="149">
-        <v>310.04285097071624</v>
+        <v>123.46</v>
       </c>
       <c r="G29" s="150">
-        <v>310.04285097071624</v>
-      </c>
-      <c r="I29" s="180">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="181"/>
+        <f t="shared" si="3"/>
+        <v>123.46</v>
+      </c>
+      <c r="I29" s="235">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="236"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E30" s="147">
+      <c r="B30" s="244" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30" s="245"/>
+      <c r="D30" s="243"/>
+      <c r="E30" s="241">
         <f>SUM(E22:E29)</f>
-        <v>4133.9046796095499</v>
-      </c>
-      <c r="G30" s="144">
+        <v>1646.0800000000002</v>
+      </c>
+      <c r="F30" s="243"/>
+      <c r="G30" s="241">
         <f>SUM(G22:G29)</f>
-        <v>4133.9046796095499</v>
-      </c>
-      <c r="I30" s="180">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="181"/>
+        <v>1646.0800000000002</v>
+      </c>
+      <c r="I30" s="235">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="236"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E31" s="147"/>
       <c r="G31" s="144"/>
-      <c r="I31" s="180">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="181"/>
+      <c r="I31" s="235">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="236"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E32" s="145"/>
       <c r="G32" s="146"/>
-      <c r="I32" s="180"/>
-      <c r="J32" s="181"/>
+      <c r="I32" s="235"/>
+      <c r="J32" s="236"/>
     </row>
     <row r="33" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E33" s="147">
         <f>E30+E21</f>
-        <v>351243.74189499998</v>
+        <v>145815.10399999996</v>
       </c>
       <c r="G33" s="144">
         <f>G21+G30</f>
-        <v>351243.74189499998</v>
-      </c>
-      <c r="I33" s="180">
+        <v>145815.10399999996</v>
+      </c>
+      <c r="I33" s="235">
         <f>E33-G33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="181"/>
+      <c r="J33" s="236"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
@@ -5119,21 +5181,6 @@
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>

--- a/SALTA 1167/Diciembre/SALTA1167-Diciembre.xlsx
+++ b/SALTA 1167/Diciembre/SALTA1167-Diciembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\SALTA 1167\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\SALTA 1167\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925466A4-DAAC-42F4-82A5-F326B30279E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52AE0A0-9FB9-4125-9F30-EDD3B686CE4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,14 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">EDESUR!$B$3:$J$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$95</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$97</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="143">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -270,9 +270,6 @@
     <t>CUIT DEL EDIFICIO: 30-719118061-9</t>
   </si>
   <si>
-    <t>Federacion patronal  Seguro obligatorio de consorcio - Poliza nro. 2223190</t>
-  </si>
-  <si>
     <t>CONSORCIO DE PROPIETARIOS EDIFICIO CALLE SALTA 1167/1169                                                                                                                                                                                           C DE P SALTA 1167 1169 LANUS           
 CTA CTE $   039 - 22273/6  CBU: 0720039720000002227368</t>
   </si>
@@ -308,9 +305,6 @@
   </si>
   <si>
     <t>Total Edesur x Depto</t>
-  </si>
-  <si>
-    <t>Bonificado x EDESUR</t>
   </si>
   <si>
     <t>SALDO a PAGAR</t>
@@ -451,6 +445,21 @@
   </si>
   <si>
     <t>Totales</t>
+  </si>
+  <si>
+    <t>Bonificado x EDESUR Noviembre</t>
+  </si>
+  <si>
+    <t>Sr. Hector Piletero</t>
+  </si>
+  <si>
+    <t>Transf 30/12</t>
+  </si>
+  <si>
+    <t>Transf 29/12</t>
+  </si>
+  <si>
+    <t>Federacion patronal  Seguro obligatorio de consorcio - Poliza nro. 1-2249124-0</t>
   </si>
 </sst>
 </file>
@@ -468,7 +477,7 @@
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -662,13 +671,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1114,7 +1116,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="246">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1332,9 +1334,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1363,14 +1362,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="26" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="26" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1379,7 +1370,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="17" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="26" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="13" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="11" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1425,145 +1415,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="17" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="26" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="13" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="12" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="12" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="12" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="12" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1575,6 +1432,137 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1939,22 +1927,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M99"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M101"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
       <c r="B1" s="51" t="s">
         <v>78</v>
@@ -1963,7 +1951,7 @@
       <c r="D1" s="51"/>
       <c r="E1" s="52"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="53" t="s">
         <v>14</v>
@@ -1972,16 +1960,16 @@
       <c r="D2" s="53"/>
       <c r="E2" s="54"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
-      <c r="B3" s="197" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" s="197"/>
-      <c r="D3" s="197"/>
-      <c r="E3" s="198"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="201" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="201"/>
+      <c r="D3" s="201"/>
+      <c r="E3" s="202"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
@@ -1992,12 +1980,12 @@
       <c r="D4" s="18"/>
       <c r="E4" s="19"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>79</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="53" t="s">
@@ -2005,7 +1993,7 @@
       </c>
       <c r="E5" s="16"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>26</v>
       </c>
@@ -2016,97 +2004,97 @@
       </c>
       <c r="E6" s="19"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="200" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="200"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="200"/>
-      <c r="C9" s="200"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="200"/>
-      <c r="C10" s="200"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="199" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" s="199"/>
-      <c r="C13" s="199"/>
-      <c r="D13" s="199"/>
-      <c r="E13" s="199"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="199"/>
-      <c r="B14" s="199"/>
-      <c r="C14" s="199"/>
-      <c r="D14" s="199"/>
-      <c r="E14" s="199"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="199"/>
-      <c r="B15" s="199"/>
-      <c r="C15" s="199"/>
-      <c r="D15" s="199"/>
-      <c r="E15" s="199"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="199"/>
-      <c r="B16" s="199"/>
-      <c r="C16" s="199"/>
-      <c r="D16" s="199"/>
-      <c r="E16" s="199"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="204" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="204"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="204"/>
+      <c r="C9" s="204"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="204"/>
+      <c r="C10" s="204"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="203" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="203"/>
+      <c r="C13" s="203"/>
+      <c r="D13" s="203"/>
+      <c r="E13" s="203"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="203"/>
+      <c r="B14" s="203"/>
+      <c r="C14" s="203"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="203"/>
+      <c r="B15" s="203"/>
+      <c r="C15" s="203"/>
+      <c r="D15" s="203"/>
+      <c r="E15" s="203"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="203"/>
+      <c r="B16" s="203"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="203"/>
+      <c r="E16" s="203"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="11"/>
       <c r="D20" s="7"/>
       <c r="E20" s="12"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
       <c r="D21" s="119"/>
       <c r="E21" s="104"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="195" t="s">
-        <v>122</v>
-      </c>
-      <c r="B22" s="196"/>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="196" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" s="197"/>
       <c r="C22" s="39"/>
-      <c r="D22" s="153">
+      <c r="D22" s="120">
         <v>464897.27</v>
       </c>
       <c r="E22" s="113" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H22" s="93"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="195"/>
-      <c r="B23" s="196"/>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="196"/>
+      <c r="B23" s="197"/>
       <c r="C23" s="39"/>
       <c r="D23" s="120"/>
       <c r="E23" s="113"/>
       <c r="H23" s="93"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
         <v>9</v>
       </c>
@@ -2118,7 +2106,7 @@
         <v>464897.27</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
         <v>18</v>
       </c>
@@ -2127,20 +2115,20 @@
       <c r="D25" s="122"/>
       <c r="E25" s="133"/>
     </row>
-    <row r="26" spans="1:8" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="201" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" s="202"/>
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="196" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26" s="197"/>
       <c r="C26" s="41"/>
-      <c r="D26" s="155">
+      <c r="D26" s="195">
         <v>74591</v>
       </c>
       <c r="E26" s="106" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
         <v>1</v>
       </c>
@@ -2152,7 +2140,7 @@
         <v>74591</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>10</v>
       </c>
@@ -2161,7 +2149,7 @@
       <c r="D28" s="123"/>
       <c r="E28" s="109"/>
     </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>70</v>
       </c>
@@ -2172,59 +2160,59 @@
       </c>
       <c r="E29" s="113"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="154">
+      <c r="D30" s="114">
         <v>5494.37</v>
       </c>
       <c r="E30" s="113" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B31" s="130"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="154">
+      <c r="D31" s="114">
         <v>323182.89</v>
       </c>
       <c r="E31" s="113" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="203" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="205" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="204"/>
+      <c r="B32" s="206"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="154">
+      <c r="D32" s="114">
         <v>358176.46</v>
       </c>
       <c r="E32" s="113" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="116" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B33" s="112"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="154">
+      <c r="D33" s="114">
         <v>21236.33</v>
       </c>
       <c r="E33" s="113" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="21" t="s">
         <v>2</v>
       </c>
@@ -2236,518 +2224,539 @@
         <v>708090.04999999993</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="25"/>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
       <c r="D35" s="121"/>
       <c r="E35" s="110"/>
     </row>
-    <row r="36" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="195" t="s">
-        <v>133</v>
-      </c>
-      <c r="B36" s="196"/>
+    <row r="36" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="196" t="s">
+        <v>131</v>
+      </c>
+      <c r="B36" s="197"/>
       <c r="C36" s="5"/>
       <c r="D36" s="114"/>
       <c r="E36" s="115"/>
     </row>
-    <row r="37" spans="1:5" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="195" t="s">
+    <row r="37" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="131" t="s">
+        <v>139</v>
+      </c>
+      <c r="B37" s="132"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="78">
+        <v>82600</v>
+      </c>
+      <c r="E37" s="115" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="196" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" s="197"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="78">
+        <v>1537000</v>
+      </c>
+      <c r="E38" s="115" t="s">
         <v>128</v>
       </c>
-      <c r="B37" s="196"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="152">
-        <v>1537000</v>
-      </c>
-      <c r="E37" s="115" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="195" t="s">
-        <v>123</v>
-      </c>
-      <c r="B38" s="196"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="152">
+    </row>
+    <row r="39" spans="1:5" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="196" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="197"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="78">
+        <v>90000</v>
+      </c>
+      <c r="E39" s="115" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="196" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" s="197"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="78">
         <v>42370</v>
       </c>
-      <c r="E38" s="115" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="195" t="s">
-        <v>134</v>
-      </c>
-      <c r="B39" s="196"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="152">
+      <c r="E40" s="115" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="196" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" s="197"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="78">
         <v>24884.21</v>
       </c>
-      <c r="E39" s="115" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="21" t="s">
+      <c r="E41" s="115" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="105">
-        <f>SUM(D36:D39)</f>
-        <v>1604254.21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="25" t="s">
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="105">
+        <f>SUM(D36:D41)</f>
+        <v>1776854.21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="119"/>
-      <c r="E41" s="104"/>
-    </row>
-    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="195" t="s">
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="119"/>
+      <c r="E43" s="104"/>
+    </row>
+    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="196" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="196"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="153">
+      <c r="B44" s="197"/>
+      <c r="C44" s="39"/>
+      <c r="D44" s="120">
         <v>140000</v>
       </c>
-      <c r="E42" s="137"/>
-    </row>
-    <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="131"/>
-      <c r="B43" s="132"/>
-      <c r="C43" s="39"/>
-      <c r="D43" s="148"/>
-      <c r="E43" s="137"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="21" t="s">
+      <c r="E44" s="137"/>
+    </row>
+    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="131"/>
+      <c r="B45" s="132"/>
+      <c r="C45" s="39"/>
+      <c r="D45" s="147"/>
+      <c r="E45" s="137"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="121"/>
-      <c r="E44" s="134">
-        <f>SUM(D42:D43)</f>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="121"/>
+      <c r="E46" s="134">
+        <f>SUM(D44:D45)</f>
         <v>140000</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="25" t="s">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="21"/>
-      <c r="D45" s="118"/>
-      <c r="E45" s="105"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
+      <c r="B47" s="49"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="118"/>
+      <c r="E47" s="105"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="114"/>
-      <c r="E46" s="111"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="154">
-        <f>40662.21-311.85-1485-4686.04-151.2-720-450</f>
-        <v>32858.120000000003</v>
-      </c>
-      <c r="E47" s="29"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="B48" s="38"/>
-      <c r="C48" s="38"/>
-      <c r="D48" s="80"/>
-      <c r="E48" s="135">
-        <f>SUM(D46:D47)</f>
-        <v>32858.120000000003</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="5"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="114"/>
+      <c r="E48" s="111"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>122</v>
+      </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="75"/>
-      <c r="E49" s="81"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="22" t="s">
+      <c r="D49" s="114">
+        <f>40662.21-311.85-1485-4686.04-151.2-720-450+720+151.2+540</f>
+        <v>34269.32</v>
+      </c>
+      <c r="E49" s="29"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="38"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="80"/>
+      <c r="E50" s="135">
+        <f>SUM(D48:D49)</f>
+        <v>34269.32</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="5"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="75"/>
+      <c r="E51" s="81"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="82"/>
+      <c r="E52" s="136"/>
+    </row>
+    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1"/>
+      <c r="D53" s="83"/>
+      <c r="E53" s="84"/>
+      <c r="F53" s="31"/>
+    </row>
+    <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B54" s="8"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="85"/>
+      <c r="E54" s="86">
+        <f>(SUM(E21:E52))</f>
+        <v>3198701.8499999996</v>
+      </c>
+      <c r="F54" s="103"/>
+      <c r="G54" s="31"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D55" s="83"/>
+      <c r="E55" s="83"/>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D56" s="83"/>
+      <c r="E56" s="83"/>
+      <c r="H56" s="125"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B57" s="10"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="87"/>
+      <c r="E57" s="88"/>
+    </row>
+    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="77"/>
+      <c r="B58" s="112"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="78"/>
+      <c r="E58" s="76"/>
+    </row>
+    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="200"/>
+      <c r="B59" s="200"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="114"/>
+      <c r="E59" s="76"/>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="5"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="77"/>
+      <c r="B61" s="79"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="78"/>
+      <c r="E61" s="76"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="36"/>
+      <c r="B62" s="35"/>
+      <c r="C62" s="35"/>
+      <c r="D62" s="42"/>
+      <c r="E62" s="42">
+        <f>SUM(D58:D61)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B65" s="22"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="23"/>
+      <c r="E65" s="74"/>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B67" s="8"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="50">
+        <f>E62+E65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="B69" s="73">
+        <f>E54</f>
+        <v>3198701.8499999996</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="B70" s="73">
+        <f>E54-E52</f>
+        <v>3198701.8499999996</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="72" t="s">
+        <v>112</v>
+      </c>
+      <c r="B71" s="73">
+        <f>E67-E65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="72" t="s">
+        <v>113</v>
+      </c>
+      <c r="B72" s="73">
+        <f>E67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74"/>
+      <c r="B74" s="30"/>
+      <c r="C74" s="27"/>
+    </row>
+    <row r="75" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="95" t="s">
+        <v>114</v>
+      </c>
+      <c r="B75" s="150">
+        <v>115565.9499999996</v>
+      </c>
+      <c r="C75" s="27"/>
+      <c r="D75" s="34"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="82"/>
-      <c r="E50" s="136"/>
-    </row>
-    <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="1"/>
-      <c r="D51" s="83"/>
-      <c r="E51" s="84"/>
-      <c r="F51" s="31"/>
-    </row>
-    <row r="52" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B52" s="8"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="85"/>
-      <c r="E52" s="86">
-        <f>(SUM(E21:E50))</f>
-        <v>3024690.65</v>
-      </c>
-      <c r="F52" s="103"/>
-      <c r="G52" s="31"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D53" s="83"/>
-      <c r="E53" s="83"/>
-    </row>
-    <row r="54" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D54" s="83"/>
-      <c r="E54" s="83"/>
-      <c r="H54" s="125"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="B55" s="10"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="87"/>
-      <c r="E55" s="88"/>
-    </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="77"/>
-      <c r="B56" s="112"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="78"/>
-      <c r="E56" s="76"/>
-    </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="207"/>
-      <c r="B57" s="207"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="114"/>
-      <c r="E57" s="76"/>
-    </row>
-    <row r="58" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="5"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="77"/>
-      <c r="B59" s="79"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="78"/>
-      <c r="E59" s="76"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="36"/>
-      <c r="B60" s="35"/>
-      <c r="C60" s="35"/>
-      <c r="D60" s="42"/>
-      <c r="E60" s="42">
-        <f>SUM(D56:D59)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="B63" s="22"/>
-      <c r="C63" s="22"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="74"/>
-    </row>
-    <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B65" s="8"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="50">
-        <f>E60+E63</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="72" t="s">
-        <v>112</v>
-      </c>
-      <c r="B67" s="73">
-        <f>E52</f>
-        <v>3024690.65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="72" t="s">
-        <v>113</v>
-      </c>
-      <c r="B68" s="73">
-        <f>E52-E50</f>
-        <v>3024690.65</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="72" t="s">
-        <v>114</v>
-      </c>
-      <c r="B69" s="73">
-        <f>E65-E63</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="72" t="s">
-        <v>115</v>
-      </c>
-      <c r="B70" s="73">
-        <f>E65</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A72"/>
-      <c r="B72" s="30"/>
-      <c r="C72" s="27"/>
-    </row>
-    <row r="73" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="95" t="s">
+      <c r="B76" s="100">
+        <f>-B70</f>
+        <v>-3198701.8499999996</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B77" s="100">
+        <f>B96</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="B73" s="151">
-        <v>115565.9499999996</v>
-      </c>
-      <c r="C73" s="27"/>
-      <c r="D73" s="34"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="B74" s="100">
-        <f>-B68</f>
-        <v>-3024690.65</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="B75" s="100">
-        <f>B94</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="41" t="s">
-        <v>118</v>
-      </c>
-      <c r="B76" s="101">
-        <f>PRORRATEO!G36-B84</f>
+      <c r="B78" s="101">
+        <f>PRORRATEO!G36-B86</f>
         <v>1986908.7200000002</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A77" s="41" t="s">
-        <v>125</v>
-      </c>
-      <c r="B77" s="101">
+    <row r="79" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A79" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="B79" s="101">
         <f>102287.66+2747.19</f>
         <v>105034.85</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="102" t="s">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="B78" s="126"/>
-    </row>
-    <row r="79" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="98" t="s">
-        <v>120</v>
-      </c>
-      <c r="B79" s="99">
-        <f>SUM(B73:C78)</f>
-        <v>-817181.13</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="96"/>
-      <c r="B80" s="96"/>
-      <c r="D80" s="31"/>
-      <c r="E80" s="30"/>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A81" s="95" t="s">
+      <c r="B80" s="126"/>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="98" t="s">
+        <v>118</v>
+      </c>
+      <c r="B81" s="99">
+        <f>SUM(B75:C80)</f>
+        <v>-991192.32999999973</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="96"/>
+      <c r="B82" s="96"/>
+      <c r="D82" s="31"/>
+      <c r="E82" s="30"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="95" t="s">
+        <v>115</v>
+      </c>
+      <c r="B83" s="150">
+        <v>2000000</v>
+      </c>
+      <c r="D83" s="30"/>
+      <c r="E83" s="31"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="B84" s="100">
+        <f>-B71</f>
+        <v>0</v>
+      </c>
+      <c r="D84" s="31"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B85" s="100">
+        <f>B104</f>
+        <v>0</v>
+      </c>
+      <c r="D85" s="31"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="B81" s="151">
+      <c r="B86" s="101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" s="126"/>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="98" t="s">
+        <v>119</v>
+      </c>
+      <c r="B88" s="99">
+        <f>SUM(B83:C87)</f>
         <v>2000000</v>
       </c>
-      <c r="D81" s="30"/>
-      <c r="E81" s="31"/>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A82" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="B82" s="100">
-        <f>-B69</f>
-        <v>0</v>
-      </c>
-      <c r="D82" s="31"/>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A83" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="B83" s="100">
-        <f>B102</f>
-        <v>0</v>
-      </c>
-      <c r="D83" s="31"/>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A84" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="B84" s="101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A85" s="102" t="s">
-        <v>25</v>
-      </c>
-      <c r="B85" s="126"/>
-    </row>
-    <row r="86" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="98" t="s">
-        <v>121</v>
-      </c>
-      <c r="B86" s="99">
-        <f>SUM(B81:C85)</f>
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A87" s="96"/>
-      <c r="B87" s="96"/>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A88" s="96"/>
-      <c r="B88" s="96"/>
-    </row>
-    <row r="89" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A90" s="206" t="s">
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="96"/>
+      <c r="B89" s="96"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="96"/>
+      <c r="B90" s="96"/>
+    </row>
+    <row r="91" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="199" t="s">
         <v>19</v>
       </c>
-      <c r="B90" s="206"/>
-      <c r="C90" s="206"/>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A91" s="206"/>
-      <c r="B91" s="206"/>
-      <c r="C91" s="206"/>
-    </row>
-    <row r="92" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="90"/>
-      <c r="B92" s="26"/>
-      <c r="C92" s="26">
+      <c r="B92" s="199"/>
+      <c r="C92" s="199"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="199"/>
+      <c r="B93" s="199"/>
+      <c r="C93" s="199"/>
+    </row>
+    <row r="94" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="90"/>
+      <c r="B94" s="26"/>
+      <c r="C94" s="26">
         <v>40000</v>
       </c>
-      <c r="E92" s="103"/>
-    </row>
-    <row r="93" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="90"/>
-      <c r="B93" s="92"/>
-      <c r="C93" s="89"/>
-      <c r="D93" s="103"/>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A94" s="32" t="s">
+      <c r="E94" s="103"/>
+    </row>
+    <row r="95" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="90"/>
+      <c r="B95" s="92"/>
+      <c r="C95" s="89"/>
+      <c r="D95" s="103"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B94" s="91">
-        <f>SUM(B92:B93)</f>
-        <v>0</v>
-      </c>
-      <c r="C94" s="33"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M95" s="6"/>
-    </row>
-    <row r="96" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="205"/>
-      <c r="B96" s="205"/>
-      <c r="C96" s="205"/>
-      <c r="D96" s="205"/>
-      <c r="E96" s="205"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="205"/>
-      <c r="B97" s="205"/>
-      <c r="C97" s="205"/>
-      <c r="D97" s="205"/>
-      <c r="E97" s="205"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="205"/>
-      <c r="B98" s="205"/>
-      <c r="C98" s="205"/>
-      <c r="D98" s="205"/>
-      <c r="E98" s="205"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="205"/>
-      <c r="B99" s="205"/>
-      <c r="C99" s="205"/>
-      <c r="D99" s="205"/>
-      <c r="E99" s="205"/>
+      <c r="B96" s="91">
+        <f>SUM(B94:B95)</f>
+        <v>0</v>
+      </c>
+      <c r="C96" s="33"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M97" s="6"/>
+    </row>
+    <row r="98" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="198"/>
+      <c r="B98" s="198"/>
+      <c r="C98" s="198"/>
+      <c r="D98" s="198"/>
+      <c r="E98" s="198"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" s="198"/>
+      <c r="B99" s="198"/>
+      <c r="C99" s="198"/>
+      <c r="D99" s="198"/>
+      <c r="E99" s="198"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" s="198"/>
+      <c r="B100" s="198"/>
+      <c r="C100" s="198"/>
+      <c r="D100" s="198"/>
+      <c r="E100" s="198"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" s="198"/>
+      <c r="B101" s="198"/>
+      <c r="C101" s="198"/>
+      <c r="D101" s="198"/>
+      <c r="E101" s="198"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A96:E99"/>
-    <mergeCell ref="A90:C91"/>
-    <mergeCell ref="A57:B57"/>
+  <mergeCells count="16">
     <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A40:B40"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
@@ -2755,6 +2764,12 @@
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A98:E101"/>
+    <mergeCell ref="A92:C93"/>
+    <mergeCell ref="A59:B59"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2765,91 +2780,91 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.33203125" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="1" max="2" width="4.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
     <col min="14" max="14" width="12" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.21875" customWidth="1"/>
-    <col min="16" max="16" width="7.21875" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" customWidth="1"/>
+    <col min="16" max="16" width="7.28515625" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="169"/>
-      <c r="B1" s="170"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="208"/>
-      <c r="F1" s="208"/>
-      <c r="G1" s="208"/>
-      <c r="H1" s="208"/>
-      <c r="I1" s="208"/>
-      <c r="J1" s="208"/>
-      <c r="K1" s="208"/>
-      <c r="L1" s="208"/>
-      <c r="M1" s="208"/>
-      <c r="N1" s="170"/>
-      <c r="O1" s="172"/>
-    </row>
-    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="173"/>
-      <c r="B2" s="174"/>
-      <c r="C2" s="175"/>
-      <c r="D2" s="176"/>
-      <c r="E2" s="176" t="s">
-        <v>102</v>
-      </c>
-      <c r="F2" s="176"/>
-      <c r="G2" s="177">
-        <v>0</v>
-      </c>
-      <c r="H2" s="176"/>
-      <c r="I2" s="176"/>
-      <c r="J2" s="178"/>
-      <c r="K2" s="176" t="s">
-        <v>101</v>
-      </c>
-      <c r="L2" s="179">
+    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="161"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
+      <c r="L1" s="210"/>
+      <c r="M1" s="210"/>
+      <c r="N1" s="162"/>
+      <c r="O1" s="164"/>
+    </row>
+    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="165"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
+      <c r="D2" s="168"/>
+      <c r="E2" s="168" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="168"/>
+      <c r="G2" s="169">
+        <v>0</v>
+      </c>
+      <c r="H2" s="168"/>
+      <c r="I2" s="168"/>
+      <c r="J2" s="170"/>
+      <c r="K2" s="168" t="s">
+        <v>99</v>
+      </c>
+      <c r="L2" s="171">
         <v>2000000</v>
       </c>
-      <c r="M2" s="180"/>
-      <c r="N2" s="181"/>
-      <c r="O2" s="182"/>
+      <c r="M2" s="172"/>
+      <c r="N2" s="173"/>
+      <c r="O2" s="174"/>
       <c r="P2" s="20"/>
     </row>
-    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="173"/>
-      <c r="B3" s="174"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="175"/>
-      <c r="L3" s="175"/>
-      <c r="M3" s="180"/>
-      <c r="N3" s="181"/>
-      <c r="O3" s="182"/>
+    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="165"/>
+      <c r="B3" s="166"/>
+      <c r="C3" s="167"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="167"/>
+      <c r="F3" s="167"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="167"/>
+      <c r="I3" s="167"/>
+      <c r="J3" s="176"/>
+      <c r="K3" s="167"/>
+      <c r="L3" s="167"/>
+      <c r="M3" s="172"/>
+      <c r="N3" s="173"/>
+      <c r="O3" s="174"/>
       <c r="P3" s="20"/>
     </row>
-    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="220" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B4" s="221"/>
       <c r="C4" s="221"/>
@@ -2867,7 +2882,7 @@
       <c r="O4" s="222"/>
       <c r="P4" s="20"/>
     </row>
-    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="223"/>
       <c r="B5" s="224"/>
       <c r="C5" s="224"/>
@@ -2885,7 +2900,7 @@
       <c r="O5" s="225"/>
       <c r="P5" s="20"/>
     </row>
-    <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="223"/>
       <c r="B6" s="224"/>
       <c r="C6" s="224"/>
@@ -2903,7 +2918,7 @@
       <c r="O6" s="225"/>
       <c r="P6" s="20"/>
     </row>
-    <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="223"/>
       <c r="B7" s="224"/>
       <c r="C7" s="224"/>
@@ -2921,7 +2936,7 @@
       <c r="O7" s="225"/>
       <c r="P7" s="20"/>
     </row>
-    <row r="8" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="226"/>
       <c r="B8" s="227"/>
       <c r="C8" s="227"/>
@@ -2938,9 +2953,9 @@
       <c r="N8" s="227"/>
       <c r="O8" s="228"/>
     </row>
-    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="231" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B9" s="232"/>
       <c r="C9" s="232"/>
@@ -2957,9 +2972,9 @@
       <c r="N9" s="232"/>
       <c r="O9" s="232"/>
     </row>
-    <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="233" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B10" s="233"/>
       <c r="C10" s="233"/>
@@ -2976,72 +2991,72 @@
       <c r="N10" s="233"/>
       <c r="O10" s="233"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="213" t="s">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="207" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="127"/>
-      <c r="C11" s="213" t="s">
+      <c r="C11" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="213" t="s">
+      <c r="D11" s="207" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="213" t="s">
+      <c r="E11" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="209" t="s">
+      <c r="F11" s="211" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="213" t="s">
+      <c r="G11" s="207" t="s">
         <v>5</v>
       </c>
       <c r="H11" s="215" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="209" t="s">
+      <c r="I11" s="211" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="209" t="s">
-        <v>84</v>
-      </c>
-      <c r="K11" s="209" t="s">
-        <v>101</v>
+      <c r="J11" s="211" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="211" t="s">
+        <v>99</v>
       </c>
       <c r="L11" s="218" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M11" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="N11" s="211" t="s">
+      <c r="N11" s="213" t="s">
         <v>12</v>
       </c>
       <c r="O11" s="229" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="214"/>
+    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="209"/>
       <c r="B12" s="128"/>
-      <c r="C12" s="214"/>
-      <c r="D12" s="234"/>
-      <c r="E12" s="214"/>
-      <c r="F12" s="210"/>
-      <c r="G12" s="214"/>
+      <c r="C12" s="209"/>
+      <c r="D12" s="208"/>
+      <c r="E12" s="209"/>
+      <c r="F12" s="212"/>
+      <c r="G12" s="209"/>
       <c r="H12" s="216"/>
-      <c r="I12" s="210"/>
+      <c r="I12" s="212"/>
       <c r="J12" s="217"/>
-      <c r="K12" s="210"/>
+      <c r="K12" s="212"/>
       <c r="L12" s="219"/>
       <c r="M12" s="43" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 15/01</v>
       </c>
-      <c r="N12" s="212"/>
+      <c r="N12" s="214"/>
       <c r="O12" s="230"/>
     </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="46">
         <v>1</v>
       </c>
@@ -3058,7 +3073,7 @@
       <c r="F13" s="56">
         <v>232082.01</v>
       </c>
-      <c r="G13" s="156">
+      <c r="G13" s="57">
         <f>256082.01-G29-G30</f>
         <v>232081.66</v>
       </c>
@@ -3098,7 +3113,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="46">
         <v>2</v>
       </c>
@@ -3115,7 +3130,7 @@
       <c r="F14" s="56">
         <v>132000.01999999999</v>
       </c>
-      <c r="G14" s="156">
+      <c r="G14" s="57">
         <f>F14</f>
         <v>132000.01999999999</v>
       </c>
@@ -3156,7 +3171,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="46">
         <v>3</v>
       </c>
@@ -3175,7 +3190,7 @@
       <c r="F15" s="56">
         <v>108000.03</v>
       </c>
-      <c r="G15" s="156">
+      <c r="G15" s="57">
         <f>F15</f>
         <v>108000.03</v>
       </c>
@@ -3216,7 +3231,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="46">
         <v>4</v>
       </c>
@@ -3235,7 +3250,7 @@
       <c r="F16" s="56">
         <v>129700.04</v>
       </c>
-      <c r="G16" s="156">
+      <c r="G16" s="57">
         <f>154060-G32</f>
         <v>129700</v>
       </c>
@@ -3276,58 +3291,58 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="185">
+    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="177">
         <v>5</v>
       </c>
-      <c r="B17" s="185" t="s">
+      <c r="B17" s="177" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="185" t="s">
+      <c r="C17" s="177" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="185" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="186">
+      <c r="D17" s="177" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="178">
         <v>6.6</v>
       </c>
-      <c r="F17" s="187">
+      <c r="F17" s="179">
         <v>132000.04999999999</v>
       </c>
-      <c r="G17" s="188">
+      <c r="G17" s="179">
         <f t="shared" ref="G17:G21" si="8">F17</f>
         <v>132000.04999999999</v>
       </c>
-      <c r="H17" s="189">
+      <c r="H17" s="180">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="189">
+      <c r="I17" s="180">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="190">
+      <c r="J17" s="181">
         <f>EDESUR!I9</f>
         <v>0</v>
       </c>
-      <c r="K17" s="191">
+      <c r="K17" s="182">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L17" s="191">
+      <c r="L17" s="182">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M17" s="192">
+      <c r="M17" s="183">
         <f t="shared" si="4"/>
         <v>132000.04999999999</v>
       </c>
-      <c r="N17" s="193">
+      <c r="N17" s="184">
         <f t="shared" si="5"/>
         <v>139920.04999999999</v>
       </c>
-      <c r="O17" s="194">
+      <c r="O17" s="185">
         <f t="shared" si="6"/>
         <v>135960.04999999999</v>
       </c>
@@ -3336,10 +3351,10 @@
         <v>0.05</v>
       </c>
       <c r="Q17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="46">
         <v>6</v>
       </c>
@@ -3350,7 +3365,7 @@
         <v>41</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E18" s="55">
         <v>5.4</v>
@@ -3358,7 +3373,7 @@
       <c r="F18" s="56">
         <v>108000.06</v>
       </c>
-      <c r="G18" s="156">
+      <c r="G18" s="57">
         <f t="shared" si="8"/>
         <v>108000.06</v>
       </c>
@@ -3399,58 +3414,58 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="158">
+    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="151">
         <v>7</v>
       </c>
-      <c r="B19" s="158" t="s">
+      <c r="B19" s="151" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="158" t="s">
+      <c r="C19" s="151" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="158" t="s">
-        <v>97</v>
-      </c>
-      <c r="E19" s="160">
+      <c r="D19" s="151" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" s="153">
         <v>5.4</v>
       </c>
-      <c r="F19" s="161">
+      <c r="F19" s="154">
         <v>108000.07</v>
       </c>
-      <c r="G19" s="162">
+      <c r="G19" s="154">
         <f t="shared" si="8"/>
         <v>108000.07</v>
       </c>
-      <c r="H19" s="163">
+      <c r="H19" s="155">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="163">
+      <c r="I19" s="155">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="164">
+      <c r="J19" s="156">
         <f>EDESUR!I11</f>
         <v>0</v>
       </c>
-      <c r="K19" s="165">
+      <c r="K19" s="157">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L19" s="165">
+      <c r="L19" s="157">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M19" s="166">
+      <c r="M19" s="158">
         <f t="shared" si="4"/>
         <v>108000.07</v>
       </c>
-      <c r="N19" s="167">
+      <c r="N19" s="159">
         <f t="shared" si="5"/>
         <v>114480.07</v>
       </c>
-      <c r="O19" s="168">
+      <c r="O19" s="160">
         <f t="shared" si="6"/>
         <v>111240.07</v>
       </c>
@@ -3459,58 +3474,58 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="158">
+    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="151">
         <v>8</v>
       </c>
-      <c r="B20" s="158" t="s">
+      <c r="B20" s="151" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="158" t="s">
+      <c r="C20" s="151" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="159" t="s">
+      <c r="D20" s="152" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="160">
+      <c r="E20" s="153">
         <v>6.6</v>
       </c>
-      <c r="F20" s="161">
+      <c r="F20" s="154">
         <v>132000.07999999999</v>
       </c>
-      <c r="G20" s="162">
+      <c r="G20" s="154">
         <f t="shared" si="8"/>
         <v>132000.07999999999</v>
       </c>
-      <c r="H20" s="163">
+      <c r="H20" s="155">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="163">
+      <c r="I20" s="155">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="164">
+      <c r="J20" s="156">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="K20" s="165">
+      <c r="K20" s="157">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L20" s="165">
+      <c r="L20" s="157">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M20" s="166">
+      <c r="M20" s="158">
         <f t="shared" si="4"/>
         <v>132000.07999999999</v>
       </c>
-      <c r="N20" s="167">
+      <c r="N20" s="159">
         <f t="shared" si="5"/>
         <v>139920.07999999999</v>
       </c>
-      <c r="O20" s="168">
+      <c r="O20" s="160">
         <f t="shared" si="6"/>
         <v>135960.07999999999</v>
       </c>
@@ -3519,7 +3534,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="46">
         <v>9</v>
       </c>
@@ -3538,7 +3553,7 @@
       <c r="F21" s="56">
         <v>132000.09</v>
       </c>
-      <c r="G21" s="156">
+      <c r="G21" s="57">
         <f t="shared" si="8"/>
         <v>132000.09</v>
       </c>
@@ -3579,7 +3594,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="46">
         <v>10</v>
       </c>
@@ -3598,7 +3613,7 @@
       <c r="F22" s="56">
         <v>68000.100000000006</v>
       </c>
-      <c r="G22" s="156">
+      <c r="G22" s="57">
         <f>F22</f>
         <v>68000.100000000006</v>
       </c>
@@ -3639,7 +3654,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="46">
         <v>11</v>
       </c>
@@ -3656,7 +3671,7 @@
       <c r="F23" s="56">
         <v>108000.11</v>
       </c>
-      <c r="G23" s="156">
+      <c r="G23" s="57">
         <f>114000.11-G34</f>
         <v>108000.11</v>
       </c>
@@ -3697,10 +3712,10 @@
         <v>0.10999999999999999</v>
       </c>
       <c r="Q23" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="46">
         <v>12</v>
       </c>
@@ -3719,7 +3734,7 @@
       <c r="F24" s="56">
         <v>132000.12</v>
       </c>
-      <c r="G24" s="156">
+      <c r="G24" s="57">
         <f>F24</f>
         <v>132000.12</v>
       </c>
@@ -3760,7 +3775,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="46">
         <v>13</v>
       </c>
@@ -3771,7 +3786,7 @@
         <v>55</v>
       </c>
       <c r="D25" s="47" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E25" s="55">
         <v>6.6</v>
@@ -3779,7 +3794,7 @@
       <c r="F25" s="56">
         <v>128040.13</v>
       </c>
-      <c r="G25" s="156">
+      <c r="G25" s="57">
         <v>131881.13</v>
       </c>
       <c r="H25" s="58">
@@ -3819,7 +3834,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="46">
         <v>14</v>
       </c>
@@ -3836,8 +3851,8 @@
       <c r="F26" s="56">
         <v>108000.14</v>
       </c>
-      <c r="G26" s="156">
-        <f>F26+RESUMEN!D39</f>
+      <c r="G26" s="57">
+        <f>F26+RESUMEN!D41</f>
         <v>132884.35</v>
       </c>
       <c r="H26" s="58">
@@ -3877,7 +3892,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="46">
         <v>15</v>
       </c>
@@ -3894,7 +3909,7 @@
       <c r="F27" s="56">
         <v>108000.15</v>
       </c>
-      <c r="G27" s="156">
+      <c r="G27" s="57">
         <f>F27</f>
         <v>108000.15</v>
       </c>
@@ -3935,7 +3950,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="46">
         <v>16</v>
       </c>
@@ -3946,7 +3961,7 @@
         <v>41</v>
       </c>
       <c r="D28" s="46" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E28" s="55">
         <v>0.7</v>
@@ -3954,7 +3969,7 @@
       <c r="F28" s="56">
         <v>14000.16</v>
       </c>
-      <c r="G28" s="156">
+      <c r="G28" s="57">
         <f>F28</f>
         <v>14000.16</v>
       </c>
@@ -3995,7 +4010,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="46">
         <v>17</v>
       </c>
@@ -4012,7 +4027,7 @@
       <c r="F29" s="57">
         <v>12000.17</v>
       </c>
-      <c r="G29" s="156">
+      <c r="G29" s="57">
         <f t="shared" ref="G29:G31" si="9">F29</f>
         <v>12000.17</v>
       </c>
@@ -4053,7 +4068,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="46">
         <v>18</v>
       </c>
@@ -4070,7 +4085,7 @@
       <c r="F30" s="56">
         <v>12000.18</v>
       </c>
-      <c r="G30" s="156">
+      <c r="G30" s="57">
         <f t="shared" si="9"/>
         <v>12000.18</v>
       </c>
@@ -4111,7 +4126,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="46">
         <v>19</v>
       </c>
@@ -4128,7 +4143,7 @@
       <c r="F31" s="56">
         <v>12000.19</v>
       </c>
-      <c r="G31" s="156">
+      <c r="G31" s="57">
         <f t="shared" si="9"/>
         <v>12000.19</v>
       </c>
@@ -4166,7 +4181,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="63">
         <v>20</v>
       </c>
@@ -4185,7 +4200,7 @@
       <c r="F32" s="65">
         <v>24360</v>
       </c>
-      <c r="G32" s="156">
+      <c r="G32" s="57">
         <f>F32</f>
         <v>24360</v>
       </c>
@@ -4223,7 +4238,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="63">
         <v>21</v>
       </c>
@@ -4242,7 +4257,7 @@
       <c r="F33" s="65">
         <v>6000</v>
       </c>
-      <c r="G33" s="157">
+      <c r="G33" s="194">
         <f>F33</f>
         <v>6000</v>
       </c>
@@ -4280,7 +4295,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="64">
         <v>22</v>
       </c>
@@ -4297,7 +4312,7 @@
       <c r="F34" s="65">
         <v>6000</v>
       </c>
-      <c r="G34" s="157">
+      <c r="G34" s="194">
         <f>F34</f>
         <v>6000</v>
       </c>
@@ -4335,7 +4350,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="46">
         <v>23</v>
       </c>
@@ -4354,7 +4369,7 @@
       <c r="F35" s="65">
         <v>6000</v>
       </c>
-      <c r="G35" s="157">
+      <c r="G35" s="194">
         <f>F35</f>
         <v>6000</v>
       </c>
@@ -4392,7 +4407,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="68"/>
       <c r="B36" s="68"/>
       <c r="C36" s="69"/>
@@ -4442,99 +4457,94 @@
         <v>2030415.76</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
     </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="205" t="str">
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="198" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="205"/>
-      <c r="E39" s="205"/>
-      <c r="F39" s="205"/>
-      <c r="G39" s="205"/>
-      <c r="H39" s="205"/>
-      <c r="I39" s="205"/>
-      <c r="J39" s="205"/>
-      <c r="K39" s="205"/>
-      <c r="L39" s="205"/>
-      <c r="M39" s="205"/>
-    </row>
-    <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="205"/>
-      <c r="D40" s="205"/>
-      <c r="E40" s="205"/>
-      <c r="F40" s="205"/>
-      <c r="G40" s="205"/>
-      <c r="H40" s="205"/>
-      <c r="I40" s="205"/>
-      <c r="J40" s="205"/>
-      <c r="K40" s="205"/>
-      <c r="L40" s="205"/>
-      <c r="M40" s="205"/>
-    </row>
-    <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="205"/>
-      <c r="D41" s="205"/>
-      <c r="E41" s="205"/>
-      <c r="F41" s="205"/>
-      <c r="G41" s="205"/>
-      <c r="H41" s="205"/>
-      <c r="I41" s="205"/>
-      <c r="J41" s="205"/>
-      <c r="K41" s="205"/>
-      <c r="L41" s="205"/>
-      <c r="M41" s="205"/>
-    </row>
-    <row r="42" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="205"/>
-      <c r="D42" s="205"/>
-      <c r="E42" s="205"/>
-      <c r="F42" s="205"/>
-      <c r="G42" s="205"/>
-      <c r="H42" s="205"/>
-      <c r="I42" s="205"/>
-      <c r="J42" s="205"/>
-      <c r="K42" s="205"/>
-      <c r="L42" s="205"/>
-      <c r="M42" s="205"/>
-    </row>
-    <row r="43" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="205"/>
-      <c r="D43" s="205"/>
-      <c r="E43" s="205"/>
-      <c r="F43" s="205"/>
-      <c r="G43" s="205"/>
-      <c r="H43" s="205"/>
-      <c r="I43" s="205"/>
-      <c r="J43" s="205"/>
-      <c r="K43" s="205"/>
-      <c r="L43" s="205"/>
-      <c r="M43" s="205"/>
-    </row>
-    <row r="44" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="205"/>
-      <c r="D44" s="205"/>
-      <c r="E44" s="205"/>
-      <c r="F44" s="205"/>
-      <c r="G44" s="205"/>
-      <c r="H44" s="205"/>
-      <c r="I44" s="205"/>
-      <c r="J44" s="205"/>
-      <c r="K44" s="205"/>
-      <c r="L44" s="205"/>
-      <c r="M44" s="205"/>
+      <c r="D39" s="198"/>
+      <c r="E39" s="198"/>
+      <c r="F39" s="198"/>
+      <c r="G39" s="198"/>
+      <c r="H39" s="198"/>
+      <c r="I39" s="198"/>
+      <c r="J39" s="198"/>
+      <c r="K39" s="198"/>
+      <c r="L39" s="198"/>
+      <c r="M39" s="198"/>
+    </row>
+    <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="198"/>
+      <c r="D40" s="198"/>
+      <c r="E40" s="198"/>
+      <c r="F40" s="198"/>
+      <c r="G40" s="198"/>
+      <c r="H40" s="198"/>
+      <c r="I40" s="198"/>
+      <c r="J40" s="198"/>
+      <c r="K40" s="198"/>
+      <c r="L40" s="198"/>
+      <c r="M40" s="198"/>
+    </row>
+    <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="198"/>
+      <c r="D41" s="198"/>
+      <c r="E41" s="198"/>
+      <c r="F41" s="198"/>
+      <c r="G41" s="198"/>
+      <c r="H41" s="198"/>
+      <c r="I41" s="198"/>
+      <c r="J41" s="198"/>
+      <c r="K41" s="198"/>
+      <c r="L41" s="198"/>
+      <c r="M41" s="198"/>
+    </row>
+    <row r="42" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="198"/>
+      <c r="D42" s="198"/>
+      <c r="E42" s="198"/>
+      <c r="F42" s="198"/>
+      <c r="G42" s="198"/>
+      <c r="H42" s="198"/>
+      <c r="I42" s="198"/>
+      <c r="J42" s="198"/>
+      <c r="K42" s="198"/>
+      <c r="L42" s="198"/>
+      <c r="M42" s="198"/>
+    </row>
+    <row r="43" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="198"/>
+      <c r="D43" s="198"/>
+      <c r="E43" s="198"/>
+      <c r="F43" s="198"/>
+      <c r="G43" s="198"/>
+      <c r="H43" s="198"/>
+      <c r="I43" s="198"/>
+      <c r="J43" s="198"/>
+      <c r="K43" s="198"/>
+      <c r="L43" s="198"/>
+      <c r="M43" s="198"/>
+    </row>
+    <row r="44" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="198"/>
+      <c r="D44" s="198"/>
+      <c r="E44" s="198"/>
+      <c r="F44" s="198"/>
+      <c r="G44" s="198"/>
+      <c r="H44" s="198"/>
+      <c r="I44" s="198"/>
+      <c r="J44" s="198"/>
+      <c r="K44" s="198"/>
+      <c r="L44" s="198"/>
+      <c r="M44" s="198"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C39:M44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
     <mergeCell ref="E1:M1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4548,623 +4558,613 @@
     <mergeCell ref="O11:O12"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="A10:O10"/>
+    <mergeCell ref="C39:M44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B3:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" customWidth="1"/>
-    <col min="6" max="6" width="4.5546875" customWidth="1"/>
-    <col min="7" max="7" width="24.44140625" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" customWidth="1"/>
+    <col min="7" max="7" width="24.42578125" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="138" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="138" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="138" t="s">
-        <v>86</v>
-      </c>
       <c r="E3" s="140" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="193" t="s">
+        <v>138</v>
+      </c>
+      <c r="I3" s="236" t="s">
         <v>92</v>
       </c>
-      <c r="G3" s="141" t="s">
-        <v>93</v>
-      </c>
-      <c r="I3" s="237" t="s">
-        <v>94</v>
-      </c>
-      <c r="J3" s="238"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J3" s="237"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="138"/>
       <c r="C4" s="138"/>
       <c r="E4" s="138"/>
-      <c r="G4" s="142"/>
-      <c r="I4" s="237"/>
-      <c r="J4" s="238"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G4" s="141"/>
+      <c r="I4" s="236"/>
+      <c r="J4" s="237"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="138">
         <v>1</v>
       </c>
       <c r="C5" s="138" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="143">
+        <v>86</v>
+      </c>
+      <c r="E5" s="142">
         <v>26132.02</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="144">
+      <c r="G5" s="143">
         <f>E5</f>
         <v>26132.02</v>
       </c>
-      <c r="I5" s="235">
+      <c r="I5" s="234">
         <f>E5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="236"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J5" s="235"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="138">
         <v>1</v>
       </c>
       <c r="C6" s="138" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" s="143">
+        <v>87</v>
+      </c>
+      <c r="E6" s="142">
         <v>12925.66</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="144">
+      <c r="G6" s="143">
         <f t="shared" ref="G6:G19" si="0">E6</f>
         <v>12925.66</v>
       </c>
-      <c r="I6" s="235">
+      <c r="I6" s="234">
         <f t="shared" ref="I6:I21" si="1">E6-G6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="236"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J6" s="235"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="138">
         <v>1</v>
       </c>
       <c r="C7" s="138" t="s">
-        <v>89</v>
-      </c>
-      <c r="E7" s="143">
+        <v>88</v>
+      </c>
+      <c r="E7" s="142">
         <v>10709.96</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="144">
+      <c r="G7" s="143">
         <f t="shared" si="0"/>
         <v>10709.96</v>
       </c>
-      <c r="I7" s="235">
+      <c r="I7" s="234">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J7" s="236"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J7" s="235"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="138">
         <v>2</v>
       </c>
       <c r="C8" s="138" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="143">
+        <v>86</v>
+      </c>
+      <c r="E8" s="142">
         <v>5448.33</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="144">
+      <c r="G8" s="143">
         <f t="shared" si="0"/>
         <v>5448.33</v>
       </c>
-      <c r="I8" s="235">
+      <c r="I8" s="234">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J8" s="236"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J8" s="235"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="139">
         <v>2</v>
       </c>
       <c r="C9" s="139" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" s="143">
+        <v>89</v>
+      </c>
+      <c r="E9" s="142">
         <v>2716.04</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="144">
+      <c r="G9" s="143">
         <f t="shared" si="0"/>
         <v>2716.04</v>
       </c>
-      <c r="I9" s="235">
+      <c r="I9" s="234">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J9" s="236"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J9" s="235"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="139">
         <v>2</v>
       </c>
       <c r="C10" s="139" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" s="143">
+        <v>87</v>
+      </c>
+      <c r="E10" s="142">
         <v>2716.04</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="144">
+      <c r="G10" s="143">
         <f t="shared" si="0"/>
         <v>2716.04</v>
       </c>
-      <c r="I10" s="235">
+      <c r="I10" s="234">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J10" s="236"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J10" s="235"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="139">
         <v>2</v>
       </c>
       <c r="C11" s="139" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" s="143">
+        <v>88</v>
+      </c>
+      <c r="E11" s="142">
         <v>2222.21</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="144">
+      <c r="G11" s="143">
         <f t="shared" si="0"/>
         <v>2222.21</v>
       </c>
-      <c r="I11" s="235">
+      <c r="I11" s="234">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J11" s="236"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J11" s="235"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="139">
         <v>3</v>
       </c>
       <c r="C12" s="139" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" s="143">
+        <v>86</v>
+      </c>
+      <c r="E12" s="142">
         <v>2222.21</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="144">
+      <c r="G12" s="143">
         <f t="shared" si="0"/>
         <v>2222.21</v>
       </c>
-      <c r="I12" s="235">
+      <c r="I12" s="234">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J12" s="236"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J12" s="235"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="138">
         <v>3</v>
       </c>
       <c r="C13" s="138" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" s="143">
+        <v>89</v>
+      </c>
+      <c r="E13" s="142">
         <v>24018.62</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="144">
+      <c r="G13" s="143">
         <f t="shared" si="0"/>
         <v>24018.62</v>
       </c>
-      <c r="I13" s="235">
+      <c r="I13" s="234">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J13" s="236"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J13" s="235"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="139">
         <v>3</v>
       </c>
       <c r="C14" s="139" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" s="143">
+        <v>87</v>
+      </c>
+      <c r="E14" s="142">
         <v>2716.04</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="144">
+      <c r="G14" s="143">
         <f t="shared" si="0"/>
         <v>2716.04</v>
       </c>
-      <c r="I14" s="235">
+      <c r="I14" s="234">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J14" s="236"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J14" s="235"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="139">
         <v>3</v>
       </c>
       <c r="C15" s="139" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" s="143">
+        <v>88</v>
+      </c>
+      <c r="E15" s="142">
         <v>2222.21</v>
       </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="144">
+      <c r="G15" s="143">
         <f t="shared" si="0"/>
         <v>2222.21</v>
       </c>
-      <c r="I15" s="235">
+      <c r="I15" s="234">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="236"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J15" s="235"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="138">
         <v>4</v>
       </c>
       <c r="C16" s="138" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" s="143">
+        <v>86</v>
+      </c>
+      <c r="E16" s="142">
         <v>36166.800000000003</v>
       </c>
       <c r="F16" s="2"/>
-      <c r="G16" s="144">
+      <c r="G16" s="143">
         <f t="shared" si="0"/>
         <v>36166.800000000003</v>
       </c>
-      <c r="I16" s="235">
+      <c r="I16" s="234">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J16" s="236"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J16" s="235"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="139">
         <v>4</v>
       </c>
       <c r="C17" s="139" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" s="143">
+        <v>89</v>
+      </c>
+      <c r="E17" s="142">
         <v>2716.04</v>
       </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="144">
+      <c r="G17" s="143">
         <f t="shared" si="0"/>
         <v>2716.04</v>
       </c>
-      <c r="I17" s="235">
+      <c r="I17" s="234">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="236"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J17" s="235"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="138">
         <v>4</v>
       </c>
       <c r="C18" s="138" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" s="143">
+        <v>87</v>
+      </c>
+      <c r="E18" s="142">
         <v>9014.634</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="144">
+      <c r="G18" s="143">
         <f t="shared" si="0"/>
         <v>9014.634</v>
       </c>
-      <c r="I18" s="235">
+      <c r="I18" s="234">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J18" s="236"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J18" s="235"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="139">
         <v>4</v>
       </c>
       <c r="C19" s="139" t="s">
-        <v>89</v>
-      </c>
-      <c r="E19" s="143">
+        <v>88</v>
+      </c>
+      <c r="E19" s="142">
         <v>2222.21</v>
       </c>
       <c r="F19" s="2"/>
-      <c r="G19" s="144">
+      <c r="G19" s="143">
         <f t="shared" si="0"/>
         <v>2222.21</v>
       </c>
-      <c r="I19" s="235">
+      <c r="I19" s="234">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="236"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J19" s="235"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="138"/>
       <c r="C20" s="138"/>
       <c r="E20" s="138"/>
-      <c r="G20" s="142"/>
-      <c r="I20" s="235"/>
-      <c r="J20" s="236"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="239" t="s">
-        <v>139</v>
-      </c>
-      <c r="C21" s="239"/>
-      <c r="D21" s="240"/>
-      <c r="E21" s="241">
+      <c r="G20" s="141"/>
+      <c r="I20" s="234"/>
+      <c r="J20" s="235"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="186" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" s="186"/>
+      <c r="D21" s="187"/>
+      <c r="E21" s="188">
         <f>SUM(E5:E20)</f>
         <v>144169.02399999998</v>
       </c>
-      <c r="F21" s="242"/>
-      <c r="G21" s="241">
+      <c r="F21" s="189"/>
+      <c r="G21" s="188">
         <f>SUM(G5:G20)</f>
         <v>144169.02399999998</v>
       </c>
-      <c r="I21" s="235">
+      <c r="I21" s="234">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="236"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J21" s="235"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="138" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C22" s="138">
         <v>1</v>
       </c>
-      <c r="E22" s="149">
+      <c r="E22" s="148">
         <v>288.06</v>
       </c>
-      <c r="G22" s="150">
+      <c r="G22" s="149">
         <f>E22</f>
         <v>288.06</v>
       </c>
-      <c r="I22" s="235">
+      <c r="I22" s="234">
         <f t="shared" ref="I22" si="2">E22-G22</f>
         <v>0</v>
       </c>
-      <c r="J22" s="236"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J22" s="235"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="138" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C23" s="138">
         <v>2</v>
       </c>
-      <c r="E23" s="149">
+      <c r="E23" s="148">
         <v>246.91</v>
       </c>
-      <c r="G23" s="150">
+      <c r="G23" s="149">
         <f t="shared" ref="G23:G29" si="3">E23</f>
         <v>246.91</v>
       </c>
-      <c r="I23" s="235">
+      <c r="I23" s="234">
         <f t="shared" ref="I23:I31" si="4">E23-G23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="236"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J23" s="235"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="138" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C24" s="138">
         <v>3</v>
       </c>
-      <c r="E24" s="149">
+      <c r="E24" s="148">
         <v>246.91</v>
       </c>
-      <c r="G24" s="150">
+      <c r="G24" s="149">
         <f t="shared" si="3"/>
         <v>246.91</v>
       </c>
-      <c r="I24" s="235">
+      <c r="I24" s="234">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J24" s="236"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J24" s="235"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="138" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C25" s="138">
         <v>4</v>
       </c>
-      <c r="E25" s="149">
+      <c r="E25" s="148">
         <v>246.91</v>
       </c>
-      <c r="G25" s="150">
+      <c r="G25" s="149">
         <f t="shared" si="3"/>
         <v>246.91</v>
       </c>
-      <c r="I25" s="235">
+      <c r="I25" s="234">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J25" s="236"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J25" s="235"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="138" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C26" s="138">
         <v>5</v>
       </c>
-      <c r="E26" s="149">
+      <c r="E26" s="148">
         <v>246.91</v>
       </c>
-      <c r="G26" s="150">
+      <c r="G26" s="149">
         <f t="shared" si="3"/>
         <v>246.91</v>
       </c>
-      <c r="I26" s="235">
+      <c r="I26" s="234">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J26" s="236"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J26" s="235"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="138" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C27" s="138">
         <v>6</v>
       </c>
-      <c r="E27" s="149">
+      <c r="E27" s="148">
         <v>123.46</v>
       </c>
-      <c r="G27" s="150">
+      <c r="G27" s="149">
         <f t="shared" si="3"/>
         <v>123.46</v>
       </c>
-      <c r="I27" s="235">
+      <c r="I27" s="234">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J27" s="236"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J27" s="235"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="138" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C28" s="138">
         <v>7</v>
       </c>
-      <c r="E28" s="149">
+      <c r="E28" s="148">
         <v>123.46</v>
       </c>
-      <c r="G28" s="150">
+      <c r="G28" s="149">
         <f t="shared" si="3"/>
         <v>123.46</v>
       </c>
-      <c r="I28" s="235">
+      <c r="I28" s="234">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J28" s="236"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J28" s="235"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="138" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C29" s="138">
         <v>8</v>
       </c>
-      <c r="E29" s="149">
+      <c r="E29" s="148">
         <v>123.46</v>
       </c>
-      <c r="G29" s="150">
+      <c r="G29" s="149">
         <f t="shared" si="3"/>
         <v>123.46</v>
       </c>
-      <c r="I29" s="235">
+      <c r="I29" s="234">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J29" s="236"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B30" s="244" t="s">
-        <v>139</v>
-      </c>
-      <c r="C30" s="245"/>
-      <c r="D30" s="243"/>
-      <c r="E30" s="241">
+      <c r="J29" s="235"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="191" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="192"/>
+      <c r="D30" s="190"/>
+      <c r="E30" s="188">
         <f>SUM(E22:E29)</f>
         <v>1646.0800000000002</v>
       </c>
-      <c r="F30" s="243"/>
-      <c r="G30" s="241">
+      <c r="F30" s="190"/>
+      <c r="G30" s="188">
         <f>SUM(G22:G29)</f>
         <v>1646.0800000000002</v>
       </c>
-      <c r="I30" s="235">
+      <c r="I30" s="234">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J30" s="236"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E31" s="147"/>
-      <c r="G31" s="144"/>
-      <c r="I31" s="235">
+      <c r="J30" s="235"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E31" s="146"/>
+      <c r="G31" s="143"/>
+      <c r="I31" s="234">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J31" s="236"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E32" s="145"/>
-      <c r="G32" s="146"/>
-      <c r="I32" s="235"/>
-      <c r="J32" s="236"/>
-    </row>
-    <row r="33" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E33" s="147">
+      <c r="J31" s="235"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E32" s="144"/>
+      <c r="G32" s="145"/>
+      <c r="I32" s="234"/>
+      <c r="J32" s="235"/>
+    </row>
+    <row r="33" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E33" s="146">
         <f>E30+E21</f>
         <v>145815.10399999996</v>
       </c>
-      <c r="G33" s="144">
+      <c r="G33" s="143">
         <f>G21+G30</f>
         <v>145815.10399999996</v>
       </c>
-      <c r="I33" s="235">
+      <c r="I33" s="234">
         <f>E33-G33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="236"/>
+      <c r="J33" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
@@ -5181,6 +5181,21 @@
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>
